--- a/data/DOFRB (TRY).xlsx
+++ b/data/DOFRB (TRY).xlsx
@@ -12,6 +12,28 @@
     <sheet name="Nakit Akış (Yıllıklan.)" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -381,14 +403,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:G108"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -396,18 +419,21 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -421,18 +447,21 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
+        <v>748413520</v>
+      </c>
+      <c r="C3">
         <v>516010545</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>117905827</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>120679477</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>29194628</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>6708976</v>
       </c>
     </row>
@@ -446,15 +475,18 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
+        <v>7286168</v>
+      </c>
+      <c r="C5">
         <v>534116849</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>2337435</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>1012756</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>444517</v>
       </c>
     </row>
@@ -468,18 +500,21 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
+        <v>564667465</v>
+      </c>
+      <c r="C7">
         <v>590961781</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>440929382</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>347849858</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>99283950</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>81662318</v>
       </c>
     </row>
@@ -498,18 +533,21 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
+        <v>3856413</v>
+      </c>
+      <c r="C10">
         <v>4320152</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>1171797</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>1548311</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>3670090</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>2710876</v>
       </c>
     </row>
@@ -533,18 +571,21 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
+        <v>285137876</v>
+      </c>
+      <c r="C14">
         <v>182494193</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>188587026</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>183250747</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>122946935</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>18517674</v>
       </c>
     </row>
@@ -563,18 +604,21 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
+        <v>717180804</v>
+      </c>
+      <c r="C17">
         <v>453480800</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>267628894</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>259174235</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>144886018</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>9489964</v>
       </c>
     </row>
@@ -588,15 +632,18 @@
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>3153645</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>1851961</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>143803</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>95910</v>
       </c>
     </row>
@@ -610,18 +657,21 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
+        <v>88162783</v>
+      </c>
+      <c r="C21">
         <v>22229174</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>3775018</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>1234881</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>2786326</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>2222577</v>
       </c>
     </row>
@@ -629,7 +679,7 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>1930468853</v>
       </c>
     </row>
@@ -643,18 +693,21 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
+        <v>2414705029</v>
+      </c>
+      <c r="C24">
         <v>2306767139</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>1024187340</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>914894068</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>403308374</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>121312385</v>
       </c>
     </row>
@@ -733,18 +786,21 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
+        <v>363064136</v>
+      </c>
+      <c r="C39">
         <v>501657494</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>44724257</v>
       </c>
-      <c r="D39">
-        <v>433953864</v>
-      </c>
       <c r="E39">
+        <v>40510216</v>
+      </c>
+      <c r="F39">
         <v>20556018</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>33376254</v>
       </c>
     </row>
@@ -753,18 +809,21 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
+        <v>516748234</v>
+      </c>
+      <c r="C40">
         <v>55459767</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>482842891</v>
       </c>
-      <c r="D40">
-        <v>40510216</v>
-      </c>
       <c r="E40">
+        <v>433953864</v>
+      </c>
+      <c r="F40">
         <v>365483555</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>234667870</v>
       </c>
     </row>
@@ -773,18 +832,21 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
+        <v>182614672</v>
+      </c>
+      <c r="C41">
         <v>139535609</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>122792475</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>86305492</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>33673650</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>22604133</v>
       </c>
     </row>
@@ -792,7 +854,7 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>4990123</v>
       </c>
     </row>
@@ -800,6 +862,12 @@
       <c r="A43" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
+      <c r="B43">
+        <v>3118996</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -821,18 +889,21 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
+        <v>1065546038</v>
+      </c>
+      <c r="C47">
         <v>696652870</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>650359623</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>560769572</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>419713223</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>295638380</v>
       </c>
     </row>
@@ -841,18 +912,21 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
+        <v>3480251067</v>
+      </c>
+      <c r="C48">
         <v>3003420009</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>1674546963</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>1475663640</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>823021597</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>416950765</v>
       </c>
     </row>
@@ -866,18 +940,21 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
+        <v>332799475</v>
+      </c>
+      <c r="C50">
         <v>354428682</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>522152940</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>234812834</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>31166046</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>15556712</v>
       </c>
     </row>
@@ -886,9 +963,12 @@
         <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
       </c>
       <c r="B51">
+        <v>15185287</v>
+      </c>
+      <c r="C51">
         <v>14939875</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>13124871</v>
       </c>
     </row>
@@ -897,18 +977,21 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
+        <v>208115059</v>
+      </c>
+      <c r="C52">
         <v>108810507</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>37680604</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>127725812</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>35376662</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>37412850</v>
       </c>
     </row>
@@ -922,18 +1005,21 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
+        <v>32659778</v>
+      </c>
+      <c r="C54">
         <v>19784673</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>31424561</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>13872462</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>5744659</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>1858741</v>
       </c>
     </row>
@@ -942,18 +1028,21 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
+        <v>735918</v>
+      </c>
+      <c r="C55">
         <v>63173</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>45749657</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>39504304</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>3814896</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>4738018</v>
       </c>
     </row>
@@ -982,18 +1071,21 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
+        <v>242647453</v>
+      </c>
+      <c r="C60">
         <v>120885733</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>71783211</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>161158999</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>148433940</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>26846317</v>
       </c>
     </row>
@@ -1001,24 +1093,33 @@
       <c r="A61" t="str">
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
+      <c r="B61">
+        <v>647184</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
+        <v>5634424</v>
+      </c>
+      <c r="C62">
         <v>2340361</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>2139804</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>2416736</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>1064897</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>253227</v>
       </c>
     </row>
@@ -1042,18 +1143,21 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
+        <v>838424578</v>
+      </c>
+      <c r="C66">
         <v>621253004</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>710930777</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>592616018</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>225601100</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>86665865</v>
       </c>
     </row>
@@ -1067,18 +1171,21 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
+        <v>79754743</v>
+      </c>
+      <c r="C68">
         <v>116176994</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>556518003</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>84820756</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>422091801</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>251732182</v>
       </c>
     </row>
@@ -1087,9 +1194,12 @@
         <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
       </c>
       <c r="B69">
+        <v>473442200</v>
+      </c>
+      <c r="C69">
         <v>460587636</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>396167992</v>
       </c>
     </row>
@@ -1105,7 +1215,10 @@
       <c r="B71">
         <v>0</v>
       </c>
-      <c r="D71">
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="E71">
         <v>58570096</v>
       </c>
     </row>
@@ -1154,18 +1267,21 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
+        <v>5136343</v>
+      </c>
+      <c r="C80">
         <v>3347440</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>2220756</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>3574212</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>2775816</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>163483</v>
       </c>
     </row>
@@ -1189,18 +1305,21 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
+        <v>558333286</v>
+      </c>
+      <c r="C84">
         <v>580112070</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>558738759</v>
       </c>
-      <c r="D84">
+      <c r="E84">
         <v>543133056</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>424867617</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>251895665</v>
       </c>
     </row>
@@ -1214,18 +1333,21 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
+        <v>2066357708</v>
+      </c>
+      <c r="C86">
         <v>1784506317</v>
       </c>
-      <c r="C86">
+      <c r="D86">
         <v>389722551</v>
       </c>
-      <c r="D86">
+      <c r="E86">
         <v>329451911</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>172168535</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>78389235</v>
       </c>
     </row>
@@ -1237,15 +1359,18 @@
         <v>155000000</v>
       </c>
       <c r="C87">
-        <v>125000000</v>
+        <v>155000000</v>
       </c>
       <c r="D87">
         <v>125000000</v>
       </c>
       <c r="E87">
+        <v>125000000</v>
+      </c>
+      <c r="F87">
         <v>27000000</v>
       </c>
-      <c r="F87">
+      <c r="G87">
         <v>27000000</v>
       </c>
     </row>
@@ -1286,7 +1411,10 @@
       <c r="B94">
         <v>1320000000</v>
       </c>
-      <c r="D94">
+      <c r="C94">
+        <v>1320000000</v>
+      </c>
+      <c r="E94">
         <v>0</v>
       </c>
     </row>
@@ -1305,18 +1433,21 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
+        <v>145353934</v>
+      </c>
+      <c r="C97">
         <v>1992575</v>
       </c>
-      <c r="C97">
+      <c r="D97">
         <v>1856015</v>
       </c>
-      <c r="D97">
-        <v>-845422</v>
-      </c>
       <c r="E97">
+        <v>3399462</v>
+      </c>
+      <c r="F97">
         <v>-769376</v>
       </c>
-      <c r="F97">
+      <c r="G97">
         <v>12285709</v>
       </c>
     </row>
@@ -1324,11 +1455,8 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
-      <c r="B98">
+      <c r="C98">
         <v>69530755</v>
-      </c>
-      <c r="D98">
-        <v>4244884</v>
       </c>
     </row>
     <row r="99">
@@ -1339,15 +1467,18 @@
         <v>4601256</v>
       </c>
       <c r="C99">
+        <v>4601256</v>
+      </c>
+      <c r="D99">
         <v>4601269</v>
       </c>
-      <c r="D99">
+      <c r="E99">
         <v>728160</v>
       </c>
-      <c r="E99">
+      <c r="F99">
         <v>728173</v>
       </c>
-      <c r="F99">
+      <c r="G99">
         <v>284391</v>
       </c>
     </row>
@@ -1355,13 +1486,13 @@
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="C100">
+      <c r="D100">
         <v>47917264</v>
       </c>
-      <c r="E100">
+      <c r="F100">
         <v>-6746106</v>
       </c>
-      <c r="F100">
+      <c r="G100">
         <v>14709585</v>
       </c>
     </row>
@@ -1386,12 +1517,15 @@
         <v>196451193</v>
       </c>
       <c r="D103">
+        <v>196451193</v>
+      </c>
+      <c r="E103">
         <v>35810792</v>
       </c>
-      <c r="E103">
+      <c r="F103">
         <v>-15230257</v>
       </c>
-      <c r="F103">
+      <c r="G103">
         <v>7017301</v>
       </c>
     </row>
@@ -1400,18 +1534,21 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
+        <v>244951325</v>
+      </c>
+      <c r="C104">
         <v>36930538</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>13896810</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>164513497</v>
       </c>
-      <c r="E104">
+      <c r="F104">
         <v>167186101</v>
       </c>
-      <c r="F104">
+      <c r="G104">
         <v>17092249</v>
       </c>
     </row>
@@ -1420,15 +1557,18 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B105">
+        <v>17135495</v>
+      </c>
+      <c r="C105">
         <v>17548618</v>
       </c>
-      <c r="C105">
+      <c r="D105">
         <v>15154876</v>
       </c>
-      <c r="D105">
+      <c r="E105">
         <v>10462655</v>
       </c>
-      <c r="E105">
+      <c r="F105">
         <v>384345</v>
       </c>
     </row>
@@ -1437,18 +1577,21 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
+        <v>2083493203</v>
+      </c>
+      <c r="C106">
         <v>1802054935</v>
       </c>
-      <c r="C106">
+      <c r="D106">
         <v>404877427</v>
       </c>
-      <c r="D106">
+      <c r="E106">
         <v>339914566</v>
       </c>
-      <c r="E106">
+      <c r="F106">
         <v>172552880</v>
       </c>
-      <c r="F106">
+      <c r="G106">
         <v>78389235</v>
       </c>
     </row>
@@ -1457,18 +1600,21 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
+        <v>3480251067</v>
+      </c>
+      <c r="C107">
         <v>3003420009</v>
       </c>
-      <c r="C107">
+      <c r="D107">
         <v>1674546963</v>
       </c>
-      <c r="D107">
+      <c r="E107">
         <v>1475663640</v>
       </c>
-      <c r="E107">
+      <c r="F107">
         <v>823021597</v>
       </c>
-      <c r="F107">
+      <c r="G107">
         <v>416950765</v>
       </c>
     </row>
@@ -1476,19 +1622,25 @@
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
+      <c r="B108">
+        <v>450095535</v>
+      </c>
+      <c r="C108">
+        <v>182024668</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:I50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -1496,6 +1648,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1503,24 +1656,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1534,24 +1690,27 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>1011968695</v>
+      </c>
+      <c r="C3">
         <v>491822469</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>267022962</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>628321226</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>254023160</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>157852482</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>422892272</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>156342926</v>
       </c>
     </row>
@@ -1564,35 +1723,56 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
+      <c r="B5">
+        <v>146595738</v>
+      </c>
+      <c r="C5">
+        <v>32775707</v>
+      </c>
+      <c r="E5">
+        <v>98646262</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
+      <c r="B6">
+        <v>863879783</v>
+      </c>
+      <c r="C6">
+        <v>456660229</v>
+      </c>
+      <c r="E6">
+        <v>547562429</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-338030467</v>
+      </c>
+      <c r="C7">
         <v>-181276792</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-98429388</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-212705658</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-125650045</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>-81685453</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-130783032</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>-83686976</v>
       </c>
     </row>
@@ -1601,24 +1781,27 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>673938228</v>
+      </c>
+      <c r="C8">
         <v>310545677</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>168593574</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>415615568</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>128373115</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>76167029</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>292109240</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>72655950</v>
       </c>
     </row>
@@ -1647,24 +1830,27 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>673938228</v>
+      </c>
+      <c r="C13">
         <v>310545677</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>168593574</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>415615568</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>128373115</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>76167029</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>292109240</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>72655950</v>
       </c>
     </row>
@@ -1674,24 +1860,27 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-267134773</v>
+      </c>
+      <c r="C15">
         <v>-114836823</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-66737249</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-79849733</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>-39044103</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>-24578203</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>-40552138</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>-19204247</v>
       </c>
     </row>
@@ -1700,24 +1889,27 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-80387044</v>
+      </c>
+      <c r="C16">
         <v>-44854991</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-30805089</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-39201093</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-24097951</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>-13891744</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>-21896767</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-10639251</v>
       </c>
     </row>
@@ -1726,24 +1918,27 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-37603639</v>
+      </c>
+      <c r="C17">
         <v>-25786217</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-15907919</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>-24577856</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>-14056343</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>-8476066</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>-11346004</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>-4515212</v>
       </c>
     </row>
@@ -1752,24 +1947,27 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>23792181</v>
+      </c>
+      <c r="C18">
         <v>40602333</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>17862530</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>30502172</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>22538092</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>17102048</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>19393593</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>14131630</v>
       </c>
     </row>
@@ -1778,24 +1976,27 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-57912286</v>
+      </c>
+      <c r="C19">
         <v>-68780795</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>-5718189</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-64088224</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>-22596758</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>-17415270</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>-41825078</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>-18726791</v>
       </c>
     </row>
@@ -1809,24 +2010,27 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>254692667</v>
+      </c>
+      <c r="C21">
         <v>96889184</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>67287658</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>238400834</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>51116052</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>28907794</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>195882846</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>33702079</v>
       </c>
     </row>
@@ -1846,18 +2050,24 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>45446148</v>
+      </c>
+      <c r="C25">
         <v>19320082</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>3713582</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
-      <c r="G25">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>1431413</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>457089</v>
       </c>
     </row>
@@ -1868,19 +2078,22 @@
       <c r="B26">
         <v>0</v>
       </c>
-      <c r="D26">
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="E26">
         <v>-890441</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>-903639</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>-12202369</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>-8283522</v>
       </c>
     </row>
@@ -1919,24 +2132,27 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>300138815</v>
+      </c>
+      <c r="C33">
         <v>116209266</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>71001240</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>237510393</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>51116052</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>28004155</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>185111890</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>25875646</v>
       </c>
     </row>
@@ -1946,24 +2162,27 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>69602222</v>
+      </c>
+      <c r="C35">
         <v>27338661</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>12856498</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>1485657</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>902976</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>698119</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>593</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>1142</v>
       </c>
     </row>
@@ -1972,24 +2191,27 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-120416830</v>
+      </c>
+      <c r="C36">
         <v>-99531427</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-65268707</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-65556831</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>-34638819</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>-25582724</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>-20196310</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>-8817366</v>
       </c>
     </row>
@@ -2003,24 +2225,27 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>249324207</v>
+      </c>
+      <c r="C38">
         <v>44016500</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>18589031</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>173439219</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>17380209</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>3119550</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>164916173</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>17059422</v>
       </c>
     </row>
@@ -2030,15 +2255,21 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>2299958</v>
+      </c>
+      <c r="C40">
         <v>0</v>
       </c>
       <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
         <v>-426260</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>2160710</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>32827</v>
       </c>
     </row>
@@ -2047,12 +2278,18 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
+        <v>-819038</v>
+      </c>
+      <c r="C41">
         <v>0</v>
       </c>
       <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
         <v>-426260</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>-11863</v>
       </c>
     </row>
@@ -2061,12 +2298,18 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>3118996</v>
+      </c>
+      <c r="C42">
         <v>0</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
-      <c r="H42">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="I42">
         <v>44690</v>
       </c>
     </row>
@@ -2075,24 +2318,27 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>251624165</v>
+      </c>
+      <c r="C43">
         <v>44016500</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>18589031</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>173439219</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>16953949</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>3119550</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>167076883</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>17092249</v>
       </c>
     </row>
@@ -2107,24 +2353,27 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>251624165</v>
+      </c>
+      <c r="C46">
         <v>44016500</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>18589031</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>173439219</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>16953949</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>3119550</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>167076883</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>17092249</v>
       </c>
     </row>
@@ -2133,21 +2382,24 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
+        <v>6672840</v>
+      </c>
+      <c r="C47">
         <v>7085962</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>4692221</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>8925722</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>-673996</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>-593350</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>-109218</v>
       </c>
     </row>
@@ -2156,24 +2408,27 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>244951325</v>
+      </c>
+      <c r="C48">
         <v>36930538</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>13896810</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>164513497</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>17627945</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>3712900</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>167186101</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>17092249</v>
       </c>
     </row>
@@ -2183,39 +2438,42 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>65840618</v>
+      </c>
+      <c r="C50">
         <v>41967651</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>24192705</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>32234100</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>19259951</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>14124351</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>20585442</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>11926139</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:I50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -2223,6 +2481,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2230,24 +2489,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2261,12 +2523,15 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>520146226</v>
+      </c>
+      <c r="C3">
         <v>224799507</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>374298066</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>96170678</v>
       </c>
     </row>
@@ -2279,23 +2544,32 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
+      <c r="B5">
+        <v>113820031</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
+      <c r="B6">
+        <v>407219554</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-156753675</v>
+      </c>
+      <c r="C7">
         <v>-82847404</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-87055613</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-43964592</v>
       </c>
     </row>
@@ -2304,12 +2578,15 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>363392551</v>
+      </c>
+      <c r="C8">
         <v>141952103</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>287242453</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>52206086</v>
       </c>
     </row>
@@ -2338,12 +2615,15 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>363392551</v>
+      </c>
+      <c r="C13">
         <v>141952103</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>287242453</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>52206086</v>
       </c>
     </row>
@@ -2353,12 +2633,15 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-152297950</v>
+      </c>
+      <c r="C15">
         <v>-48099574</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-40805630</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>-14465900</v>
       </c>
     </row>
@@ -2367,12 +2650,15 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-35532053</v>
+      </c>
+      <c r="C16">
         <v>-14049902</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-15103142</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-10206207</v>
       </c>
     </row>
@@ -2381,12 +2667,15 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-11817422</v>
+      </c>
+      <c r="C17">
         <v>-9878298</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>-10521513</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>-5580277</v>
       </c>
     </row>
@@ -2395,12 +2684,15 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>-16810152</v>
+      </c>
+      <c r="C18">
         <v>22739803</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>7964080</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>5436044</v>
       </c>
     </row>
@@ -2409,12 +2701,15 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>10868509</v>
+      </c>
+      <c r="C19">
         <v>-63062606</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-41491466</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>-5181488</v>
       </c>
     </row>
@@ -2428,12 +2723,15 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>157803483</v>
+      </c>
+      <c r="C21">
         <v>29601526</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>187284782</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>22208258</v>
       </c>
     </row>
@@ -2453,17 +2751,26 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>26126066</v>
+      </c>
+      <c r="C25">
         <v>15606500</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="D26">
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="E26">
         <v>-890441</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>903639</v>
       </c>
     </row>
@@ -2502,12 +2809,15 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>183929549</v>
+      </c>
+      <c r="C33">
         <v>45208026</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>186394341</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>23111897</v>
       </c>
     </row>
@@ -2517,12 +2827,15 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>42263561</v>
+      </c>
+      <c r="C35">
         <v>14482163</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>582681</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>204857</v>
       </c>
     </row>
@@ -2531,12 +2844,15 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-20885403</v>
+      </c>
+      <c r="C36">
         <v>-34262720</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-30918012</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>-9056095</v>
       </c>
     </row>
@@ -2550,12 +2866,15 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>205307707</v>
+      </c>
+      <c r="C38">
         <v>25427469</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>156059010</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>14260659</v>
       </c>
     </row>
@@ -2564,28 +2883,49 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B40">
+        <v>2299958</v>
+      </c>
+      <c r="E40">
+        <v>426260</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B41">
+        <v>-819038</v>
+      </c>
+      <c r="E41">
+        <v>426260</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B42">
+        <v>3118996</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>207607665</v>
+      </c>
+      <c r="C43">
         <v>25427469</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>156485270</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>13834399</v>
       </c>
     </row>
@@ -2600,12 +2940,15 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>207607665</v>
+      </c>
+      <c r="C46">
         <v>25427469</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>156485270</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>13834399</v>
       </c>
     </row>
@@ -2614,12 +2957,15 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
+        <v>-413122</v>
+      </c>
+      <c r="C47">
         <v>2393741</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>9599718</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>-80646</v>
       </c>
     </row>
@@ -2628,12 +2974,15 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>208020787</v>
+      </c>
+      <c r="C48">
         <v>23033728</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>146885552</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>13915045</v>
       </c>
     </row>
@@ -2643,27 +2992,30 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>23872967</v>
+      </c>
+      <c r="C50">
         <v>17774946</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>12974149</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>5135600</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:I50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -2671,6 +3023,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2678,24 +3031,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2709,18 +3065,21 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>1011968695</v>
+      </c>
+      <c r="C3">
         <v>866120535</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>737491706</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>628321226</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>422892272</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>156342926</v>
       </c>
     </row>
@@ -2733,29 +3092,44 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
+      <c r="B5">
+        <v>146595738</v>
+      </c>
+      <c r="E5">
+        <v>98646262</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
+      <c r="B6">
+        <v>863879783</v>
+      </c>
+      <c r="E6">
+        <v>547562429</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-338030467</v>
+      </c>
+      <c r="C7">
         <v>-268332405</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-229449593</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-212705658</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-130783032</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>-83686976</v>
       </c>
     </row>
@@ -2764,18 +3138,21 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>673938228</v>
+      </c>
+      <c r="C8">
         <v>597788130</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>508042113</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>415615568</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>292109240</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>72655950</v>
       </c>
     </row>
@@ -2804,18 +3181,21 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>673938228</v>
+      </c>
+      <c r="C13">
         <v>597788130</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>508042113</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>415615568</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>292109240</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>72655950</v>
       </c>
     </row>
@@ -2825,18 +3205,21 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-267134773</v>
+      </c>
+      <c r="C15">
         <v>-155642453</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-122008779</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-79849733</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>-40552138</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>-19204247</v>
       </c>
     </row>
@@ -2845,18 +3228,21 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-80387044</v>
+      </c>
+      <c r="C16">
         <v>-59958133</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-56114438</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-39201093</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>-21896767</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-10639251</v>
       </c>
     </row>
@@ -2865,18 +3251,21 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-37603639</v>
+      </c>
+      <c r="C17">
         <v>-36307730</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-32009709</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>-24577856</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>-11346004</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>-4515212</v>
       </c>
     </row>
@@ -2885,18 +3274,21 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>23792181</v>
+      </c>
+      <c r="C18">
         <v>48566413</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>31262654</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>30502172</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>19393593</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>14131630</v>
       </c>
     </row>
@@ -2905,18 +3297,21 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-57912286</v>
+      </c>
+      <c r="C19">
         <v>-110272261</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>-52391143</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-64088224</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>-41825078</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>-18726791</v>
       </c>
     </row>
@@ -2930,18 +3325,21 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>254692667</v>
+      </c>
+      <c r="C21">
         <v>284173966</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>276780698</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>238400834</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>195882846</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>33702079</v>
       </c>
     </row>
@@ -2960,10 +3358,19 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
-      <c r="G25">
+      <c r="B25">
+        <v>45446148</v>
+      </c>
+      <c r="C25">
+        <v>19320082</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>1431413</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>457089</v>
       </c>
     </row>
@@ -2972,15 +3379,18 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
         <v>-890441</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>-890441</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>-12202369</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>-8283522</v>
       </c>
     </row>
@@ -3019,18 +3429,21 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>300138815</v>
+      </c>
+      <c r="C33">
         <v>302603607</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>280507478</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>237510393</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>185111890</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>25875646</v>
       </c>
     </row>
@@ -3040,18 +3453,21 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>69602222</v>
+      </c>
+      <c r="C35">
         <v>27921342</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>13644036</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>1485657</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>593</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>1142</v>
       </c>
     </row>
@@ -3060,18 +3476,21 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-120416830</v>
+      </c>
+      <c r="C36">
         <v>-130449439</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-105242814</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-65556831</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>-20196310</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>-8817366</v>
       </c>
     </row>
@@ -3085,18 +3504,21 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>249324207</v>
+      </c>
+      <c r="C38">
         <v>200075510</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>188908700</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>173439219</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>164916173</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>17059422</v>
       </c>
     </row>
@@ -3105,10 +3527,19 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
-      <c r="G40">
+      <c r="B40">
+        <v>2299958</v>
+      </c>
+      <c r="C40">
+        <v>426260</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>2160710</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>32827</v>
       </c>
     </row>
@@ -3116,7 +3547,16 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="H41">
+      <c r="B41">
+        <v>-819038</v>
+      </c>
+      <c r="C41">
+        <v>426260</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="I41">
         <v>-11863</v>
       </c>
     </row>
@@ -3124,7 +3564,16 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
-      <c r="H42">
+      <c r="B42">
+        <v>3118996</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="I42">
         <v>44690</v>
       </c>
     </row>
@@ -3133,18 +3582,21 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>251624165</v>
+      </c>
+      <c r="C43">
         <v>200501770</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>188908700</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>173439219</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>167076883</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>17092249</v>
       </c>
     </row>
@@ -3159,18 +3611,21 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>251624165</v>
+      </c>
+      <c r="C46">
         <v>200501770</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>188908700</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>173439219</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>167076883</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>17092249</v>
       </c>
     </row>
@@ -3179,15 +3634,18 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
+        <v>6672840</v>
+      </c>
+      <c r="C47">
         <v>16685680</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>14211293</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>8925722</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>-109218</v>
       </c>
     </row>
@@ -3196,18 +3654,21 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>244951325</v>
+      </c>
+      <c r="C48">
         <v>183816090</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>174697407</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>164513497</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>167186101</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>17092249</v>
       </c>
     </row>
@@ -3217,33 +3678,36 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>65840618</v>
+      </c>
+      <c r="C50">
         <v>54941800</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>42302454</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>32234100</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>20585442</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>11926139</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:I129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -3251,6 +3715,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3258,24 +3723,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3289,24 +3757,27 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>-503185322</v>
+      </c>
+      <c r="C3">
         <v>-1029328262</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>-194359396</v>
       </c>
-      <c r="D3">
-        <v>-7558425</v>
-      </c>
       <c r="E3">
+        <v>-48088078</v>
+      </c>
+      <c r="F3">
         <v>-77778337</v>
       </c>
-      <c r="F3">
-        <v>25195672</v>
-      </c>
       <c r="G3">
+        <v>19883571</v>
+      </c>
+      <c r="H3">
         <v>58558396</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>12848534</v>
       </c>
     </row>
@@ -3315,24 +3786,27 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>244951325</v>
+      </c>
+      <c r="C4">
         <v>36930538</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>13896810</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>164513497</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>17627945</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>3712900</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>167186101</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>17092249</v>
       </c>
     </row>
@@ -3341,9 +3815,15 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-16978346</v>
+      </c>
+      <c r="C5">
         <v>14250618</v>
       </c>
       <c r="E5">
+        <v>98657147</v>
+      </c>
+      <c r="F5">
         <v>2945839</v>
       </c>
     </row>
@@ -3352,24 +3832,27 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>65840618</v>
+      </c>
+      <c r="C6">
         <v>41967651</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>24192705</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>32234100</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>19259951</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>14124351</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>20585442</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>11926139</v>
       </c>
     </row>
@@ -3378,24 +3861,27 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
+        <v>-66325</v>
+      </c>
+      <c r="C7">
         <v>-54581</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-39105</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-62023</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-49498</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>21380</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-391852</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>-136354</v>
       </c>
     </row>
@@ -3404,9 +3890,15 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>5462188</v>
+      </c>
+      <c r="C8">
         <v>1589088</v>
       </c>
       <c r="E8">
+        <v>1388032</v>
+      </c>
+      <c r="F8">
         <v>3839795</v>
       </c>
     </row>
@@ -3430,24 +3922,27 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>50814608</v>
+      </c>
+      <c r="C12">
         <v>72192766</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>52330717</v>
       </c>
-      <c r="D12">
-        <v>64055229</v>
-      </c>
       <c r="E12">
+        <v>64071174</v>
+      </c>
+      <c r="F12">
         <v>33735843</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>24873081</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>20130319</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>8804874</v>
       </c>
     </row>
@@ -3466,24 +3961,27 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>-136729477</v>
+      </c>
+      <c r="C15">
         <v>-91649780</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-8354105</v>
       </c>
-      <c r="D15">
-        <v>145423</v>
-      </c>
       <c r="E15">
+        <v>1025864</v>
+      </c>
+      <c r="F15">
         <v>-53840252</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>-5883645</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>-30900633</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>-13477221</v>
       </c>
     </row>
@@ -3501,10 +3999,10 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>-9794526</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0</v>
       </c>
     </row>
@@ -3517,10 +4015,16 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="G20">
+      <c r="B20">
+        <v>-2299958</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>2160710</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>32827</v>
       </c>
     </row>
@@ -3528,19 +4032,16 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>-1280942</v>
       </c>
-      <c r="D21">
-        <v>1388032</v>
-      </c>
-      <c r="F21">
+      <c r="G21">
         <v>-2898259</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>3673212</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>265968</v>
       </c>
     </row>
@@ -3548,19 +4049,16 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>-3713582</v>
       </c>
-      <c r="D22">
-        <v>890441</v>
-      </c>
-      <c r="F22">
+      <c r="G22">
         <v>903639</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>10770956</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>7826433</v>
       </c>
     </row>
@@ -3594,24 +4092,27 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-730180294</v>
+      </c>
+      <c r="C28">
         <v>-1080509418</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>77032498</v>
       </c>
-      <c r="D28">
-        <v>263164699</v>
-      </c>
       <c r="E28">
+        <v>-311258722</v>
+      </c>
+      <c r="F28">
         <v>-98352121</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>34853447</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>193214255</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>32334915</v>
       </c>
     </row>
@@ -3620,9 +4121,15 @@
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
       <c r="B29">
+        <v>-6273412</v>
+      </c>
+      <c r="C29">
         <v>-523309567</v>
       </c>
       <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <v>0</v>
       </c>
     </row>
@@ -3636,24 +4143,27 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>-216817614</v>
+      </c>
+      <c r="C31">
         <v>-243111935</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-93079514</v>
       </c>
-      <c r="D31">
-        <v>-248565380</v>
-      </c>
       <c r="E31">
+        <v>-289100978</v>
+      </c>
+      <c r="F31">
         <v>-57255009</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>-62440075</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>-17622181</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>-51201567</v>
       </c>
     </row>
@@ -3667,24 +4177,27 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-2308102</v>
+      </c>
+      <c r="C33">
         <v>-2771841</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>376514</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>2607306</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>2215027</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>-910310</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>-959214</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>175606</v>
       </c>
     </row>
@@ -3708,24 +4221,27 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>-101887129</v>
+      </c>
+      <c r="C37">
         <v>756644</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>-5336279</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>-60303812</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>-25867949</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>-524195</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>-104429261</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>10948116</v>
       </c>
     </row>
@@ -3739,24 +4255,27 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-457862766</v>
+      </c>
+      <c r="C39">
         <v>-197316407</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>-10162817</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-114336110</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>-29425921</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>65006444</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>-130501841</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>3839601</v>
       </c>
     </row>
@@ -3765,24 +4284,27 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>80389247</v>
+      </c>
+      <c r="C40">
         <v>-18915305</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>-92746647</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>83509636</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>31307380</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>3066235</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>-2036188</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>8236744</v>
       </c>
     </row>
@@ -3796,18 +4318,24 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>18787316</v>
+      </c>
+      <c r="C42">
         <v>4867683</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>-1000000</v>
       </c>
       <c r="E42">
+        <v>8127802</v>
+      </c>
+      <c r="F42">
         <v>41448231</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>-488617</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>-167998</v>
       </c>
     </row>
@@ -3821,24 +4349,27 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-38768386</v>
+      </c>
+      <c r="C44">
         <v>-39441131</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>6245353</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>44528922</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>6517920</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>53191859</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>-923122</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>3547293</v>
       </c>
     </row>
@@ -3857,24 +4388,27 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>81488454</v>
+      </c>
+      <c r="C47">
         <v>-40273266</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>-89375788</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>12725059</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>-60762778</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>-62269602</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>121587623</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>3953812</v>
       </c>
     </row>
@@ -3883,24 +4417,27 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-86927902</v>
+      </c>
+      <c r="C48">
         <v>-20994293</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>-3864816</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>983453</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>-6529022</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>-4778131</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>-1008266</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>458653</v>
       </c>
     </row>
@@ -3909,9 +4446,15 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>-502207315</v>
+      </c>
+      <c r="C49">
         <v>-1029328262</v>
       </c>
       <c r="E49">
+        <v>-48088078</v>
+      </c>
+      <c r="F49">
         <v>-77778337</v>
       </c>
     </row>
@@ -3939,10 +4482,16 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="G54">
+      <c r="B54">
+        <v>-171855</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>-2160710</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>-32827</v>
       </c>
     </row>
@@ -3986,18 +4535,18 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
+        <v>-806152</v>
+      </c>
+      <c r="C62">
         <v>0</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>17552100</v>
       </c>
-      <c r="D62">
-        <v>8127802</v>
-      </c>
-      <c r="E62">
+      <c r="F62">
         <v>0</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>-5312101</v>
       </c>
     </row>
@@ -4008,619 +4557,662 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-      <c r="G64">
-        <v>-2160710</v>
-      </c>
-      <c r="H64">
-        <v>-32827</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-428503635</v>
+      </c>
+      <c r="C67">
+        <v>-84542318</v>
+      </c>
+      <c r="D67">
+        <v>-43607628</v>
+      </c>
+      <c r="E67">
+        <v>-89669978</v>
+      </c>
+      <c r="F67">
+        <v>-70451695</v>
+      </c>
+      <c r="G67">
+        <v>-45082744</v>
+      </c>
+      <c r="H67">
+        <v>6317149</v>
+      </c>
+      <c r="I67">
+        <v>-27499067</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B68">
-        <v>-84542318</v>
-      </c>
-      <c r="C68">
-        <v>-43607628</v>
-      </c>
-      <c r="D68">
-        <v>-89669978</v>
-      </c>
-      <c r="E68">
-        <v>-70451695</v>
-      </c>
-      <c r="F68">
-        <v>-45082744</v>
-      </c>
-      <c r="G68">
-        <v>6317149</v>
-      </c>
-      <c r="H68">
-        <v>-27499067</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>361234</v>
+      </c>
+      <c r="D77">
+        <v>3713582</v>
+      </c>
+      <c r="E77">
+        <v>3652873</v>
+      </c>
+      <c r="F77">
+        <v>9150837</v>
+      </c>
+      <c r="G77">
+        <v>2793705</v>
+      </c>
+      <c r="H77">
+        <v>26001500</v>
+      </c>
+      <c r="I77">
+        <v>15577842</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>361234</v>
+        <v>-428503635</v>
       </c>
       <c r="C78">
-        <v>3713582</v>
+        <v>-84903552</v>
       </c>
       <c r="D78">
-        <v>3652873</v>
+        <v>-47321210</v>
       </c>
       <c r="E78">
-        <v>9150837</v>
+        <v>-93322851</v>
       </c>
       <c r="F78">
-        <v>2793705</v>
+        <v>-79602532</v>
       </c>
       <c r="G78">
-        <v>26001500</v>
+        <v>-47876449</v>
       </c>
       <c r="H78">
-        <v>15577842</v>
+        <v>-19684351</v>
+      </c>
+      <c r="I78">
+        <v>-43076909</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B79">
-        <v>-84903552</v>
-      </c>
-      <c r="C79">
-        <v>-47321210</v>
-      </c>
-      <c r="D79">
-        <v>-93322851</v>
-      </c>
-      <c r="E79">
-        <v>-79602532</v>
-      </c>
-      <c r="F79">
-        <v>-47876449</v>
-      </c>
-      <c r="G79">
-        <v>-19684351</v>
-      </c>
-      <c r="H79">
-        <v>-43076909</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>1418179757</v>
+      </c>
+      <c r="C101">
+        <v>1443915777</v>
+      </c>
+      <c r="D101">
+        <v>191035455</v>
+      </c>
+      <c r="E101">
+        <v>178191856</v>
+      </c>
+      <c r="F101">
+        <v>133521590</v>
+      </c>
+      <c r="G101">
+        <v>8468858</v>
+      </c>
+      <c r="H101">
+        <v>-20934216</v>
+      </c>
+      <c r="I101">
+        <v>10779707</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>1443915777</v>
-      </c>
-      <c r="C102">
-        <v>191035455</v>
-      </c>
-      <c r="D102">
-        <v>178207801</v>
-      </c>
-      <c r="E102">
-        <v>133521590</v>
-      </c>
-      <c r="F102">
-        <v>8468858</v>
-      </c>
-      <c r="G102">
-        <v>-20934216</v>
-      </c>
-      <c r="H102">
-        <v>10779707</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B104">
+        <v>1320711229</v>
+      </c>
+      <c r="C104">
+        <v>1322837997</v>
+      </c>
+      <c r="E104">
+        <v>-76046</v>
+      </c>
+      <c r="F104">
+        <v>212004</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B105">
-        <v>1322837997</v>
-      </c>
-      <c r="E105">
-        <v>212004</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+      </c>
+      <c r="H106">
+        <v>-18408566</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
-      </c>
-      <c r="G107">
-        <v>-18408566</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B107">
+        <v>30000000</v>
+      </c>
+      <c r="C107">
+        <v>30000000</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>22000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B108">
-        <v>30000000</v>
-      </c>
-      <c r="E108">
-        <v>0</v>
-      </c>
-      <c r="H108">
-        <v>22000000</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B109">
+        <v>118283136</v>
+      </c>
+      <c r="C109">
+        <v>163270546</v>
+      </c>
+      <c r="D109">
+        <v>240746227</v>
+      </c>
+      <c r="E109">
+        <v>260484128</v>
+      </c>
+      <c r="F109">
+        <v>185190481</v>
+      </c>
+      <c r="G109">
+        <v>48649964</v>
+      </c>
+      <c r="H109">
+        <v>51147213</v>
+      </c>
+      <c r="I109">
+        <v>-2580974</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B110">
-        <v>163270546</v>
-      </c>
-      <c r="C110">
-        <v>240746227</v>
-      </c>
-      <c r="D110">
-        <v>260484128</v>
-      </c>
-      <c r="E110">
-        <v>185190481</v>
-      </c>
-      <c r="F110">
-        <v>48649964</v>
-      </c>
-      <c r="G110">
-        <v>51147213</v>
-      </c>
-      <c r="H110">
-        <v>-2580974</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>-18145052</v>
+      </c>
+      <c r="F117">
+        <v>-18145052</v>
+      </c>
+      <c r="G117">
+        <v>-18145052</v>
+      </c>
+      <c r="H117">
+        <v>-21675261</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>-120416830</v>
+      </c>
+      <c r="C118">
+        <v>-99531427</v>
       </c>
       <c r="D118">
-        <v>-18145052</v>
+        <v>-65268707</v>
       </c>
       <c r="E118">
-        <v>-18145052</v>
+        <v>-65556831</v>
       </c>
       <c r="F118">
-        <v>-18145052</v>
+        <v>-34638819</v>
       </c>
       <c r="G118">
-        <v>-21675261</v>
+        <v>-25582724</v>
+      </c>
+      <c r="H118">
+        <v>-20130912</v>
+      </c>
+      <c r="I118">
+        <v>-8806015</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>-99531427</v>
+        <v>69602222</v>
       </c>
       <c r="C119">
-        <v>-65268707</v>
+        <v>27338661</v>
       </c>
       <c r="D119">
-        <v>-65540886</v>
+        <v>12856498</v>
       </c>
       <c r="E119">
-        <v>-34638819</v>
+        <v>1485657</v>
       </c>
       <c r="F119">
-        <v>-25582724</v>
+        <v>902976</v>
       </c>
       <c r="G119">
-        <v>-20130912</v>
+        <v>698119</v>
       </c>
       <c r="H119">
-        <v>-8806015</v>
+        <v>593</v>
+      </c>
+      <c r="I119">
+        <v>1142</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B120">
-        <v>27338661</v>
-      </c>
-      <c r="C120">
-        <v>12856498</v>
-      </c>
-      <c r="D120">
-        <v>1485657</v>
-      </c>
-      <c r="E120">
-        <v>902976</v>
-      </c>
-      <c r="F120">
-        <v>698119</v>
-      </c>
-      <c r="G120">
-        <v>593</v>
-      </c>
-      <c r="H120">
-        <v>1142</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="D123">
+        <v>2701437</v>
+      </c>
+      <c r="G123">
+        <v>2848551</v>
+      </c>
+      <c r="H123">
+        <v>-11867283</v>
+      </c>
+      <c r="I123">
+        <v>165554</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="C124">
-        <v>2701437</v>
-      </c>
-      <c r="D124">
-        <v>-76046</v>
-      </c>
-      <c r="F124">
-        <v>2848551</v>
-      </c>
-      <c r="G124">
-        <v>-11867283</v>
-      </c>
-      <c r="H124">
-        <v>165554</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>486490800</v>
+      </c>
+      <c r="C125">
+        <v>330045197</v>
+      </c>
+      <c r="D125">
+        <v>-46931569</v>
+      </c>
+      <c r="E125">
+        <v>40433800</v>
+      </c>
+      <c r="F125">
+        <v>-14708442</v>
+      </c>
+      <c r="G125">
+        <v>-16730315</v>
+      </c>
+      <c r="H125">
+        <v>43941329</v>
+      </c>
+      <c r="I125">
+        <v>-3870826</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>330045197</v>
+        <v>141243243</v>
       </c>
       <c r="C126">
-        <v>-46931569</v>
+        <v>65285871</v>
       </c>
       <c r="D126">
-        <v>80979398</v>
+        <v>44157919</v>
       </c>
       <c r="E126">
-        <v>-14708442</v>
+        <v>51051049</v>
       </c>
       <c r="F126">
-        <v>-16730315</v>
+        <v>10990976</v>
       </c>
       <c r="G126">
-        <v>43941329</v>
+        <v>14808978</v>
       </c>
       <c r="H126">
-        <v>-3870826</v>
+        <v>-21455677</v>
+      </c>
+      <c r="I126">
+        <v>8491086</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>65285871</v>
+        <v>627734043</v>
       </c>
       <c r="C127">
-        <v>44157919</v>
+        <v>395331068</v>
       </c>
       <c r="D127">
-        <v>10505451</v>
+        <v>-2773650</v>
       </c>
       <c r="E127">
-        <v>10990976</v>
+        <v>91484849</v>
       </c>
       <c r="F127">
-        <v>14808978</v>
+        <v>-3717466</v>
       </c>
       <c r="G127">
-        <v>-21455677</v>
+        <v>-1921337</v>
       </c>
       <c r="H127">
-        <v>8491086</v>
+        <v>22485652</v>
+      </c>
+      <c r="I127">
+        <v>4620260</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>395331068</v>
+        <v>120679477</v>
       </c>
       <c r="C128">
-        <v>-2773650</v>
-      </c>
-      <c r="D128">
-        <v>91484849</v>
+        <v>120679477</v>
       </c>
       <c r="E128">
-        <v>-3717466</v>
+        <v>29194628</v>
       </c>
       <c r="F128">
-        <v>-1921337</v>
-      </c>
-      <c r="G128">
-        <v>22485652</v>
-      </c>
-      <c r="H128">
-        <v>4620260</v>
+        <v>29194628</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>748413520</v>
+      </c>
+      <c r="C129">
+        <v>516010545</v>
+      </c>
+      <c r="E129">
         <v>120679477</v>
       </c>
-      <c r="E129">
-        <v>29194628</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B130">
-        <v>516010545</v>
-      </c>
-      <c r="E130">
+      <c r="F129">
         <v>25477162</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:I129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -4628,6 +5220,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4635,24 +5228,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -4666,13 +5262,16 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>526142940</v>
+      </c>
+      <c r="C3">
         <v>-834968866</v>
       </c>
-      <c r="D3">
-        <v>70219912</v>
-      </c>
       <c r="E3">
-        <v>-102974009</v>
+        <v>29690259</v>
+      </c>
+      <c r="F3">
+        <v>-97661908</v>
       </c>
     </row>
     <row r="4">
@@ -4680,12 +5279,15 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>208020787</v>
+      </c>
+      <c r="C4">
         <v>23033728</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>146885552</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>13915045</v>
       </c>
     </row>
@@ -4693,18 +5295,27 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B5">
+        <v>-31228964</v>
+      </c>
+      <c r="E5">
+        <v>95711308</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>23872967</v>
+      </c>
+      <c r="C6">
         <v>17774946</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>12974149</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>5135600</v>
       </c>
     </row>
@@ -4713,12 +5324,15 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
+        <v>-11744</v>
+      </c>
+      <c r="C7">
         <v>-15476</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-12525</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-70878</v>
       </c>
     </row>
@@ -4726,6 +5340,12 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B8">
+        <v>3873100</v>
+      </c>
+      <c r="E8">
+        <v>-2451763</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -4747,12 +5367,15 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>-21378158</v>
+      </c>
+      <c r="C12">
         <v>19862049</v>
       </c>
-      <c r="D12">
-        <v>30319386</v>
-      </c>
       <c r="E12">
+        <v>30335331</v>
+      </c>
+      <c r="F12">
         <v>8862762</v>
       </c>
     </row>
@@ -4771,12 +5394,15 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>-45079697</v>
+      </c>
+      <c r="C15">
         <v>-83295675</v>
       </c>
-      <c r="D15">
-        <v>53985675</v>
-      </c>
       <c r="E15">
+        <v>54866116</v>
+      </c>
+      <c r="F15">
         <v>-47956607</v>
       </c>
     </row>
@@ -4845,12 +5471,15 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>350329124</v>
+      </c>
+      <c r="C28">
         <v>-1157541916</v>
       </c>
-      <c r="D28">
-        <v>361516820</v>
-      </c>
       <c r="E28">
+        <v>-212906601</v>
+      </c>
+      <c r="F28">
         <v>-133205568</v>
       </c>
     </row>
@@ -4858,6 +5487,12 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
+      <c r="B29">
+        <v>517036155</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -4869,12 +5504,15 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>26294321</v>
+      </c>
+      <c r="C31">
         <v>-150032421</v>
       </c>
-      <c r="D31">
-        <v>-191310371</v>
-      </c>
       <c r="E31">
+        <v>-231845969</v>
+      </c>
+      <c r="F31">
         <v>5185066</v>
       </c>
     </row>
@@ -4888,12 +5526,15 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>463739</v>
+      </c>
+      <c r="C33">
         <v>-3148355</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>392279</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>3125337</v>
       </c>
     </row>
@@ -4917,12 +5558,15 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>-102643773</v>
+      </c>
+      <c r="C37">
         <v>6092923</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>-34435863</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>-25343754</v>
       </c>
     </row>
@@ -4936,12 +5580,15 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-260546359</v>
+      </c>
+      <c r="C39">
         <v>-187153590</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-84910189</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>-94432365</v>
       </c>
     </row>
@@ -4950,12 +5597,15 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>99304552</v>
+      </c>
+      <c r="C40">
         <v>73831342</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>52202256</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>28241145</v>
       </c>
     </row>
@@ -4969,7 +5619,13 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>13919633</v>
+      </c>
+      <c r="C42">
         <v>5867683</v>
+      </c>
+      <c r="E42">
+        <v>-33320429</v>
       </c>
     </row>
     <row r="43">
@@ -4982,12 +5638,15 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>672745</v>
+      </c>
+      <c r="C44">
         <v>-45686484</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>38011002</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>-46673939</v>
       </c>
     </row>
@@ -5006,12 +5665,15 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>121761720</v>
+      </c>
+      <c r="C47">
         <v>49102522</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>73487837</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>1506824</v>
       </c>
     </row>
@@ -5020,12 +5682,15 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-65933609</v>
+      </c>
+      <c r="C48">
         <v>-17129477</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>7512475</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>-1750891</v>
       </c>
     </row>
@@ -5033,6 +5698,12 @@
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>527120947</v>
+      </c>
+      <c r="E49">
+        <v>29690259</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -5099,12 +5770,12 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
+        <v>-806152</v>
+      </c>
+      <c r="C62">
         <v>-17552100</v>
       </c>
-      <c r="D62">
-        <v>8127802</v>
-      </c>
-      <c r="E62">
+      <c r="F62">
         <v>5312101</v>
       </c>
     </row>
@@ -5115,439 +5786,491 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-343961317</v>
+      </c>
+      <c r="C67">
+        <v>-40934690</v>
+      </c>
+      <c r="E67">
+        <v>-19218283</v>
+      </c>
+      <c r="F67">
+        <v>-25368951</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B68">
-        <v>-40934690</v>
-      </c>
-      <c r="D68">
-        <v>-19218283</v>
-      </c>
-      <c r="E68">
-        <v>-25368951</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B77">
+        <v>-361234</v>
+      </c>
+      <c r="C77">
+        <v>-3352348</v>
+      </c>
+      <c r="E77">
+        <v>-5497964</v>
+      </c>
+      <c r="F77">
+        <v>6357132</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-3352348</v>
-      </c>
-      <c r="D78">
-        <v>-5497964</v>
+        <v>-343600083</v>
+      </c>
+      <c r="C78">
+        <v>-37582342</v>
       </c>
       <c r="E78">
-        <v>6357132</v>
+        <v>-13720319</v>
+      </c>
+      <c r="F78">
+        <v>-31726083</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B79">
-        <v>-37582342</v>
-      </c>
-      <c r="D79">
-        <v>-13720319</v>
-      </c>
-      <c r="E79">
-        <v>-31726083</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>-25736020</v>
+      </c>
+      <c r="C101">
+        <v>1252880322</v>
+      </c>
+      <c r="E101">
+        <v>44670266</v>
+      </c>
+      <c r="F101">
+        <v>125052732</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>1252880322</v>
-      </c>
-      <c r="D102">
-        <v>44686211</v>
-      </c>
-      <c r="E102">
-        <v>125052732</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B104">
+        <v>-2126768</v>
+      </c>
+      <c r="E104">
+        <v>-288050</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B109">
+        <v>-44987410</v>
+      </c>
+      <c r="C109">
+        <v>-77475681</v>
+      </c>
+      <c r="E109">
+        <v>75293647</v>
+      </c>
+      <c r="F109">
+        <v>136540517</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B110">
-        <v>-77475681</v>
-      </c>
-      <c r="D110">
-        <v>75293647</v>
-      </c>
-      <c r="E110">
-        <v>136540517</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
-      </c>
-      <c r="D118">
-        <v>0</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+      <c r="B118">
+        <v>-20885403</v>
+      </c>
+      <c r="C118">
+        <v>-34262720</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>-30918012</v>
+      </c>
+      <c r="F118">
+        <v>-9056095</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>-34262720</v>
-      </c>
-      <c r="D119">
-        <v>-30902067</v>
+        <v>42263561</v>
+      </c>
+      <c r="C119">
+        <v>14482163</v>
       </c>
       <c r="E119">
-        <v>-9056095</v>
+        <v>582681</v>
+      </c>
+      <c r="F119">
+        <v>204857</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B120">
-        <v>14482163</v>
-      </c>
-      <c r="D120">
-        <v>582681</v>
-      </c>
-      <c r="E120">
-        <v>204857</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>156445603</v>
+      </c>
+      <c r="C125">
+        <v>376976766</v>
+      </c>
+      <c r="E125">
+        <v>55142242</v>
+      </c>
+      <c r="F125">
+        <v>2021873</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>376976766</v>
-      </c>
-      <c r="D126">
-        <v>95687840</v>
+        <v>75957372</v>
+      </c>
+      <c r="C126">
+        <v>21127952</v>
       </c>
       <c r="E126">
-        <v>2021873</v>
+        <v>40060073</v>
+      </c>
+      <c r="F126">
+        <v>-3818002</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>21127952</v>
-      </c>
-      <c r="D127">
-        <v>-485525</v>
+        <v>232402975</v>
+      </c>
+      <c r="C127">
+        <v>398104718</v>
       </c>
       <c r="E127">
-        <v>-3818002</v>
+        <v>95202315</v>
+      </c>
+      <c r="F127">
+        <v>-1796129</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>398104718</v>
-      </c>
-      <c r="D128">
-        <v>95202315</v>
+        <v>0</v>
       </c>
       <c r="E128">
-        <v>-1796129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>232402975</v>
+      </c>
+      <c r="E129">
+        <v>95202315</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:I129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -5555,6 +6278,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5562,24 +6286,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5593,18 +6320,21 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-959108350</v>
+        <v>-503185322</v>
       </c>
       <c r="C3">
-        <v>-227113493</v>
+        <v>-999638003</v>
       </c>
       <c r="D3">
-        <v>-7558425</v>
-      </c>
-      <c r="G3">
+        <v>-262331045</v>
+      </c>
+      <c r="E3">
+        <v>-48088078</v>
+      </c>
+      <c r="H3">
         <v>58558396</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>12848534</v>
       </c>
     </row>
@@ -5613,18 +6343,21 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>244951325</v>
+      </c>
+      <c r="C4">
         <v>183816090</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>174697407</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>164513497</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>167186101</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>17092249</v>
       </c>
     </row>
@@ -5632,24 +6365,36 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B5">
+        <v>-16978346</v>
+      </c>
+      <c r="C5">
+        <v>109961926</v>
+      </c>
+      <c r="E5">
+        <v>98657147</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>65840618</v>
+      </c>
+      <c r="C6">
         <v>54941800</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>42302454</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>32234100</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>20585442</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>11926139</v>
       </c>
     </row>
@@ -5658,18 +6403,21 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
+        <v>-66325</v>
+      </c>
+      <c r="C7">
         <v>-67106</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-122508</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-62023</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-391852</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>-136354</v>
       </c>
     </row>
@@ -5677,6 +6425,15 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B8">
+        <v>5462188</v>
+      </c>
+      <c r="C8">
+        <v>-862675</v>
+      </c>
+      <c r="E8">
+        <v>1388032</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -5698,18 +6455,21 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>102512152</v>
+        <v>50814608</v>
       </c>
       <c r="C12">
-        <v>91512865</v>
+        <v>102528097</v>
       </c>
       <c r="D12">
-        <v>64055229</v>
-      </c>
-      <c r="G12">
+        <v>91528810</v>
+      </c>
+      <c r="E12">
+        <v>64071174</v>
+      </c>
+      <c r="H12">
         <v>20130319</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>8804874</v>
       </c>
     </row>
@@ -5728,18 +6488,21 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
-        <v>-37664105</v>
+        <v>-136729477</v>
       </c>
       <c r="C15">
-        <v>-2325037</v>
+        <v>-36783664</v>
       </c>
       <c r="D15">
-        <v>145423</v>
-      </c>
-      <c r="G15">
+        <v>-1444596</v>
+      </c>
+      <c r="E15">
+        <v>1025864</v>
+      </c>
+      <c r="H15">
         <v>-30900633</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>-13477221</v>
       </c>
     </row>
@@ -5767,10 +6530,16 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="G20">
+      <c r="B20">
+        <v>-2299958</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>2160710</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>32827</v>
       </c>
     </row>
@@ -5778,16 +6547,10 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="C21">
-        <v>3005349</v>
-      </c>
-      <c r="D21">
-        <v>1388032</v>
-      </c>
-      <c r="G21">
+      <c r="H21">
         <v>3673212</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>265968</v>
       </c>
     </row>
@@ -5795,16 +6558,10 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C22">
-        <v>-3726780</v>
-      </c>
-      <c r="D22">
-        <v>890441</v>
-      </c>
-      <c r="G22">
+      <c r="H22">
         <v>10770956</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>7826433</v>
       </c>
     </row>
@@ -5838,18 +6595,21 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-718992598</v>
+        <v>-730180294</v>
       </c>
       <c r="C28">
-        <v>305343750</v>
+        <v>-1293416019</v>
       </c>
       <c r="D28">
-        <v>263164699</v>
-      </c>
-      <c r="G28">
+        <v>-269079671</v>
+      </c>
+      <c r="E28">
+        <v>-311258722</v>
+      </c>
+      <c r="H28">
         <v>193214255</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>32334915</v>
       </c>
     </row>
@@ -5857,6 +6617,15 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
+      <c r="B29">
+        <v>-6273412</v>
+      </c>
+      <c r="C29">
+        <v>-523309567</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -5868,18 +6637,21 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-434422306</v>
+        <v>-216817614</v>
       </c>
       <c r="C31">
-        <v>-279204819</v>
+        <v>-474957904</v>
       </c>
       <c r="D31">
-        <v>-248565380</v>
-      </c>
-      <c r="G31">
+        <v>-319740417</v>
+      </c>
+      <c r="E31">
+        <v>-289100978</v>
+      </c>
+      <c r="H31">
         <v>-17622181</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>-51201567</v>
       </c>
     </row>
@@ -5893,18 +6665,21 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-2308102</v>
+      </c>
+      <c r="C33">
         <v>-2379562</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>3894130</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>2607306</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>-959214</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>175606</v>
       </c>
     </row>
@@ -5928,18 +6703,21 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>-101887129</v>
+      </c>
+      <c r="C37">
         <v>-33679219</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>-65115896</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>-60303812</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>-104429261</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>10948116</v>
       </c>
     </row>
@@ -5953,18 +6731,21 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-457862766</v>
+      </c>
+      <c r="C39">
         <v>-282226596</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>-189505371</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-114336110</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>-130501841</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>3839601</v>
       </c>
     </row>
@@ -5973,18 +6754,21 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>80389247</v>
+      </c>
+      <c r="C40">
         <v>33286951</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>-12303246</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>83509636</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>-2036188</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>8236744</v>
       </c>
     </row>
@@ -5997,10 +6781,19 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
-      <c r="G42">
+      <c r="B42">
+        <v>18787316</v>
+      </c>
+      <c r="C42">
+        <v>-28452746</v>
+      </c>
+      <c r="E42">
+        <v>8127802</v>
+      </c>
+      <c r="H42">
         <v>-488617</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>-167998</v>
       </c>
     </row>
@@ -6014,18 +6807,21 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-38768386</v>
+      </c>
+      <c r="C44">
         <v>-1430129</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-2417584</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>44528922</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>-923122</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>3547293</v>
       </c>
     </row>
@@ -6044,18 +6840,21 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>81488454</v>
+      </c>
+      <c r="C47">
         <v>33214571</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>-14381127</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>12725059</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>121587623</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>3953812</v>
       </c>
     </row>
@@ -6064,18 +6863,21 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-86927902</v>
+      </c>
+      <c r="C48">
         <v>-13481818</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>1896768</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>983453</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>-1008266</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>458653</v>
       </c>
     </row>
@@ -6083,6 +6885,15 @@
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>-502207315</v>
+      </c>
+      <c r="C49">
+        <v>-999638003</v>
+      </c>
+      <c r="E49">
+        <v>-48088078</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -6108,10 +6919,16 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="G54">
+      <c r="B54">
+        <v>-171855</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>-2160710</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>-32827</v>
       </c>
     </row>
@@ -6155,13 +6972,7 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>8127802</v>
-      </c>
-      <c r="C62">
-        <v>30992003</v>
-      </c>
-      <c r="D62">
-        <v>8127802</v>
+        <v>-806152</v>
       </c>
     </row>
     <row r="63">
@@ -6171,517 +6982,569 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-      <c r="G64">
-        <v>-2160710</v>
-      </c>
-      <c r="H64">
-        <v>-32827</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-428503635</v>
+      </c>
+      <c r="C67">
+        <v>-103760601</v>
+      </c>
+      <c r="D67">
+        <v>-88194862</v>
+      </c>
+      <c r="E67">
+        <v>-89669978</v>
+      </c>
+      <c r="H67">
+        <v>6317149</v>
+      </c>
+      <c r="I67">
+        <v>-27499067</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B68">
-        <v>-103760601</v>
-      </c>
-      <c r="C68">
-        <v>-88194862</v>
-      </c>
-      <c r="D68">
-        <v>-89669978</v>
-      </c>
-      <c r="G68">
-        <v>6317149</v>
-      </c>
-      <c r="H68">
-        <v>-27499067</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>-5136730</v>
+      </c>
+      <c r="D77">
+        <v>4572750</v>
+      </c>
+      <c r="E77">
+        <v>3652873</v>
+      </c>
+      <c r="H77">
+        <v>26001500</v>
+      </c>
+      <c r="I77">
+        <v>15577842</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-5136730</v>
+        <v>-428503635</v>
       </c>
       <c r="C78">
-        <v>4572750</v>
+        <v>-98623871</v>
       </c>
       <c r="D78">
-        <v>3652873</v>
-      </c>
-      <c r="G78">
-        <v>26001500</v>
+        <v>-92767612</v>
+      </c>
+      <c r="E78">
+        <v>-93322851</v>
       </c>
       <c r="H78">
-        <v>15577842</v>
+        <v>-19684351</v>
+      </c>
+      <c r="I78">
+        <v>-43076909</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B79">
-        <v>-98623871</v>
-      </c>
-      <c r="C79">
-        <v>-92767612</v>
-      </c>
-      <c r="D79">
-        <v>-93322851</v>
-      </c>
-      <c r="G79">
-        <v>-19684351</v>
-      </c>
-      <c r="H79">
-        <v>-43076909</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>1418179757</v>
+      </c>
+      <c r="C101">
+        <v>1488586043</v>
+      </c>
+      <c r="D101">
+        <v>360758453</v>
+      </c>
+      <c r="E101">
+        <v>178191856</v>
+      </c>
+      <c r="H101">
+        <v>-20934216</v>
+      </c>
+      <c r="I101">
+        <v>10779707</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>1488601988</v>
-      </c>
-      <c r="C102">
-        <v>360774398</v>
-      </c>
-      <c r="D102">
-        <v>178207801</v>
-      </c>
-      <c r="G102">
-        <v>-20934216</v>
-      </c>
-      <c r="H102">
-        <v>10779707</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B104">
+        <v>1320711229</v>
+      </c>
+      <c r="C104">
+        <v>1322549947</v>
+      </c>
+      <c r="E104">
+        <v>-76046</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+      </c>
+      <c r="H106">
+        <v>-18408566</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
-      </c>
-      <c r="G107">
-        <v>-18408566</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B107">
+        <v>30000000</v>
+      </c>
+      <c r="C107">
+        <v>30000000</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>22000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="H108">
-        <v>22000000</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B109">
+        <v>118283136</v>
+      </c>
+      <c r="C109">
+        <v>238564193</v>
+      </c>
+      <c r="D109">
+        <v>452580391</v>
+      </c>
+      <c r="E109">
+        <v>260484128</v>
+      </c>
+      <c r="H109">
+        <v>51147213</v>
+      </c>
+      <c r="I109">
+        <v>-2580974</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B110">
-        <v>238564193</v>
-      </c>
-      <c r="C110">
-        <v>452580391</v>
-      </c>
-      <c r="D110">
-        <v>260484128</v>
-      </c>
-      <c r="G110">
-        <v>51147213</v>
-      </c>
-      <c r="H110">
-        <v>-2580974</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>-18145052</v>
+      </c>
+      <c r="H117">
+        <v>-21675261</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>-120416830</v>
+      </c>
+      <c r="C118">
+        <v>-130449439</v>
       </c>
       <c r="D118">
-        <v>-18145052</v>
-      </c>
-      <c r="G118">
-        <v>-21675261</v>
+        <v>-105242814</v>
+      </c>
+      <c r="E118">
+        <v>-65556831</v>
+      </c>
+      <c r="H118">
+        <v>-20130912</v>
+      </c>
+      <c r="I118">
+        <v>-8806015</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>-130433494</v>
+        <v>69602222</v>
       </c>
       <c r="C119">
-        <v>-105226869</v>
+        <v>27921342</v>
       </c>
       <c r="D119">
-        <v>-65540886</v>
-      </c>
-      <c r="G119">
-        <v>-20130912</v>
+        <v>13644036</v>
+      </c>
+      <c r="E119">
+        <v>1485657</v>
       </c>
       <c r="H119">
-        <v>-8806015</v>
+        <v>593</v>
+      </c>
+      <c r="I119">
+        <v>1142</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B120">
-        <v>27921342</v>
-      </c>
-      <c r="C120">
-        <v>13644036</v>
-      </c>
-      <c r="D120">
-        <v>1485657</v>
-      </c>
-      <c r="G120">
-        <v>593</v>
-      </c>
-      <c r="H120">
-        <v>1142</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="H123">
+        <v>-11867283</v>
+      </c>
+      <c r="I123">
+        <v>165554</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="C124">
-        <v>-223160</v>
-      </c>
-      <c r="D124">
-        <v>-76046</v>
-      </c>
-      <c r="G124">
-        <v>-11867283</v>
-      </c>
-      <c r="H124">
-        <v>165554</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>486490800</v>
+      </c>
+      <c r="C125">
+        <v>385187439</v>
+      </c>
+      <c r="D125">
+        <v>10232546</v>
+      </c>
+      <c r="E125">
+        <v>40433800</v>
+      </c>
+      <c r="H125">
+        <v>43941329</v>
+      </c>
+      <c r="I125">
+        <v>-3870826</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>425733037</v>
+        <v>141243243</v>
       </c>
       <c r="C126">
-        <v>50778144</v>
+        <v>105345944</v>
       </c>
       <c r="D126">
-        <v>80979398</v>
-      </c>
-      <c r="G126">
-        <v>43941329</v>
+        <v>80399990</v>
+      </c>
+      <c r="E126">
+        <v>51051049</v>
       </c>
       <c r="H126">
-        <v>-3870826</v>
+        <v>-21455677</v>
+      </c>
+      <c r="I126">
+        <v>8491086</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>64800346</v>
+        <v>627734043</v>
       </c>
       <c r="C127">
-        <v>39854392</v>
+        <v>490533383</v>
       </c>
       <c r="D127">
-        <v>10505451</v>
-      </c>
-      <c r="G127">
-        <v>-21455677</v>
+        <v>90632536</v>
+      </c>
+      <c r="E127">
+        <v>91484849</v>
       </c>
       <c r="H127">
-        <v>8491086</v>
+        <v>22485652</v>
+      </c>
+      <c r="I127">
+        <v>4620260</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>490533383</v>
+        <v>120679477</v>
       </c>
       <c r="C128">
-        <v>90632536</v>
-      </c>
-      <c r="D128">
-        <v>91484849</v>
-      </c>
-      <c r="G128">
-        <v>22485652</v>
-      </c>
-      <c r="H128">
-        <v>4620260</v>
+        <v>120679477</v>
+      </c>
+      <c r="E128">
+        <v>29194628</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>748413520</v>
+      </c>
+      <c r="C129">
+        <v>611212860</v>
+      </c>
+      <c r="E129">
+        <v>120679477</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/DOFRB (TRY).xlsx
+++ b/data/DOFRB (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -447,21 +451,24 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
+        <v>397904175</v>
+      </c>
+      <c r="C3">
         <v>748413520</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>516010545</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>117905827</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>120679477</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>29194628</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>6708976</v>
       </c>
     </row>
@@ -475,18 +482,21 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
+        <v>202701050</v>
+      </c>
+      <c r="C5">
         <v>7286168</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>534116849</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>2337435</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>1012756</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>444517</v>
       </c>
     </row>
@@ -500,21 +510,24 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
+        <v>647609240</v>
+      </c>
+      <c r="C7">
         <v>564667465</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>590961781</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>440929382</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>347849858</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>99283950</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>81662318</v>
       </c>
     </row>
@@ -533,21 +546,24 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
+        <v>13801726</v>
+      </c>
+      <c r="C10">
         <v>3856413</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>4320152</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>1171797</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>1548311</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>3670090</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>2710876</v>
       </c>
     </row>
@@ -571,21 +587,24 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
+        <v>155807092</v>
+      </c>
+      <c r="C14">
         <v>285137876</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>182494193</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>188587026</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>183250747</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>122946935</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>18517674</v>
       </c>
     </row>
@@ -604,21 +623,24 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
+        <v>773990952</v>
+      </c>
+      <c r="C17">
         <v>717180804</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>453480800</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>267628894</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>259174235</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>144886018</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>9489964</v>
       </c>
     </row>
@@ -635,15 +657,18 @@
         <v>0</v>
       </c>
       <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
         <v>3153645</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>1851961</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>143803</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>95910</v>
       </c>
     </row>
@@ -657,21 +682,24 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
+        <v>97392169</v>
+      </c>
+      <c r="C21">
         <v>88162783</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>22229174</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>3775018</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>1234881</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>2786326</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>2222577</v>
       </c>
     </row>
@@ -679,7 +707,7 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>1930468853</v>
       </c>
     </row>
@@ -693,21 +721,24 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
+        <v>2289206404</v>
+      </c>
+      <c r="C24">
         <v>2414705029</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>2306767139</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>1024187340</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>914894068</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>403308374</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>121312385</v>
       </c>
     </row>
@@ -786,21 +817,24 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
+        <v>405012657</v>
+      </c>
+      <c r="C39">
         <v>363064136</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>501657494</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>44724257</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>40510216</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>20556018</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>33376254</v>
       </c>
     </row>
@@ -809,21 +843,24 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
+        <v>533547801</v>
+      </c>
+      <c r="C40">
         <v>516748234</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>55459767</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>482842891</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>433953864</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>365483555</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>234667870</v>
       </c>
     </row>
@@ -832,21 +869,24 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
+        <v>206057037</v>
+      </c>
+      <c r="C41">
         <v>182614672</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>139535609</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>122792475</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>86305492</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>33673650</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>22604133</v>
       </c>
     </row>
@@ -854,7 +894,13 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
-      <c r="G42">
+      <c r="B42">
+        <v>978668</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>4990123</v>
       </c>
     </row>
@@ -863,9 +909,12 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
         <v>3118996</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>0</v>
       </c>
     </row>
@@ -889,21 +938,24 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
+        <v>1145596163</v>
+      </c>
+      <c r="C47">
         <v>1065546038</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>696652870</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>650359623</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>560769572</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>419713223</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>295638380</v>
       </c>
     </row>
@@ -912,21 +964,24 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
+        <v>3434802567</v>
+      </c>
+      <c r="C48">
         <v>3480251067</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>3003420009</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>1674546963</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>1475663640</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>823021597</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>416950765</v>
       </c>
     </row>
@@ -940,21 +995,24 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
+        <v>333762110</v>
+      </c>
+      <c r="C50">
         <v>332799475</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>354428682</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>522152940</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>234812834</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>31166046</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>15556712</v>
       </c>
     </row>
@@ -963,12 +1021,15 @@
         <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
       </c>
       <c r="B51">
+        <v>13143954</v>
+      </c>
+      <c r="C51">
         <v>15185287</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>14939875</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>13124871</v>
       </c>
     </row>
@@ -977,21 +1038,24 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
+        <v>221383345</v>
+      </c>
+      <c r="C52">
         <v>208115059</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>108810507</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>37680604</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>127725812</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>35376662</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>37412850</v>
       </c>
     </row>
@@ -1005,21 +1069,24 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
+        <v>52662965</v>
+      </c>
+      <c r="C54">
         <v>32659778</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>19784673</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>31424561</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>13872462</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>5744659</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>1858741</v>
       </c>
     </row>
@@ -1028,21 +1095,24 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
         <v>735918</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>63173</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>45749657</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>39504304</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>3814896</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>4738018</v>
       </c>
     </row>
@@ -1071,21 +1141,24 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
+        <v>80179934</v>
+      </c>
+      <c r="C60">
         <v>242647453</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>120885733</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>71783211</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>161158999</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>148433940</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>26846317</v>
       </c>
     </row>
@@ -1094,9 +1167,12 @@
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
       <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
         <v>647184</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>0</v>
       </c>
     </row>
@@ -1105,21 +1181,24 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
+        <v>8056471</v>
+      </c>
+      <c r="C62">
         <v>5634424</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>2340361</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>2139804</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>2416736</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>1064897</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>253227</v>
       </c>
     </row>
@@ -1143,21 +1222,24 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
+        <v>709188779</v>
+      </c>
+      <c r="C66">
         <v>838424578</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>621253004</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>710930777</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>592616018</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>225601100</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>86665865</v>
       </c>
     </row>
@@ -1171,21 +1253,24 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
+        <v>69333301</v>
+      </c>
+      <c r="C68">
         <v>79754743</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>116176994</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>556518003</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>84820756</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>422091801</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>251732182</v>
       </c>
     </row>
@@ -1194,12 +1279,15 @@
         <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
       </c>
       <c r="B69">
+        <v>487750738</v>
+      </c>
+      <c r="C69">
         <v>473442200</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>460587636</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>396167992</v>
       </c>
     </row>
@@ -1212,13 +1300,10 @@
       <c r="A71" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
       </c>
-      <c r="B71">
+      <c r="D71">
         <v>0</v>
       </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="E71">
+      <c r="F71">
         <v>58570096</v>
       </c>
     </row>
@@ -1267,21 +1352,24 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
+        <v>8971076</v>
+      </c>
+      <c r="C80">
         <v>5136343</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>3347440</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>2220756</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>3574212</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>2775816</v>
       </c>
-      <c r="G80">
+      <c r="H80">
         <v>163483</v>
       </c>
     </row>
@@ -1294,6 +1382,12 @@
       <c r="A82" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
+      <c r="B82">
+        <v>1218273</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -1305,21 +1399,24 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
+        <v>567273388</v>
+      </c>
+      <c r="C84">
         <v>558333286</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>580112070</v>
       </c>
-      <c r="D84">
+      <c r="E84">
         <v>558738759</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>543133056</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>424867617</v>
       </c>
-      <c r="G84">
+      <c r="H84">
         <v>251895665</v>
       </c>
     </row>
@@ -1333,21 +1430,24 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
+        <v>2142280161</v>
+      </c>
+      <c r="C86">
         <v>2066357708</v>
       </c>
-      <c r="C86">
+      <c r="D86">
         <v>1784506317</v>
       </c>
-      <c r="D86">
+      <c r="E86">
         <v>389722551</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>329451911</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>172168535</v>
       </c>
-      <c r="G86">
+      <c r="H86">
         <v>78389235</v>
       </c>
     </row>
@@ -1362,15 +1462,18 @@
         <v>155000000</v>
       </c>
       <c r="D87">
-        <v>125000000</v>
+        <v>155000000</v>
       </c>
       <c r="E87">
         <v>125000000</v>
       </c>
       <c r="F87">
+        <v>125000000</v>
+      </c>
+      <c r="G87">
         <v>27000000</v>
       </c>
-      <c r="G87">
+      <c r="H87">
         <v>27000000</v>
       </c>
     </row>
@@ -1414,7 +1517,10 @@
       <c r="C94">
         <v>1320000000</v>
       </c>
-      <c r="E94">
+      <c r="D94">
+        <v>1320000000</v>
+      </c>
+      <c r="F94">
         <v>0</v>
       </c>
     </row>
@@ -1433,21 +1539,24 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>145353934</v>
+        <v>120802</v>
       </c>
       <c r="C97">
+        <v>-134193</v>
+      </c>
+      <c r="D97">
         <v>1992575</v>
       </c>
-      <c r="D97">
+      <c r="E97">
         <v>1856015</v>
       </c>
-      <c r="E97">
+      <c r="F97">
         <v>3399462</v>
       </c>
-      <c r="F97">
+      <c r="G97">
         <v>-769376</v>
       </c>
-      <c r="G97">
+      <c r="H97">
         <v>12285709</v>
       </c>
     </row>
@@ -1455,7 +1564,13 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
+      <c r="B98">
+        <v>214254585</v>
+      </c>
       <c r="C98">
+        <v>145488127</v>
+      </c>
+      <c r="D98">
         <v>69530755</v>
       </c>
     </row>
@@ -1464,21 +1579,24 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>4601256</v>
+        <v>12010117</v>
       </c>
       <c r="C99">
         <v>4601256</v>
       </c>
       <c r="D99">
+        <v>4601256</v>
+      </c>
+      <c r="E99">
         <v>4601269</v>
       </c>
-      <c r="E99">
+      <c r="F99">
         <v>728160</v>
       </c>
-      <c r="F99">
+      <c r="G99">
         <v>728173</v>
       </c>
-      <c r="G99">
+      <c r="H99">
         <v>284391</v>
       </c>
     </row>
@@ -1486,13 +1604,13 @@
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="D100">
+      <c r="E100">
         <v>47917264</v>
       </c>
-      <c r="F100">
+      <c r="G100">
         <v>-6746106</v>
       </c>
-      <c r="G100">
+      <c r="H100">
         <v>14709585</v>
       </c>
     </row>
@@ -1511,7 +1629,7 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>196451193</v>
+        <v>433993657</v>
       </c>
       <c r="C103">
         <v>196451193</v>
@@ -1520,12 +1638,15 @@
         <v>196451193</v>
       </c>
       <c r="E103">
+        <v>196451193</v>
+      </c>
+      <c r="F103">
         <v>35810792</v>
       </c>
-      <c r="F103">
+      <c r="G103">
         <v>-15230257</v>
       </c>
-      <c r="G103">
+      <c r="H103">
         <v>7017301</v>
       </c>
     </row>
@@ -1534,21 +1655,24 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
+        <v>6901000</v>
+      </c>
+      <c r="C104">
         <v>244951325</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>36930538</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>13896810</v>
       </c>
-      <c r="E104">
+      <c r="F104">
         <v>164513497</v>
       </c>
-      <c r="F104">
+      <c r="G104">
         <v>167186101</v>
       </c>
-      <c r="G104">
+      <c r="H104">
         <v>17092249</v>
       </c>
     </row>
@@ -1557,18 +1681,21 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B105">
+        <v>16060239</v>
+      </c>
+      <c r="C105">
         <v>17135495</v>
       </c>
-      <c r="C105">
+      <c r="D105">
         <v>17548618</v>
       </c>
-      <c r="D105">
+      <c r="E105">
         <v>15154876</v>
       </c>
-      <c r="E105">
+      <c r="F105">
         <v>10462655</v>
       </c>
-      <c r="F105">
+      <c r="G105">
         <v>384345</v>
       </c>
     </row>
@@ -1577,21 +1704,24 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
+        <v>2158340400</v>
+      </c>
+      <c r="C106">
         <v>2083493203</v>
       </c>
-      <c r="C106">
+      <c r="D106">
         <v>1802054935</v>
       </c>
-      <c r="D106">
+      <c r="E106">
         <v>404877427</v>
       </c>
-      <c r="E106">
+      <c r="F106">
         <v>339914566</v>
       </c>
-      <c r="F106">
+      <c r="G106">
         <v>172552880</v>
       </c>
-      <c r="G106">
+      <c r="H106">
         <v>78389235</v>
       </c>
     </row>
@@ -1600,21 +1730,24 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
+        <v>3434802567</v>
+      </c>
+      <c r="C107">
         <v>3480251067</v>
       </c>
-      <c r="C107">
+      <c r="D107">
         <v>3003420009</v>
       </c>
-      <c r="D107">
+      <c r="E107">
         <v>1674546963</v>
       </c>
-      <c r="E107">
+      <c r="F107">
         <v>1475663640</v>
       </c>
-      <c r="F107">
+      <c r="G107">
         <v>823021597</v>
       </c>
-      <c r="G107">
+      <c r="H107">
         <v>416950765</v>
       </c>
     </row>
@@ -1622,23 +1755,23 @@
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
-      <c r="B108">
+      <c r="C108">
         <v>450095535</v>
       </c>
-      <c r="C108">
+      <c r="D108">
         <v>182024668</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1649,6 +1782,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1656,27 +1791,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1690,27 +1831,33 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>197927592</v>
+      </c>
+      <c r="C3">
         <v>1011968695</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>491822469</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>267022962</v>
       </c>
-      <c r="E3">
+      <c r="F3">
+        <v>113767057</v>
+      </c>
+      <c r="G3">
         <v>628321226</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>254023160</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>157852482</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>422892272</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>156342926</v>
       </c>
     </row>
@@ -1723,13 +1870,13 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>146595738</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>32775707</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>98646262</v>
       </c>
     </row>
@@ -1737,13 +1884,13 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>863879783</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>456660229</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>547562429</v>
       </c>
     </row>
@@ -1752,27 +1899,33 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-63563455</v>
+      </c>
+      <c r="C7">
         <v>-338030467</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-181276792</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-98429388</v>
       </c>
-      <c r="E7">
+      <c r="F7">
+        <v>-39868049</v>
+      </c>
+      <c r="G7">
         <v>-212705658</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>-125650045</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>-81685453</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>-130783032</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>-83686976</v>
       </c>
     </row>
@@ -1781,27 +1934,33 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>134364137</v>
+      </c>
+      <c r="C8">
         <v>673938228</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>310545677</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>168593574</v>
       </c>
-      <c r="E8">
+      <c r="F8">
+        <v>73899008</v>
+      </c>
+      <c r="G8">
         <v>415615568</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>128373115</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>76167029</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>292109240</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>72655950</v>
       </c>
     </row>
@@ -1830,27 +1989,33 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>134364137</v>
+      </c>
+      <c r="C13">
         <v>673938228</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>310545677</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>168593574</v>
       </c>
-      <c r="E13">
+      <c r="F13">
+        <v>73899008</v>
+      </c>
+      <c r="G13">
         <v>415615568</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>128373115</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>76167029</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>292109240</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>72655950</v>
       </c>
     </row>
@@ -1860,27 +2025,33 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-79966378</v>
+      </c>
+      <c r="C15">
         <v>-267134773</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-114836823</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-66737249</v>
       </c>
-      <c r="E15">
+      <c r="F15">
+        <v>-13483238</v>
+      </c>
+      <c r="G15">
         <v>-79849733</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-39044103</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>-24578203</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-40552138</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-19204247</v>
       </c>
     </row>
@@ -1889,27 +2060,33 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-47263904</v>
+      </c>
+      <c r="C16">
         <v>-80387044</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-44854991</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-30805089</v>
       </c>
-      <c r="E16">
+      <c r="F16">
+        <v>-1524530</v>
+      </c>
+      <c r="G16">
         <v>-39201093</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>-24097951</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>-13891744</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>-21896767</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>-10639251</v>
       </c>
     </row>
@@ -1918,27 +2095,33 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-14436129</v>
+      </c>
+      <c r="C17">
         <v>-37603639</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-25786217</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>-15907919</v>
       </c>
-      <c r="E17">
+      <c r="F17">
+        <v>-7012932</v>
+      </c>
+      <c r="G17">
         <v>-24577856</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>-14056343</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>-8476066</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>-11346004</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>-4515212</v>
       </c>
     </row>
@@ -1947,27 +2130,33 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>3733341</v>
+      </c>
+      <c r="C18">
         <v>23792181</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>40602333</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>17862530</v>
       </c>
-      <c r="E18">
+      <c r="F18">
+        <v>8636218</v>
+      </c>
+      <c r="G18">
         <v>30502172</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>22538092</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>17102048</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>19393593</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>14131630</v>
       </c>
     </row>
@@ -1976,27 +2165,33 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-28718445</v>
+      </c>
+      <c r="C19">
         <v>-57912286</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>-68780795</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-5718189</v>
       </c>
-      <c r="E19">
+      <c r="F19">
+        <v>-45618652</v>
+      </c>
+      <c r="G19">
         <v>-64088224</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>-22596758</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>-17415270</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>-41825078</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>-18726791</v>
       </c>
     </row>
@@ -2010,27 +2205,33 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>-32287378</v>
+      </c>
+      <c r="C21">
         <v>254692667</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>96889184</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>67287658</v>
       </c>
-      <c r="E21">
+      <c r="F21">
+        <v>14895874</v>
+      </c>
+      <c r="G21">
         <v>238400834</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>51116052</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>28907794</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>195882846</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>33702079</v>
       </c>
     </row>
@@ -2050,24 +2251,30 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>10482138</v>
+      </c>
+      <c r="C25">
         <v>45446148</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>19320082</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>3713582</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
       <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <v>1431413</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>457089</v>
       </c>
     </row>
@@ -2081,19 +2288,25 @@
       <c r="C26">
         <v>0</v>
       </c>
-      <c r="E26">
-        <v>-890441</v>
+      <c r="D26">
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
+        <v>-890441</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
         <v>-903639</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>-12202369</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>-8283522</v>
       </c>
     </row>
@@ -2132,27 +2345,33 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>-21805240</v>
+      </c>
+      <c r="C33">
         <v>300138815</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>116209266</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>71001240</v>
       </c>
-      <c r="E33">
+      <c r="F33">
+        <v>14895874</v>
+      </c>
+      <c r="G33">
         <v>237510393</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>51116052</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>28004155</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>185111890</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>25875646</v>
       </c>
     </row>
@@ -2162,27 +2381,33 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>60385379</v>
+      </c>
+      <c r="C35">
         <v>69602222</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>27338661</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>12856498</v>
       </c>
-      <c r="E35">
+      <c r="F35">
+        <v>5789437</v>
+      </c>
+      <c r="G35">
         <v>1485657</v>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>902976</v>
       </c>
-      <c r="G35">
+      <c r="I35">
         <v>698119</v>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>593</v>
       </c>
-      <c r="I35">
+      <c r="K35">
         <v>1142</v>
       </c>
     </row>
@@ -2191,27 +2416,33 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-28304263</v>
+      </c>
+      <c r="C36">
         <v>-120416830</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-99531427</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-65268707</v>
       </c>
-      <c r="E36">
+      <c r="F36">
+        <v>-10162847</v>
+      </c>
+      <c r="G36">
         <v>-65556831</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>-34638819</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>-25582724</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>-20196310</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>-8817366</v>
       </c>
     </row>
@@ -2225,27 +2456,33 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>10275876</v>
+      </c>
+      <c r="C38">
         <v>249324207</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>44016500</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>18589031</v>
       </c>
-      <c r="E38">
+      <c r="F38">
+        <v>10522464</v>
+      </c>
+      <c r="G38">
         <v>173439219</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>17380209</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>3119550</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>164916173</v>
       </c>
-      <c r="I38">
+      <c r="K38">
         <v>17059422</v>
       </c>
     </row>
@@ -2255,21 +2492,27 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>-4450132</v>
+      </c>
+      <c r="C40">
         <v>2299958</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>0</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>0</v>
       </c>
-      <c r="F40">
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>-426260</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>2160710</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>32827</v>
       </c>
     </row>
@@ -2278,18 +2521,24 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
         <v>-819038</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>0</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>0</v>
       </c>
-      <c r="F41">
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>-426260</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>-11863</v>
       </c>
     </row>
@@ -2298,18 +2547,24 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>-4450132</v>
+      </c>
+      <c r="C42">
         <v>3118996</v>
       </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="E42">
+      <c r="D42">
         <v>0</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
-      <c r="I42">
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="K42">
         <v>44690</v>
       </c>
     </row>
@@ -2318,33 +2573,45 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>5825744</v>
+      </c>
+      <c r="C43">
         <v>251624165</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>44016500</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>18589031</v>
       </c>
-      <c r="E43">
+      <c r="F43">
+        <v>10522464</v>
+      </c>
+      <c r="G43">
         <v>173439219</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>16953949</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>3119550</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>167076883</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>17092249</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
       </c>
     </row>
     <row r="45"/>
@@ -2353,27 +2620,33 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>5825744</v>
+      </c>
+      <c r="C46">
         <v>251624165</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>44016500</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>18589031</v>
       </c>
-      <c r="E46">
+      <c r="F46">
+        <v>10522464</v>
+      </c>
+      <c r="G46">
         <v>173439219</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>16953949</v>
       </c>
-      <c r="G46">
+      <c r="I46">
         <v>3119550</v>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>167076883</v>
       </c>
-      <c r="I46">
+      <c r="K46">
         <v>17092249</v>
       </c>
     </row>
@@ -2382,24 +2655,30 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
+        <v>-1075256</v>
+      </c>
+      <c r="C47">
         <v>6672840</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>7085962</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>4692221</v>
       </c>
-      <c r="E47">
+      <c r="F47">
+        <v>-688554</v>
+      </c>
+      <c r="G47">
         <v>8925722</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>-673996</v>
       </c>
-      <c r="G47">
+      <c r="I47">
         <v>-593350</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>-109218</v>
       </c>
     </row>
@@ -2408,27 +2687,33 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>6901000</v>
+      </c>
+      <c r="C48">
         <v>244951325</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>36930538</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>13896810</v>
       </c>
-      <c r="E48">
+      <c r="F48">
+        <v>11211018</v>
+      </c>
+      <c r="G48">
         <v>164513497</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>17627945</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>3712900</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>167186101</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>17092249</v>
       </c>
     </row>
@@ -2438,40 +2723,46 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>27484584</v>
+      </c>
+      <c r="C50">
         <v>65840618</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>41967651</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>24192705</v>
       </c>
-      <c r="E50">
+      <c r="F50">
+        <v>11372131</v>
+      </c>
+      <c r="G50">
         <v>32234100</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>19259951</v>
       </c>
-      <c r="G50">
+      <c r="I50">
         <v>14124351</v>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>20585442</v>
       </c>
-      <c r="I50">
+      <c r="K50">
         <v>11926139</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2482,6 +2773,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2489,27 +2782,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2523,15 +2822,24 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>197927592</v>
+      </c>
+      <c r="C3">
         <v>520146226</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>224799507</v>
       </c>
       <c r="E3">
+        <v>153255905</v>
+      </c>
+      <c r="F3">
+        <v>113767057</v>
+      </c>
+      <c r="G3">
         <v>374298066</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>96170678</v>
       </c>
     </row>
@@ -2544,7 +2852,7 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>113820031</v>
       </c>
     </row>
@@ -2552,7 +2860,7 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>407219554</v>
       </c>
     </row>
@@ -2561,15 +2869,24 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-63563455</v>
+      </c>
+      <c r="C7">
         <v>-156753675</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-82847404</v>
       </c>
       <c r="E7">
+        <v>-58561339</v>
+      </c>
+      <c r="F7">
+        <v>-39868049</v>
+      </c>
+      <c r="G7">
         <v>-87055613</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>-43964592</v>
       </c>
     </row>
@@ -2578,15 +2895,24 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>134364137</v>
+      </c>
+      <c r="C8">
         <v>363392551</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>141952103</v>
       </c>
       <c r="E8">
+        <v>94694566</v>
+      </c>
+      <c r="F8">
+        <v>73899008</v>
+      </c>
+      <c r="G8">
         <v>287242453</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>52206086</v>
       </c>
     </row>
@@ -2615,15 +2941,24 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>134364137</v>
+      </c>
+      <c r="C13">
         <v>363392551</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>141952103</v>
       </c>
       <c r="E13">
+        <v>94694566</v>
+      </c>
+      <c r="F13">
+        <v>73899008</v>
+      </c>
+      <c r="G13">
         <v>287242453</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>52206086</v>
       </c>
     </row>
@@ -2633,15 +2968,24 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-79966378</v>
+      </c>
+      <c r="C15">
         <v>-152297950</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-48099574</v>
       </c>
       <c r="E15">
+        <v>-53254011</v>
+      </c>
+      <c r="F15">
+        <v>-13483238</v>
+      </c>
+      <c r="G15">
         <v>-40805630</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-14465900</v>
       </c>
     </row>
@@ -2650,15 +2994,24 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-47263904</v>
+      </c>
+      <c r="C16">
         <v>-35532053</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-14049902</v>
       </c>
       <c r="E16">
+        <v>-29280559</v>
+      </c>
+      <c r="F16">
+        <v>-1524530</v>
+      </c>
+      <c r="G16">
         <v>-15103142</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>-10206207</v>
       </c>
     </row>
@@ -2667,15 +3020,24 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-14436129</v>
+      </c>
+      <c r="C17">
         <v>-11817422</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-9878298</v>
       </c>
       <c r="E17">
+        <v>-8894987</v>
+      </c>
+      <c r="F17">
+        <v>-7012932</v>
+      </c>
+      <c r="G17">
         <v>-10521513</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>-5580277</v>
       </c>
     </row>
@@ -2684,15 +3046,24 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>3733341</v>
+      </c>
+      <c r="C18">
         <v>-16810152</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>22739803</v>
       </c>
       <c r="E18">
+        <v>9226312</v>
+      </c>
+      <c r="F18">
+        <v>8636218</v>
+      </c>
+      <c r="G18">
         <v>7964080</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>5436044</v>
       </c>
     </row>
@@ -2701,15 +3072,24 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-28718445</v>
+      </c>
+      <c r="C19">
         <v>10868509</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>-63062606</v>
       </c>
       <c r="E19">
+        <v>39900463</v>
+      </c>
+      <c r="F19">
+        <v>-45618652</v>
+      </c>
+      <c r="G19">
         <v>-41491466</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>-5181488</v>
       </c>
     </row>
@@ -2723,15 +3103,24 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>-32287378</v>
+      </c>
+      <c r="C21">
         <v>157803483</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>29601526</v>
       </c>
       <c r="E21">
+        <v>52391784</v>
+      </c>
+      <c r="F21">
+        <v>14895874</v>
+      </c>
+      <c r="G21">
         <v>187284782</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>22208258</v>
       </c>
     </row>
@@ -2751,12 +3140,21 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>10482138</v>
+      </c>
+      <c r="C25">
         <v>26126066</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>15606500</v>
       </c>
       <c r="E25">
+        <v>3713582</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>0</v>
       </c>
     </row>
@@ -2767,10 +3165,16 @@
       <c r="B26">
         <v>0</v>
       </c>
-      <c r="E26">
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
         <v>-890441</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>903639</v>
       </c>
     </row>
@@ -2809,15 +3213,24 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>-21805240</v>
+      </c>
+      <c r="C33">
         <v>183929549</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>45208026</v>
       </c>
       <c r="E33">
+        <v>56105366</v>
+      </c>
+      <c r="F33">
+        <v>14895874</v>
+      </c>
+      <c r="G33">
         <v>186394341</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>23111897</v>
       </c>
     </row>
@@ -2827,15 +3240,24 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>60385379</v>
+      </c>
+      <c r="C35">
         <v>42263561</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>14482163</v>
       </c>
       <c r="E35">
+        <v>7067061</v>
+      </c>
+      <c r="F35">
+        <v>5789437</v>
+      </c>
+      <c r="G35">
         <v>582681</v>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>204857</v>
       </c>
     </row>
@@ -2844,15 +3266,24 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-28304263</v>
+      </c>
+      <c r="C36">
         <v>-20885403</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-34262720</v>
       </c>
       <c r="E36">
+        <v>-55105860</v>
+      </c>
+      <c r="F36">
+        <v>-10162847</v>
+      </c>
+      <c r="G36">
         <v>-30918012</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>-9056095</v>
       </c>
     </row>
@@ -2866,15 +3297,24 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>10275876</v>
+      </c>
+      <c r="C38">
         <v>205307707</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>25427469</v>
       </c>
       <c r="E38">
+        <v>8066567</v>
+      </c>
+      <c r="F38">
+        <v>10522464</v>
+      </c>
+      <c r="G38">
         <v>156059010</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>14260659</v>
       </c>
     </row>
@@ -2884,9 +3324,15 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>-4450132</v>
+      </c>
+      <c r="C40">
         <v>2299958</v>
       </c>
-      <c r="E40">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
         <v>426260</v>
       </c>
     </row>
@@ -2895,9 +3341,15 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
         <v>-819038</v>
       </c>
-      <c r="E41">
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
         <v>426260</v>
       </c>
     </row>
@@ -2906,9 +3358,15 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>-4450132</v>
+      </c>
+      <c r="C42">
         <v>3118996</v>
       </c>
-      <c r="E42">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
         <v>0</v>
       </c>
     </row>
@@ -2917,21 +3375,36 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>5825744</v>
+      </c>
+      <c r="C43">
         <v>207607665</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>25427469</v>
       </c>
       <c r="E43">
+        <v>8066567</v>
+      </c>
+      <c r="F43">
+        <v>10522464</v>
+      </c>
+      <c r="G43">
         <v>156485270</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>13834399</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
       </c>
     </row>
     <row r="45"/>
@@ -2940,15 +3413,24 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>5825744</v>
+      </c>
+      <c r="C46">
         <v>207607665</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>25427469</v>
       </c>
       <c r="E46">
+        <v>8066567</v>
+      </c>
+      <c r="F46">
+        <v>10522464</v>
+      </c>
+      <c r="G46">
         <v>156485270</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>13834399</v>
       </c>
     </row>
@@ -2957,15 +3439,24 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
+        <v>-1075256</v>
+      </c>
+      <c r="C47">
         <v>-413122</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>2393741</v>
       </c>
       <c r="E47">
+        <v>5380775</v>
+      </c>
+      <c r="F47">
+        <v>-688554</v>
+      </c>
+      <c r="G47">
         <v>9599718</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>-80646</v>
       </c>
     </row>
@@ -2974,15 +3465,24 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>6901000</v>
+      </c>
+      <c r="C48">
         <v>208020787</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>23033728</v>
       </c>
       <c r="E48">
+        <v>2685792</v>
+      </c>
+      <c r="F48">
+        <v>11211018</v>
+      </c>
+      <c r="G48">
         <v>146885552</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>13915045</v>
       </c>
     </row>
@@ -2992,28 +3492,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>27484584</v>
+      </c>
+      <c r="C50">
         <v>23872967</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>17774946</v>
       </c>
       <c r="E50">
+        <v>12820574</v>
+      </c>
+      <c r="F50">
+        <v>11372131</v>
+      </c>
+      <c r="G50">
         <v>12974149</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>5135600</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3024,6 +3533,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3031,27 +3542,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3065,21 +3582,24 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>1096129230</v>
+      </c>
+      <c r="C3">
         <v>1011968695</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>866120535</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>737491706</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>628321226</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>422892272</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>156342926</v>
       </c>
     </row>
@@ -3092,10 +3612,10 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>146595738</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>98646262</v>
       </c>
     </row>
@@ -3103,10 +3623,10 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>863879783</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>547562429</v>
       </c>
     </row>
@@ -3115,21 +3635,24 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-361725873</v>
+      </c>
+      <c r="C7">
         <v>-338030467</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-268332405</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-229449593</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>-212705658</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>-130783032</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>-83686976</v>
       </c>
     </row>
@@ -3138,21 +3661,24 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>734403357</v>
+      </c>
+      <c r="C8">
         <v>673938228</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>597788130</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>508042113</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>415615568</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>292109240</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>72655950</v>
       </c>
     </row>
@@ -3181,21 +3707,24 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>734403357</v>
+      </c>
+      <c r="C13">
         <v>673938228</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>597788130</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>508042113</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>415615568</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>292109240</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>72655950</v>
       </c>
     </row>
@@ -3205,21 +3734,24 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-333617913</v>
+      </c>
+      <c r="C15">
         <v>-267134773</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-155642453</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-122008779</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>-79849733</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-40552138</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-19204247</v>
       </c>
     </row>
@@ -3228,21 +3760,24 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-126126418</v>
+      </c>
+      <c r="C16">
         <v>-80387044</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-59958133</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-56114438</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>-39201093</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>-21896767</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>-10639251</v>
       </c>
     </row>
@@ -3251,21 +3786,24 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-45026836</v>
+      </c>
+      <c r="C17">
         <v>-37603639</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-36307730</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>-32009709</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>-24577856</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>-11346004</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>-4515212</v>
       </c>
     </row>
@@ -3274,21 +3812,24 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>18889304</v>
+      </c>
+      <c r="C18">
         <v>23792181</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>48566413</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>31262654</v>
       </c>
-      <c r="E18">
+      <c r="G18">
         <v>30502172</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>19393593</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>14131630</v>
       </c>
     </row>
@@ -3297,21 +3838,24 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-41012079</v>
+      </c>
+      <c r="C19">
         <v>-57912286</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>-110272261</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-52391143</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>-64088224</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>-41825078</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>-18726791</v>
       </c>
     </row>
@@ -3325,21 +3869,24 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>207509415</v>
+      </c>
+      <c r="C21">
         <v>254692667</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>284173966</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>276780698</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>238400834</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>195882846</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>33702079</v>
       </c>
     </row>
@@ -3359,18 +3906,21 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>55928286</v>
+      </c>
+      <c r="C25">
         <v>45446148</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>19320082</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <v>0</v>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>1431413</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>457089</v>
       </c>
     </row>
@@ -3382,15 +3932,18 @@
         <v>0</v>
       </c>
       <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
         <v>-890441</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <v>-890441</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>-12202369</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>-8283522</v>
       </c>
     </row>
@@ -3429,21 +3982,24 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>263437701</v>
+      </c>
+      <c r="C33">
         <v>300138815</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>302603607</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>280507478</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>237510393</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>185111890</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>25875646</v>
       </c>
     </row>
@@ -3453,21 +4009,24 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>124198164</v>
+      </c>
+      <c r="C35">
         <v>69602222</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>27921342</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>13644036</v>
       </c>
-      <c r="E35">
+      <c r="G35">
         <v>1485657</v>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>593</v>
       </c>
-      <c r="I35">
+      <c r="K35">
         <v>1142</v>
       </c>
     </row>
@@ -3476,21 +4035,24 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-138558246</v>
+      </c>
+      <c r="C36">
         <v>-120416830</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-130449439</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-105242814</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>-65556831</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>-20196310</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>-8817366</v>
       </c>
     </row>
@@ -3504,21 +4066,24 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>249077619</v>
+      </c>
+      <c r="C38">
         <v>249324207</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>200075510</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>188908700</v>
       </c>
-      <c r="E38">
+      <c r="G38">
         <v>173439219</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>164916173</v>
       </c>
-      <c r="I38">
+      <c r="K38">
         <v>17059422</v>
       </c>
     </row>
@@ -3528,18 +4093,21 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>-2150174</v>
+      </c>
+      <c r="C40">
         <v>2299958</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>426260</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>2160710</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>32827</v>
       </c>
     </row>
@@ -3551,12 +4119,15 @@
         <v>-819038</v>
       </c>
       <c r="C41">
+        <v>-819038</v>
+      </c>
+      <c r="D41">
         <v>426260</v>
       </c>
-      <c r="E41">
+      <c r="G41">
         <v>0</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>-11863</v>
       </c>
     </row>
@@ -3565,15 +4136,18 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>-1331136</v>
+      </c>
+      <c r="C42">
         <v>3118996</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>0</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <v>0</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>44690</v>
       </c>
     </row>
@@ -3582,21 +4156,24 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>246927445</v>
+      </c>
+      <c r="C43">
         <v>251624165</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>200501770</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>188908700</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>173439219</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>167076883</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>17092249</v>
       </c>
     </row>
@@ -3611,21 +4188,24 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>246927445</v>
+      </c>
+      <c r="C46">
         <v>251624165</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>200501770</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>188908700</v>
       </c>
-      <c r="E46">
+      <c r="G46">
         <v>173439219</v>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>167076883</v>
       </c>
-      <c r="I46">
+      <c r="K46">
         <v>17092249</v>
       </c>
     </row>
@@ -3634,18 +4214,21 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
+        <v>6286138</v>
+      </c>
+      <c r="C47">
         <v>6672840</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>16685680</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>14211293</v>
       </c>
-      <c r="E47">
+      <c r="G47">
         <v>8925722</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>-109218</v>
       </c>
     </row>
@@ -3654,21 +4237,24 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>240641307</v>
+      </c>
+      <c r="C48">
         <v>244951325</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>183816090</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>174697407</v>
       </c>
-      <c r="E48">
+      <c r="G48">
         <v>164513497</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>167186101</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>17092249</v>
       </c>
     </row>
@@ -3678,34 +4264,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>81953071</v>
+      </c>
+      <c r="C50">
         <v>65840618</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>54941800</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>42302454</v>
       </c>
-      <c r="E50">
+      <c r="G50">
         <v>32234100</v>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>20585442</v>
       </c>
-      <c r="I50">
+      <c r="K50">
         <v>11926139</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3716,6 +4305,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3723,27 +4314,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3757,27 +4354,33 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>-469115735</v>
+      </c>
+      <c r="C3">
         <v>-503185322</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>-1029328262</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>-194359396</v>
       </c>
-      <c r="E3">
+      <c r="F3">
+        <v>-96320615</v>
+      </c>
+      <c r="G3">
         <v>-48088078</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>-77778337</v>
       </c>
-      <c r="G3">
-        <v>19883571</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
+        <v>25195672</v>
+      </c>
+      <c r="J3">
         <v>58558396</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>12848534</v>
       </c>
     </row>
@@ -3786,27 +4389,33 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>6901000</v>
+      </c>
+      <c r="C4">
         <v>244951325</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>36930538</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>13896810</v>
       </c>
-      <c r="E4">
+      <c r="F4">
+        <v>11211018</v>
+      </c>
+      <c r="G4">
         <v>164513497</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>17627945</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>3712900</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>167186101</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>17092249</v>
       </c>
     </row>
@@ -3815,15 +4424,21 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-315830805</v>
+      </c>
+      <c r="C5">
         <v>-16978346</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>14250618</v>
       </c>
-      <c r="E5">
+      <c r="F5">
+        <v>7337228</v>
+      </c>
+      <c r="G5">
         <v>98657147</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>2945839</v>
       </c>
     </row>
@@ -3832,27 +4447,33 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>27484584</v>
+      </c>
+      <c r="C6">
         <v>65840618</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>41967651</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>24192705</v>
       </c>
-      <c r="E6">
+      <c r="F6">
+        <v>11372131</v>
+      </c>
+      <c r="G6">
         <v>32234100</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>19259951</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>14124351</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>20585442</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>11926139</v>
       </c>
     </row>
@@ -3861,27 +4482,33 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
+        <v>-320540</v>
+      </c>
+      <c r="C7">
         <v>-66325</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-54581</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-39105</v>
       </c>
-      <c r="E7">
+      <c r="F7">
+        <v>-21791</v>
+      </c>
+      <c r="G7">
         <v>-62023</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>-49498</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>21380</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>-391852</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>-136354</v>
       </c>
     </row>
@@ -3890,15 +4517,21 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>5607180</v>
+      </c>
+      <c r="C8">
         <v>5462188</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>1589088</v>
       </c>
-      <c r="E8">
+      <c r="F8">
+        <v>97058</v>
+      </c>
+      <c r="G8">
         <v>1388032</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>3839795</v>
       </c>
     </row>
@@ -3922,27 +4555,33 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>-32081116</v>
+      </c>
+      <c r="C12">
         <v>50814608</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>72192766</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>52330717</v>
       </c>
-      <c r="E12">
+      <c r="F12">
+        <v>4373410</v>
+      </c>
+      <c r="G12">
         <v>64071174</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>33735843</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>24873081</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>20130319</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>8804874</v>
       </c>
     </row>
@@ -3961,27 +4600,33 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>-125556163</v>
+      </c>
+      <c r="C15">
         <v>-136729477</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-91649780</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-8354105</v>
       </c>
-      <c r="E15">
+      <c r="F15">
+        <v>-8483580</v>
+      </c>
+      <c r="G15">
         <v>1025864</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-53840252</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>-5883645</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-30900633</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-13477221</v>
       </c>
     </row>
@@ -3999,10 +4644,16 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
+      <c r="B18">
+        <v>-195414882</v>
+      </c>
+      <c r="D18">
         <v>-9794526</v>
       </c>
       <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>0</v>
       </c>
     </row>
@@ -4016,15 +4667,21 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>4450132</v>
+      </c>
+      <c r="C20">
         <v>-2299958</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0</v>
       </c>
-      <c r="H20">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="J20">
         <v>2160710</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>32827</v>
       </c>
     </row>
@@ -4032,16 +4689,16 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>-1280942</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>-2898259</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>3673212</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>265968</v>
       </c>
     </row>
@@ -4049,16 +4706,16 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>-3713582</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>903639</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>10770956</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>7826433</v>
       </c>
     </row>
@@ -4092,27 +4749,33 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-160185930</v>
+      </c>
+      <c r="C28">
         <v>-730180294</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-1080509418</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>77032498</v>
       </c>
-      <c r="E28">
+      <c r="F28">
+        <v>-114868861</v>
+      </c>
+      <c r="G28">
         <v>-311258722</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>-98352121</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>34853447</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>193214255</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>32334915</v>
       </c>
     </row>
@@ -4120,16 +4783,16 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>-6273412</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>-523309567</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>0</v>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>0</v>
       </c>
     </row>
@@ -4143,27 +4806,33 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>-82621235</v>
+      </c>
+      <c r="C31">
         <v>-216817614</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-243111935</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>-93079514</v>
       </c>
-      <c r="E31">
+      <c r="F31">
+        <v>-45245739</v>
+      </c>
+      <c r="G31">
         <v>-289100978</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>-57255009</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>-62440075</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>-17622181</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>-51201567</v>
       </c>
     </row>
@@ -4177,27 +4846,33 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-9945313</v>
+      </c>
+      <c r="C33">
         <v>-2308102</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>-2771841</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>376514</v>
       </c>
-      <c r="E33">
+      <c r="F33">
+        <v>424822</v>
+      </c>
+      <c r="G33">
         <v>2607306</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>2215027</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>-910310</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>-959214</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>175606</v>
       </c>
     </row>
@@ -4221,27 +4896,33 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>129330784</v>
+      </c>
+      <c r="C37">
         <v>-101887129</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>756644</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>-5336279</v>
       </c>
-      <c r="E37">
+      <c r="F37">
+        <v>-16839937</v>
+      </c>
+      <c r="G37">
         <v>-60303812</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>-25867949</v>
       </c>
-      <c r="G37">
+      <c r="I37">
         <v>-524195</v>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>-104429261</v>
       </c>
-      <c r="I37">
+      <c r="K37">
         <v>10948116</v>
       </c>
     </row>
@@ -4255,27 +4936,33 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-57788816</v>
+      </c>
+      <c r="C39">
         <v>-457862766</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>-197316407</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-10162817</v>
       </c>
-      <c r="E39">
+      <c r="F39">
+        <v>-63828379</v>
+      </c>
+      <c r="G39">
         <v>-114336110</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>-29425921</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>65006444</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>-130501841</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>3839601</v>
       </c>
     </row>
@@ -4284,27 +4971,33 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>13268286</v>
+      </c>
+      <c r="C40">
         <v>80389247</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>-18915305</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>-92746647</v>
       </c>
-      <c r="E40">
+      <c r="F40">
+        <v>-1666228</v>
+      </c>
+      <c r="G40">
         <v>83509636</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>31307380</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>3066235</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>-2036188</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>8236744</v>
       </c>
     </row>
@@ -4318,24 +5011,30 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>20003187</v>
+      </c>
+      <c r="C42">
         <v>18787316</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>4867683</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>-1000000</v>
       </c>
-      <c r="E42">
+      <c r="F42">
+        <v>11307526</v>
+      </c>
+      <c r="G42">
         <v>8127802</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>41448231</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>-488617</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>-167998</v>
       </c>
     </row>
@@ -4349,27 +5048,33 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-735918</v>
+      </c>
+      <c r="C44">
         <v>-38768386</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-39441131</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>6245353</v>
       </c>
-      <c r="E44">
+      <c r="F44">
+        <v>-9761401</v>
+      </c>
+      <c r="G44">
         <v>44528922</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>6517920</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>53191859</v>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>-923122</v>
       </c>
-      <c r="I44">
+      <c r="K44">
         <v>3547293</v>
       </c>
     </row>
@@ -4388,27 +5093,33 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>-162467519</v>
+      </c>
+      <c r="C47">
         <v>81488454</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>-40273266</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>-89375788</v>
       </c>
-      <c r="E47">
+      <c r="F47">
+        <v>12386094</v>
+      </c>
+      <c r="G47">
         <v>12725059</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>-60762778</v>
       </c>
-      <c r="G47">
+      <c r="I47">
         <v>-62269602</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>121587623</v>
       </c>
-      <c r="I47">
+      <c r="K47">
         <v>3953812</v>
       </c>
     </row>
@@ -4417,27 +5128,33 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-9229386</v>
+      </c>
+      <c r="C48">
         <v>-86927902</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>-20994293</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>-3864816</v>
       </c>
-      <c r="E48">
+      <c r="F48">
+        <v>-1645619</v>
+      </c>
+      <c r="G48">
         <v>983453</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>-6529022</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>-4778131</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>-1008266</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>458653</v>
       </c>
     </row>
@@ -4446,15 +5163,21 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>-469115735</v>
+      </c>
+      <c r="C49">
         <v>-502207315</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>-1029328262</v>
       </c>
-      <c r="E49">
+      <c r="F49">
+        <v>-96320615</v>
+      </c>
+      <c r="G49">
         <v>-48088078</v>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>-77778337</v>
       </c>
     </row>
@@ -4482,16 +5205,16 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>-171855</v>
       </c>
-      <c r="E54">
+      <c r="G54">
         <v>0</v>
       </c>
-      <c r="H54">
+      <c r="J54">
         <v>-2160710</v>
       </c>
-      <c r="I54">
+      <c r="K54">
         <v>-32827</v>
       </c>
     </row>
@@ -4534,19 +5257,19 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>-806152</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>0</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>17552100</v>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>0</v>
       </c>
-      <c r="G62">
+      <c r="I62">
         <v>-5312101</v>
       </c>
     </row>
@@ -4571,27 +5294,33 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-71252567</v>
+      </c>
+      <c r="C67">
         <v>-428503635</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>-84542318</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>-43607628</v>
       </c>
-      <c r="E67">
+      <c r="F67">
+        <v>-22095128</v>
+      </c>
+      <c r="G67">
         <v>-89669978</v>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>-70451695</v>
       </c>
-      <c r="G67">
+      <c r="I67">
         <v>-45082744</v>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>6317149</v>
       </c>
-      <c r="I67">
+      <c r="K67">
         <v>-27499067</v>
       </c>
     </row>
@@ -4644,28 +5373,28 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>0</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>361234</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>3713582</v>
       </c>
-      <c r="E77">
+      <c r="G77">
         <v>3652873</v>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>9150837</v>
       </c>
-      <c r="G77">
+      <c r="I77">
         <v>2793705</v>
       </c>
-      <c r="H77">
+      <c r="J77">
         <v>26001500</v>
       </c>
-      <c r="I77">
+      <c r="K77">
         <v>15577842</v>
       </c>
     </row>
@@ -4674,27 +5403,33 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-71252567</v>
+      </c>
+      <c r="C78">
         <v>-428503635</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>-84903552</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>-47321210</v>
       </c>
-      <c r="E78">
+      <c r="F78">
+        <v>-22095128</v>
+      </c>
+      <c r="G78">
         <v>-93322851</v>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>-79602532</v>
       </c>
-      <c r="G78">
+      <c r="I78">
         <v>-47876449</v>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>-19684351</v>
       </c>
-      <c r="I78">
+      <c r="K78">
         <v>-43076909</v>
       </c>
     </row>
@@ -4809,27 +5544,33 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>48615714</v>
+      </c>
+      <c r="C101">
         <v>1418179757</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>1443915777</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>191035455</v>
       </c>
-      <c r="E101">
+      <c r="F101">
+        <v>145764664</v>
+      </c>
+      <c r="G101">
         <v>178191856</v>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>133521590</v>
       </c>
-      <c r="G101">
+      <c r="I101">
         <v>8468858</v>
       </c>
-      <c r="H101">
+      <c r="J101">
         <v>-20934216</v>
       </c>
-      <c r="I101">
+      <c r="K101">
         <v>10779707</v>
       </c>
     </row>
@@ -4848,15 +5589,21 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
+        <v>254995</v>
+      </c>
+      <c r="C104">
         <v>1320711229</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>1322837997</v>
       </c>
-      <c r="E104">
+      <c r="F104">
+        <v>-59555</v>
+      </c>
+      <c r="G104">
         <v>-76046</v>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>212004</v>
       </c>
     </row>
@@ -4869,7 +5616,7 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="H106">
+      <c r="J106">
         <v>-18408566</v>
       </c>
     </row>
@@ -4877,19 +5624,19 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B107">
-        <v>30000000</v>
-      </c>
       <c r="C107">
         <v>30000000</v>
       </c>
-      <c r="E107">
+      <c r="D107">
+        <v>30000000</v>
+      </c>
+      <c r="G107">
         <v>0</v>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>0</v>
       </c>
-      <c r="I107">
+      <c r="K107">
         <v>22000000</v>
       </c>
     </row>
@@ -4903,27 +5650,33 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
+        <v>16279603</v>
+      </c>
+      <c r="C109">
         <v>118283136</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>163270546</v>
       </c>
-      <c r="D109">
+      <c r="E109">
         <v>240746227</v>
       </c>
-      <c r="E109">
+      <c r="F109">
+        <v>150197629</v>
+      </c>
+      <c r="G109">
         <v>260484128</v>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>185190481</v>
       </c>
-      <c r="G109">
+      <c r="I109">
         <v>48649964</v>
       </c>
-      <c r="H109">
+      <c r="J109">
         <v>51147213</v>
       </c>
-      <c r="I109">
+      <c r="K109">
         <v>-2580974</v>
       </c>
     </row>
@@ -4966,22 +5719,22 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="B117">
-        <v>0</v>
-      </c>
       <c r="C117">
         <v>0</v>
       </c>
-      <c r="E117">
-        <v>-18145052</v>
-      </c>
-      <c r="F117">
-        <v>-18145052</v>
+      <c r="D117">
+        <v>0</v>
       </c>
       <c r="G117">
         <v>-18145052</v>
       </c>
       <c r="H117">
+        <v>-18145052</v>
+      </c>
+      <c r="I117">
+        <v>-18145052</v>
+      </c>
+      <c r="J117">
         <v>-21675261</v>
       </c>
     </row>
@@ -4990,27 +5743,33 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-28304263</v>
+      </c>
+      <c r="C118">
         <v>-120416830</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>-99531427</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>-65268707</v>
       </c>
-      <c r="E118">
+      <c r="F118">
+        <v>-10162847</v>
+      </c>
+      <c r="G118">
         <v>-65556831</v>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>-34638819</v>
       </c>
-      <c r="G118">
+      <c r="I118">
         <v>-25582724</v>
       </c>
-      <c r="H118">
+      <c r="J118">
         <v>-20130912</v>
       </c>
-      <c r="I118">
+      <c r="K118">
         <v>-8806015</v>
       </c>
     </row>
@@ -5019,27 +5778,33 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
+        <v>60385379</v>
+      </c>
+      <c r="C119">
         <v>69602222</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>27338661</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>12856498</v>
       </c>
-      <c r="E119">
+      <c r="F119">
+        <v>5789437</v>
+      </c>
+      <c r="G119">
         <v>1485657</v>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>902976</v>
       </c>
-      <c r="G119">
+      <c r="I119">
         <v>698119</v>
       </c>
-      <c r="H119">
+      <c r="J119">
         <v>593</v>
       </c>
-      <c r="I119">
+      <c r="K119">
         <v>1142</v>
       </c>
     </row>
@@ -5062,16 +5827,16 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="D123">
+      <c r="E123">
         <v>2701437</v>
       </c>
-      <c r="G123">
+      <c r="I123">
         <v>2848551</v>
       </c>
-      <c r="H123">
+      <c r="J123">
         <v>-11867283</v>
       </c>
-      <c r="I123">
+      <c r="K123">
         <v>165554</v>
       </c>
     </row>
@@ -5085,27 +5850,33 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>-491752588</v>
+      </c>
+      <c r="C125">
         <v>486490800</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>330045197</v>
       </c>
-      <c r="D125">
+      <c r="E125">
         <v>-46931569</v>
       </c>
-      <c r="E125">
+      <c r="F125">
+        <v>27348921</v>
+      </c>
+      <c r="G125">
         <v>40433800</v>
       </c>
-      <c r="F125">
+      <c r="H125">
         <v>-14708442</v>
       </c>
-      <c r="G125">
+      <c r="I125">
         <v>-16730315</v>
       </c>
-      <c r="H125">
+      <c r="J125">
         <v>43941329</v>
       </c>
-      <c r="I125">
+      <c r="K125">
         <v>-3870826</v>
       </c>
     </row>
@@ -5117,24 +5888,30 @@
         <v>141243243</v>
       </c>
       <c r="C126">
+        <v>141243243</v>
+      </c>
+      <c r="D126">
         <v>65285871</v>
       </c>
-      <c r="D126">
+      <c r="E126">
         <v>44157919</v>
       </c>
-      <c r="E126">
+      <c r="F126">
+        <v>18887737</v>
+      </c>
+      <c r="G126">
         <v>51051049</v>
       </c>
-      <c r="F126">
+      <c r="H126">
         <v>10990976</v>
       </c>
-      <c r="G126">
+      <c r="I126">
         <v>14808978</v>
       </c>
-      <c r="H126">
+      <c r="J126">
         <v>-21455677</v>
       </c>
-      <c r="I126">
+      <c r="K126">
         <v>8491086</v>
       </c>
     </row>
@@ -5143,27 +5920,33 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>-350509345</v>
+      </c>
+      <c r="C127">
         <v>627734043</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>395331068</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>-2773650</v>
       </c>
-      <c r="E127">
+      <c r="F127">
+        <v>46236658</v>
+      </c>
+      <c r="G127">
         <v>91484849</v>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>-3717466</v>
       </c>
-      <c r="G127">
+      <c r="I127">
         <v>-1921337</v>
       </c>
-      <c r="H127">
+      <c r="J127">
         <v>22485652</v>
       </c>
-      <c r="I127">
+      <c r="K127">
         <v>4620260</v>
       </c>
     </row>
@@ -5172,15 +5955,21 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>120679477</v>
+        <v>748413520</v>
       </c>
       <c r="C128">
         <v>120679477</v>
       </c>
-      <c r="E128">
+      <c r="D128">
+        <v>120679477</v>
+      </c>
+      <c r="F128">
+        <v>120679477</v>
+      </c>
+      <c r="G128">
         <v>29194628</v>
       </c>
-      <c r="F128">
+      <c r="H128">
         <v>29194628</v>
       </c>
     </row>
@@ -5189,28 +5978,34 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>397904175</v>
+      </c>
+      <c r="C129">
         <v>748413520</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>516010545</v>
       </c>
-      <c r="E129">
+      <c r="F129">
+        <v>166916135</v>
+      </c>
+      <c r="G129">
         <v>120679477</v>
       </c>
-      <c r="F129">
+      <c r="H129">
         <v>25477162</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5221,6 +6016,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5228,27 +6025,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5262,16 +6065,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>-469115735</v>
+      </c>
+      <c r="C3">
         <v>526142940</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>-834968866</v>
       </c>
       <c r="E3">
+        <v>-98038781</v>
+      </c>
+      <c r="F3">
+        <v>-96320615</v>
+      </c>
+      <c r="G3">
         <v>29690259</v>
       </c>
-      <c r="F3">
-        <v>-97661908</v>
+      <c r="H3">
+        <v>-102974009</v>
       </c>
     </row>
     <row r="4">
@@ -5279,15 +6091,24 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>6901000</v>
+      </c>
+      <c r="C4">
         <v>208020787</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>23033728</v>
       </c>
       <c r="E4">
+        <v>2685792</v>
+      </c>
+      <c r="F4">
+        <v>11211018</v>
+      </c>
+      <c r="G4">
         <v>146885552</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>13915045</v>
       </c>
     </row>
@@ -5296,9 +6117,15 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-315830805</v>
+      </c>
+      <c r="C5">
         <v>-31228964</v>
       </c>
-      <c r="E5">
+      <c r="F5">
+        <v>7337228</v>
+      </c>
+      <c r="G5">
         <v>95711308</v>
       </c>
     </row>
@@ -5307,15 +6134,24 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>27484584</v>
+      </c>
+      <c r="C6">
         <v>23872967</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>17774946</v>
       </c>
       <c r="E6">
+        <v>12820574</v>
+      </c>
+      <c r="F6">
+        <v>11372131</v>
+      </c>
+      <c r="G6">
         <v>12974149</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>5135600</v>
       </c>
     </row>
@@ -5324,15 +6160,24 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
+        <v>-320540</v>
+      </c>
+      <c r="C7">
         <v>-11744</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-15476</v>
       </c>
       <c r="E7">
+        <v>-17314</v>
+      </c>
+      <c r="F7">
+        <v>-21791</v>
+      </c>
+      <c r="G7">
         <v>-12525</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>-70878</v>
       </c>
     </row>
@@ -5341,9 +6186,15 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>5607180</v>
+      </c>
+      <c r="C8">
         <v>3873100</v>
       </c>
-      <c r="E8">
+      <c r="F8">
+        <v>97058</v>
+      </c>
+      <c r="G8">
         <v>-2451763</v>
       </c>
     </row>
@@ -5367,15 +6218,24 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>-32081116</v>
+      </c>
+      <c r="C12">
         <v>-21378158</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>19862049</v>
       </c>
       <c r="E12">
+        <v>47957307</v>
+      </c>
+      <c r="F12">
+        <v>4373410</v>
+      </c>
+      <c r="G12">
         <v>30335331</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>8862762</v>
       </c>
     </row>
@@ -5394,15 +6254,24 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>-125556163</v>
+      </c>
+      <c r="C15">
         <v>-45079697</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-83295675</v>
       </c>
       <c r="E15">
+        <v>129475</v>
+      </c>
+      <c r="F15">
+        <v>-8483580</v>
+      </c>
+      <c r="G15">
         <v>54866116</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-47956607</v>
       </c>
     </row>
@@ -5420,6 +6289,12 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B18">
+        <v>-195414882</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -5430,6 +6305,12 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B20">
+        <v>4450132</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -5471,15 +6352,24 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-160185930</v>
+      </c>
+      <c r="C28">
         <v>350329124</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-1157541916</v>
       </c>
       <c r="E28">
+        <v>191901359</v>
+      </c>
+      <c r="F28">
+        <v>-114868861</v>
+      </c>
+      <c r="G28">
         <v>-212906601</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>-133205568</v>
       </c>
     </row>
@@ -5487,10 +6377,10 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>517036155</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>0</v>
       </c>
     </row>
@@ -5504,15 +6394,24 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>-82621235</v>
+      </c>
+      <c r="C31">
         <v>26294321</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-150032421</v>
       </c>
       <c r="E31">
+        <v>-47833775</v>
+      </c>
+      <c r="F31">
+        <v>-45245739</v>
+      </c>
+      <c r="G31">
         <v>-231845969</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>5185066</v>
       </c>
     </row>
@@ -5526,15 +6425,24 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-9945313</v>
+      </c>
+      <c r="C33">
         <v>463739</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>-3148355</v>
       </c>
       <c r="E33">
+        <v>-48308</v>
+      </c>
+      <c r="F33">
+        <v>424822</v>
+      </c>
+      <c r="G33">
         <v>392279</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>3125337</v>
       </c>
     </row>
@@ -5558,15 +6466,24 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>129330784</v>
+      </c>
+      <c r="C37">
         <v>-102643773</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>6092923</v>
       </c>
       <c r="E37">
+        <v>11503658</v>
+      </c>
+      <c r="F37">
+        <v>-16839937</v>
+      </c>
+      <c r="G37">
         <v>-34435863</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>-25343754</v>
       </c>
     </row>
@@ -5580,15 +6497,24 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-57788816</v>
+      </c>
+      <c r="C39">
         <v>-260546359</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>-187153590</v>
       </c>
       <c r="E39">
+        <v>53665562</v>
+      </c>
+      <c r="F39">
+        <v>-63828379</v>
+      </c>
+      <c r="G39">
         <v>-84910189</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>-94432365</v>
       </c>
     </row>
@@ -5597,15 +6523,24 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>13268286</v>
+      </c>
+      <c r="C40">
         <v>99304552</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>73831342</v>
       </c>
       <c r="E40">
+        <v>-91080419</v>
+      </c>
+      <c r="F40">
+        <v>-1666228</v>
+      </c>
+      <c r="G40">
         <v>52202256</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>28241145</v>
       </c>
     </row>
@@ -5619,12 +6554,21 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>20003187</v>
+      </c>
+      <c r="C42">
         <v>13919633</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>5867683</v>
       </c>
       <c r="E42">
+        <v>-12307526</v>
+      </c>
+      <c r="F42">
+        <v>11307526</v>
+      </c>
+      <c r="G42">
         <v>-33320429</v>
       </c>
     </row>
@@ -5638,15 +6582,24 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-735918</v>
+      </c>
+      <c r="C44">
         <v>672745</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-45686484</v>
       </c>
       <c r="E44">
+        <v>16006754</v>
+      </c>
+      <c r="F44">
+        <v>-9761401</v>
+      </c>
+      <c r="G44">
         <v>38011002</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>-46673939</v>
       </c>
     </row>
@@ -5665,15 +6618,24 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>-162467519</v>
+      </c>
+      <c r="C47">
         <v>121761720</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>49102522</v>
       </c>
       <c r="E47">
+        <v>-101761882</v>
+      </c>
+      <c r="F47">
+        <v>12386094</v>
+      </c>
+      <c r="G47">
         <v>73487837</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>1506824</v>
       </c>
     </row>
@@ -5682,15 +6644,24 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-9229386</v>
+      </c>
+      <c r="C48">
         <v>-65933609</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>-17129477</v>
       </c>
       <c r="E48">
+        <v>-2219197</v>
+      </c>
+      <c r="F48">
+        <v>-1645619</v>
+      </c>
+      <c r="G48">
         <v>7512475</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>-1750891</v>
       </c>
     </row>
@@ -5699,9 +6670,15 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>-469115735</v>
+      </c>
+      <c r="C49">
         <v>527120947</v>
       </c>
-      <c r="E49">
+      <c r="F49">
+        <v>-96320615</v>
+      </c>
+      <c r="G49">
         <v>29690259</v>
       </c>
     </row>
@@ -5769,13 +6746,13 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>-806152</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>-17552100</v>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>5312101</v>
       </c>
     </row>
@@ -5800,15 +6777,24 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-71252567</v>
+      </c>
+      <c r="C67">
         <v>-343961317</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>-40934690</v>
       </c>
       <c r="E67">
+        <v>-21512500</v>
+      </c>
+      <c r="F67">
+        <v>-22095128</v>
+      </c>
+      <c r="G67">
         <v>-19218283</v>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>-25368951</v>
       </c>
     </row>
@@ -5861,16 +6847,16 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>-361234</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>-3352348</v>
       </c>
-      <c r="E77">
+      <c r="G77">
         <v>-5497964</v>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>6357132</v>
       </c>
     </row>
@@ -5879,15 +6865,24 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-71252567</v>
+      </c>
+      <c r="C78">
         <v>-343600083</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>-37582342</v>
       </c>
       <c r="E78">
+        <v>-25226082</v>
+      </c>
+      <c r="F78">
+        <v>-22095128</v>
+      </c>
+      <c r="G78">
         <v>-13720319</v>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>-31726083</v>
       </c>
     </row>
@@ -6002,15 +6997,24 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>48615714</v>
+      </c>
+      <c r="C101">
         <v>-25736020</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>1252880322</v>
       </c>
       <c r="E101">
+        <v>45270791</v>
+      </c>
+      <c r="F101">
+        <v>145764664</v>
+      </c>
+      <c r="G101">
         <v>44670266</v>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>125052732</v>
       </c>
     </row>
@@ -6029,9 +7033,15 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
+        <v>254995</v>
+      </c>
+      <c r="C104">
         <v>-2126768</v>
       </c>
-      <c r="E104">
+      <c r="F104">
+        <v>-59555</v>
+      </c>
+      <c r="G104">
         <v>-288050</v>
       </c>
     </row>
@@ -6049,10 +7059,10 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B107">
+      <c r="C107">
         <v>0</v>
       </c>
-      <c r="E107">
+      <c r="G107">
         <v>0</v>
       </c>
     </row>
@@ -6066,15 +7076,24 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
+        <v>16279603</v>
+      </c>
+      <c r="C109">
         <v>-44987410</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>-77475681</v>
       </c>
       <c r="E109">
+        <v>90548598</v>
+      </c>
+      <c r="F109">
+        <v>150197629</v>
+      </c>
+      <c r="G109">
         <v>75293647</v>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>136540517</v>
       </c>
     </row>
@@ -6117,13 +7136,13 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="B117">
+      <c r="C117">
         <v>0</v>
       </c>
-      <c r="E117">
+      <c r="G117">
         <v>0</v>
       </c>
-      <c r="F117">
+      <c r="H117">
         <v>0</v>
       </c>
     </row>
@@ -6132,15 +7151,24 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-28304263</v>
+      </c>
+      <c r="C118">
         <v>-20885403</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>-34262720</v>
       </c>
       <c r="E118">
+        <v>-55105860</v>
+      </c>
+      <c r="F118">
+        <v>-10162847</v>
+      </c>
+      <c r="G118">
         <v>-30918012</v>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>-9056095</v>
       </c>
     </row>
@@ -6149,15 +7177,24 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
+        <v>60385379</v>
+      </c>
+      <c r="C119">
         <v>42263561</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>14482163</v>
       </c>
       <c r="E119">
+        <v>7067061</v>
+      </c>
+      <c r="F119">
+        <v>5789437</v>
+      </c>
+      <c r="G119">
         <v>582681</v>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>204857</v>
       </c>
     </row>
@@ -6191,15 +7228,24 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>-491752588</v>
+      </c>
+      <c r="C125">
         <v>156445603</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>376976766</v>
       </c>
       <c r="E125">
+        <v>-74280490</v>
+      </c>
+      <c r="F125">
+        <v>27348921</v>
+      </c>
+      <c r="G125">
         <v>55142242</v>
       </c>
-      <c r="F125">
+      <c r="H125">
         <v>2021873</v>
       </c>
     </row>
@@ -6208,15 +7254,24 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
+        <v>141243243</v>
+      </c>
+      <c r="C126">
         <v>75957372</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>21127952</v>
       </c>
       <c r="E126">
+        <v>25270182</v>
+      </c>
+      <c r="F126">
+        <v>18887737</v>
+      </c>
+      <c r="G126">
         <v>40060073</v>
       </c>
-      <c r="F126">
+      <c r="H126">
         <v>-3818002</v>
       </c>
     </row>
@@ -6225,15 +7280,24 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>-350509345</v>
+      </c>
+      <c r="C127">
         <v>232402975</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>398104718</v>
       </c>
       <c r="E127">
+        <v>-49010308</v>
+      </c>
+      <c r="F127">
+        <v>46236658</v>
+      </c>
+      <c r="G127">
         <v>95202315</v>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>-1796129</v>
       </c>
     </row>
@@ -6242,9 +7306,15 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
+        <v>748413520</v>
+      </c>
+      <c r="C128">
         <v>0</v>
       </c>
-      <c r="E128">
+      <c r="F128">
+        <v>120679477</v>
+      </c>
+      <c r="G128">
         <v>0</v>
       </c>
     </row>
@@ -6253,22 +7323,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>397904175</v>
+      </c>
+      <c r="C129">
         <v>232402975</v>
       </c>
-      <c r="E129">
+      <c r="F129">
+        <v>166916135</v>
+      </c>
+      <c r="G129">
         <v>95202315</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6279,6 +7355,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6286,27 +7364,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -6320,21 +7404,24 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>-875980442</v>
+      </c>
+      <c r="C3">
         <v>-503185322</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>-999638003</v>
       </c>
-      <c r="D3">
-        <v>-262331045</v>
-      </c>
       <c r="E3">
+        <v>-267643146</v>
+      </c>
+      <c r="G3">
         <v>-48088078</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>58558396</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>12848534</v>
       </c>
     </row>
@@ -6343,21 +7430,24 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>240641307</v>
+      </c>
+      <c r="C4">
         <v>244951325</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>183816090</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>174697407</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>164513497</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>167186101</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>17092249</v>
       </c>
     </row>
@@ -6366,12 +7456,15 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-340146379</v>
+      </c>
+      <c r="C5">
         <v>-16978346</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>109961926</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>98657147</v>
       </c>
     </row>
@@ -6380,21 +7473,24 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>81953071</v>
+      </c>
+      <c r="C6">
         <v>65840618</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>54941800</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>42302454</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>32234100</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>20585442</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>11926139</v>
       </c>
     </row>
@@ -6403,21 +7499,24 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
+        <v>-365074</v>
+      </c>
+      <c r="C7">
         <v>-66325</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-67106</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-122508</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>-62023</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>-391852</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>-136354</v>
       </c>
     </row>
@@ -6426,12 +7525,15 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>10972310</v>
+      </c>
+      <c r="C8">
         <v>5462188</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>-862675</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>1388032</v>
       </c>
     </row>
@@ -6455,21 +7557,24 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>14360082</v>
+      </c>
+      <c r="C12">
         <v>50814608</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>102528097</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>91528810</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>64071174</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>20130319</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>8804874</v>
       </c>
     </row>
@@ -6488,21 +7593,24 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>-253802060</v>
+      </c>
+      <c r="C15">
         <v>-136729477</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-36783664</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-1444596</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>1025864</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-30900633</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-13477221</v>
       </c>
     </row>
@@ -6531,15 +7639,18 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>2150174</v>
+      </c>
+      <c r="C20">
         <v>-2299958</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>0</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>2160710</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>32827</v>
       </c>
     </row>
@@ -6547,10 +7658,10 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>3673212</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>265968</v>
       </c>
     </row>
@@ -6558,10 +7669,10 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>10770956</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>7826433</v>
       </c>
     </row>
@@ -6595,21 +7706,24 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-775497363</v>
+      </c>
+      <c r="C28">
         <v>-730180294</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-1293416019</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>-269079671</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>-311258722</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>193214255</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>32334915</v>
       </c>
     </row>
@@ -6617,13 +7731,13 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>-6273412</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>-523309567</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>0</v>
       </c>
     </row>
@@ -6637,21 +7751,24 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>-254193110</v>
+      </c>
+      <c r="C31">
         <v>-216817614</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-474957904</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>-319740417</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <v>-289100978</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>-17622181</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>-51201567</v>
       </c>
     </row>
@@ -6665,21 +7782,24 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-12678237</v>
+      </c>
+      <c r="C33">
         <v>-2308102</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>-2379562</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>3894130</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>2607306</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>-959214</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>175606</v>
       </c>
     </row>
@@ -6703,21 +7823,24 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>44283592</v>
+      </c>
+      <c r="C37">
         <v>-101887129</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>-33679219</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>-65115896</v>
       </c>
-      <c r="E37">
+      <c r="G37">
         <v>-60303812</v>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>-104429261</v>
       </c>
-      <c r="I37">
+      <c r="K37">
         <v>10948116</v>
       </c>
     </row>
@@ -6731,21 +7854,24 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-451823203</v>
+      </c>
+      <c r="C39">
         <v>-457862766</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>-282226596</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-189505371</v>
       </c>
-      <c r="E39">
+      <c r="G39">
         <v>-114336110</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>-130501841</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>3839601</v>
       </c>
     </row>
@@ -6754,21 +7880,24 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>95323761</v>
+      </c>
+      <c r="C40">
         <v>80389247</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>33286951</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>-12303246</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>83509636</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>-2036188</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>8236744</v>
       </c>
     </row>
@@ -6782,18 +7911,21 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>27482977</v>
+      </c>
+      <c r="C42">
         <v>18787316</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>-28452746</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <v>8127802</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>-488617</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>-167998</v>
       </c>
     </row>
@@ -6807,21 +7939,24 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-29742903</v>
+      </c>
+      <c r="C44">
         <v>-38768386</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-1430129</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>-2417584</v>
       </c>
-      <c r="E44">
+      <c r="G44">
         <v>44528922</v>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>-923122</v>
       </c>
-      <c r="I44">
+      <c r="K44">
         <v>3547293</v>
       </c>
     </row>
@@ -6840,21 +7975,24 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>-93365159</v>
+      </c>
+      <c r="C47">
         <v>81488454</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>33214571</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>-14381127</v>
       </c>
-      <c r="E47">
+      <c r="G47">
         <v>12725059</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>121587623</v>
       </c>
-      <c r="I47">
+      <c r="K47">
         <v>3953812</v>
       </c>
     </row>
@@ -6863,21 +8001,24 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-94511669</v>
+      </c>
+      <c r="C48">
         <v>-86927902</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>-13481818</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>1896768</v>
       </c>
-      <c r="E48">
+      <c r="G48">
         <v>983453</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>-1008266</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>458653</v>
       </c>
     </row>
@@ -6886,12 +8027,15 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>-875002435</v>
+      </c>
+      <c r="C49">
         <v>-502207315</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>-999638003</v>
       </c>
-      <c r="E49">
+      <c r="G49">
         <v>-48088078</v>
       </c>
     </row>
@@ -6919,16 +8063,16 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>-171855</v>
       </c>
-      <c r="E54">
+      <c r="G54">
         <v>0</v>
       </c>
-      <c r="H54">
+      <c r="J54">
         <v>-2160710</v>
       </c>
-      <c r="I54">
+      <c r="K54">
         <v>-32827</v>
       </c>
     </row>
@@ -6971,7 +8115,7 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>-806152</v>
       </c>
     </row>
@@ -6996,21 +8140,24 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-477661074</v>
+      </c>
+      <c r="C67">
         <v>-428503635</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>-103760601</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>-88194862</v>
       </c>
-      <c r="E67">
+      <c r="G67">
         <v>-89669978</v>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>6317149</v>
       </c>
-      <c r="I67">
+      <c r="K67">
         <v>-27499067</v>
       </c>
     </row>
@@ -7063,22 +8210,22 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>0</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>-5136730</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>4572750</v>
       </c>
-      <c r="E77">
+      <c r="G77">
         <v>3652873</v>
       </c>
-      <c r="H77">
+      <c r="J77">
         <v>26001500</v>
       </c>
-      <c r="I77">
+      <c r="K77">
         <v>15577842</v>
       </c>
     </row>
@@ -7087,21 +8234,24 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-477661074</v>
+      </c>
+      <c r="C78">
         <v>-428503635</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>-98623871</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>-92767612</v>
       </c>
-      <c r="E78">
+      <c r="G78">
         <v>-93322851</v>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>-19684351</v>
       </c>
-      <c r="I78">
+      <c r="K78">
         <v>-43076909</v>
       </c>
     </row>
@@ -7216,21 +8366,24 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>1321030807</v>
+      </c>
+      <c r="C101">
         <v>1418179757</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>1488586043</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>360758453</v>
       </c>
-      <c r="E101">
+      <c r="G101">
         <v>178191856</v>
       </c>
-      <c r="H101">
+      <c r="J101">
         <v>-20934216</v>
       </c>
-      <c r="I101">
+      <c r="K101">
         <v>10779707</v>
       </c>
     </row>
@@ -7249,12 +8402,15 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
+        <v>1321025779</v>
+      </c>
+      <c r="C104">
         <v>1320711229</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>1322549947</v>
       </c>
-      <c r="E104">
+      <c r="G104">
         <v>-76046</v>
       </c>
     </row>
@@ -7267,7 +8423,7 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="H106">
+      <c r="J106">
         <v>-18408566</v>
       </c>
     </row>
@@ -7275,16 +8431,16 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B107">
-        <v>30000000</v>
-      </c>
       <c r="C107">
         <v>30000000</v>
       </c>
-      <c r="E107">
+      <c r="D107">
+        <v>30000000</v>
+      </c>
+      <c r="G107">
         <v>0</v>
       </c>
-      <c r="I107">
+      <c r="K107">
         <v>22000000</v>
       </c>
     </row>
@@ -7298,21 +8454,24 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
+        <v>-15634890</v>
+      </c>
+      <c r="C109">
         <v>118283136</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>238564193</v>
       </c>
-      <c r="D109">
+      <c r="E109">
         <v>452580391</v>
       </c>
-      <c r="E109">
+      <c r="G109">
         <v>260484128</v>
       </c>
-      <c r="H109">
+      <c r="J109">
         <v>51147213</v>
       </c>
-      <c r="I109">
+      <c r="K109">
         <v>-2580974</v>
       </c>
     </row>
@@ -7355,16 +8514,16 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="B117">
-        <v>0</v>
-      </c>
       <c r="C117">
         <v>0</v>
       </c>
-      <c r="E117">
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="G117">
         <v>-18145052</v>
       </c>
-      <c r="H117">
+      <c r="J117">
         <v>-21675261</v>
       </c>
     </row>
@@ -7373,21 +8532,24 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-138558246</v>
+      </c>
+      <c r="C118">
         <v>-120416830</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>-130449439</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>-105242814</v>
       </c>
-      <c r="E118">
+      <c r="G118">
         <v>-65556831</v>
       </c>
-      <c r="H118">
+      <c r="J118">
         <v>-20130912</v>
       </c>
-      <c r="I118">
+      <c r="K118">
         <v>-8806015</v>
       </c>
     </row>
@@ -7396,21 +8558,24 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
+        <v>124198164</v>
+      </c>
+      <c r="C119">
         <v>69602222</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>27921342</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>13644036</v>
       </c>
-      <c r="E119">
+      <c r="G119">
         <v>1485657</v>
       </c>
-      <c r="H119">
+      <c r="J119">
         <v>593</v>
       </c>
-      <c r="I119">
+      <c r="K119">
         <v>1142</v>
       </c>
     </row>
@@ -7433,10 +8598,10 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="H123">
+      <c r="J123">
         <v>-11867283</v>
       </c>
-      <c r="I123">
+      <c r="K123">
         <v>165554</v>
       </c>
     </row>
@@ -7450,21 +8615,24 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>-32610709</v>
+      </c>
+      <c r="C125">
         <v>486490800</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>385187439</v>
       </c>
-      <c r="D125">
+      <c r="E125">
         <v>10232546</v>
       </c>
-      <c r="E125">
+      <c r="G125">
         <v>40433800</v>
       </c>
-      <c r="H125">
+      <c r="J125">
         <v>43941329</v>
       </c>
-      <c r="I125">
+      <c r="K125">
         <v>-3870826</v>
       </c>
     </row>
@@ -7473,21 +8641,24 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
+        <v>263598749</v>
+      </c>
+      <c r="C126">
         <v>141243243</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>105345944</v>
       </c>
-      <c r="D126">
+      <c r="E126">
         <v>80399990</v>
       </c>
-      <c r="E126">
+      <c r="G126">
         <v>51051049</v>
       </c>
-      <c r="H126">
+      <c r="J126">
         <v>-21455677</v>
       </c>
-      <c r="I126">
+      <c r="K126">
         <v>8491086</v>
       </c>
     </row>
@@ -7496,21 +8667,24 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>230988040</v>
+      </c>
+      <c r="C127">
         <v>627734043</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>490533383</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>90632536</v>
       </c>
-      <c r="E127">
+      <c r="G127">
         <v>91484849</v>
       </c>
-      <c r="H127">
+      <c r="J127">
         <v>22485652</v>
       </c>
-      <c r="I127">
+      <c r="K127">
         <v>4620260</v>
       </c>
     </row>
@@ -7519,12 +8693,15 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>120679477</v>
+        <v>748413520</v>
       </c>
       <c r="C128">
         <v>120679477</v>
       </c>
-      <c r="E128">
+      <c r="D128">
+        <v>120679477</v>
+      </c>
+      <c r="G128">
         <v>29194628</v>
       </c>
     </row>
@@ -7533,18 +8710,21 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>979401560</v>
+      </c>
+      <c r="C129">
         <v>748413520</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>611212860</v>
       </c>
-      <c r="E129">
+      <c r="G129">
         <v>120679477</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/DOFRB (TRY).xlsx
+++ b/data/DOFRB (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:I108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -413,6 +413,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -420,24 +421,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -451,24 +455,27 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
+        <v>501050883</v>
+      </c>
+      <c r="C3">
         <v>397904175</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>748413520</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>516010545</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>117905827</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>120679477</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>29194628</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>6708976</v>
       </c>
     </row>
@@ -482,21 +489,24 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
+        <v>391354269</v>
+      </c>
+      <c r="C5">
         <v>202701050</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>7286168</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>534116849</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>2337435</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>1012756</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>444517</v>
       </c>
     </row>
@@ -510,24 +520,27 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
+        <v>865638911</v>
+      </c>
+      <c r="C7">
         <v>647609240</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>564667465</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>590961781</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>440929382</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>347849858</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>99283950</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>81662318</v>
       </c>
     </row>
@@ -546,24 +559,27 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
+        <v>4371967</v>
+      </c>
+      <c r="C10">
         <v>13801726</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>3856413</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>4320152</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>1171797</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>1548311</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>3670090</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>2710876</v>
       </c>
     </row>
@@ -587,24 +603,27 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
+        <v>189831351</v>
+      </c>
+      <c r="C14">
         <v>155807092</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>285137876</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>182494193</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>188587026</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>183250747</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>122946935</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>18517674</v>
       </c>
     </row>
@@ -623,24 +642,27 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
+        <v>983806424</v>
+      </c>
+      <c r="C17">
         <v>773990952</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>717180804</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>453480800</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>267628894</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>259174235</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>144886018</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>9489964</v>
       </c>
     </row>
@@ -653,22 +675,19 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
       <c r="C19">
         <v>0</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>3153645</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>1851961</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>143803</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>95910</v>
       </c>
     </row>
@@ -682,24 +701,27 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
+        <v>140201775</v>
+      </c>
+      <c r="C21">
         <v>97392169</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>88162783</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>22229174</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>3775018</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>1234881</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>2786326</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>2222577</v>
       </c>
     </row>
@@ -707,7 +729,7 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>1930468853</v>
       </c>
     </row>
@@ -721,24 +743,27 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
+        <v>3076255580</v>
+      </c>
+      <c r="C24">
         <v>2289206404</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>2414705029</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>2306767139</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>1024187340</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>914894068</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>403308374</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>121312385</v>
       </c>
     </row>
@@ -817,24 +842,27 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
+        <v>582727752</v>
+      </c>
+      <c r="C39">
         <v>405012657</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>363064136</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>501657494</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>44724257</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>40510216</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>20556018</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>33376254</v>
       </c>
     </row>
@@ -843,24 +871,27 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
+        <v>109763294</v>
+      </c>
+      <c r="C40">
         <v>533547801</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>516748234</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>55459767</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>482842891</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>433953864</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>365483555</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>234667870</v>
       </c>
     </row>
@@ -869,24 +900,27 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
+        <v>245387999</v>
+      </c>
+      <c r="C41">
         <v>206057037</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>182614672</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>139535609</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>122792475</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>86305492</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>33673650</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>22604133</v>
       </c>
     </row>
@@ -894,13 +928,10 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>978668</v>
       </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="H42">
+      <c r="I42">
         <v>4990123</v>
       </c>
     </row>
@@ -909,12 +940,15 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B43">
+        <v>590847</v>
+      </c>
+      <c r="C43">
         <v>0</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>3118996</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>0</v>
       </c>
     </row>
@@ -938,24 +972,27 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
+        <v>938469892</v>
+      </c>
+      <c r="C47">
         <v>1145596163</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>1065546038</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>696652870</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>650359623</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>560769572</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>419713223</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>295638380</v>
       </c>
     </row>
@@ -964,24 +1001,27 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
+        <v>4014725472</v>
+      </c>
+      <c r="C48">
         <v>3434802567</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>3480251067</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>3003420009</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>1674546963</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>1475663640</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>823021597</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>416950765</v>
       </c>
     </row>
@@ -995,24 +1035,27 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
+        <v>865982352</v>
+      </c>
+      <c r="C50">
         <v>333762110</v>
       </c>
-      <c r="C50">
-        <v>332799475</v>
-      </c>
       <c r="D50">
+        <v>347984762</v>
+      </c>
+      <c r="E50">
         <v>354428682</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>522152940</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>234812834</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>31166046</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>15556712</v>
       </c>
     </row>
@@ -1020,16 +1063,13 @@
       <c r="A51" t="str">
         <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <v>13143954</v>
       </c>
-      <c r="C51">
-        <v>15185287</v>
-      </c>
-      <c r="D51">
+      <c r="E51">
         <v>14939875</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>13124871</v>
       </c>
     </row>
@@ -1038,24 +1078,27 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
+        <v>91013409</v>
+      </c>
+      <c r="C52">
         <v>221383345</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>208115059</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>108810507</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>37680604</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>127725812</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>35376662</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>37412850</v>
       </c>
     </row>
@@ -1069,24 +1112,27 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
+        <v>62448802</v>
+      </c>
+      <c r="C54">
         <v>52662965</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>32659778</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>19784673</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>31424561</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>13872462</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>5744659</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>1858741</v>
       </c>
     </row>
@@ -1095,24 +1141,27 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
+        <v>481769</v>
+      </c>
+      <c r="C55">
         <v>0</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>735918</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>63173</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>45749657</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>39504304</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>3814896</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>4738018</v>
       </c>
     </row>
@@ -1141,24 +1190,27 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
+        <v>394576900</v>
+      </c>
+      <c r="C60">
         <v>80179934</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>242647453</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>120885733</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>71783211</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>161158999</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>148433940</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>26846317</v>
       </c>
     </row>
@@ -1166,13 +1218,13 @@
       <c r="A61" t="str">
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
-      <c r="B61">
+      <c r="C61">
         <v>0</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>647184</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>0</v>
       </c>
     </row>
@@ -1181,24 +1233,27 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
+        <v>8517302</v>
+      </c>
+      <c r="C62">
         <v>8056471</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>5634424</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>2340361</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>2139804</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>2416736</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>1064897</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>253227</v>
       </c>
     </row>
@@ -1222,24 +1277,27 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
+        <v>1423020534</v>
+      </c>
+      <c r="C66">
         <v>709188779</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>838424578</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>621253004</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>710930777</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>592616018</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>225601100</v>
       </c>
-      <c r="H66">
+      <c r="I66">
         <v>86665865</v>
       </c>
     </row>
@@ -1253,24 +1311,27 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
+        <v>246057400</v>
+      </c>
+      <c r="C68">
         <v>69333301</v>
       </c>
-      <c r="C68">
-        <v>79754743</v>
-      </c>
       <c r="D68">
+        <v>553196943</v>
+      </c>
+      <c r="E68">
         <v>116176994</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>556518003</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>84820756</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>422091801</v>
       </c>
-      <c r="H68">
+      <c r="I68">
         <v>251732182</v>
       </c>
     </row>
@@ -1278,16 +1339,13 @@
       <c r="A69" t="str">
         <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
       </c>
-      <c r="B69">
+      <c r="C69">
         <v>487750738</v>
       </c>
-      <c r="C69">
-        <v>473442200</v>
-      </c>
-      <c r="D69">
+      <c r="E69">
         <v>460587636</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>396167992</v>
       </c>
     </row>
@@ -1300,10 +1358,10 @@
       <c r="A71" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
       </c>
-      <c r="D71">
+      <c r="E71">
         <v>0</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>58570096</v>
       </c>
     </row>
@@ -1352,24 +1410,27 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
+        <v>6351438</v>
+      </c>
+      <c r="C80">
         <v>8971076</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>5136343</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>3347440</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>2220756</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>3574212</v>
       </c>
-      <c r="G80">
+      <c r="H80">
         <v>2775816</v>
       </c>
-      <c r="H80">
+      <c r="I80">
         <v>163483</v>
       </c>
     </row>
@@ -1382,11 +1443,8 @@
       <c r="A82" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
-      <c r="B82">
+      <c r="C82">
         <v>1218273</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1399,24 +1457,27 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
+        <v>252408838</v>
+      </c>
+      <c r="C84">
         <v>567273388</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>558333286</v>
       </c>
-      <c r="D84">
+      <c r="E84">
         <v>580112070</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>558738759</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>543133056</v>
       </c>
-      <c r="G84">
+      <c r="H84">
         <v>424867617</v>
       </c>
-      <c r="H84">
+      <c r="I84">
         <v>251895665</v>
       </c>
     </row>
@@ -1430,24 +1491,27 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
+        <v>2324426885</v>
+      </c>
+      <c r="C86">
         <v>2142280161</v>
       </c>
-      <c r="C86">
+      <c r="D86">
         <v>2066357708</v>
       </c>
-      <c r="D86">
+      <c r="E86">
         <v>1784506317</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>389722551</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>329451911</v>
       </c>
-      <c r="G86">
+      <c r="H86">
         <v>172168535</v>
       </c>
-      <c r="H86">
+      <c r="I86">
         <v>78389235</v>
       </c>
     </row>
@@ -1465,15 +1529,18 @@
         <v>155000000</v>
       </c>
       <c r="E87">
-        <v>125000000</v>
+        <v>155000000</v>
       </c>
       <c r="F87">
         <v>125000000</v>
       </c>
       <c r="G87">
+        <v>125000000</v>
+      </c>
+      <c r="H87">
         <v>27000000</v>
       </c>
-      <c r="H87">
+      <c r="I87">
         <v>27000000</v>
       </c>
     </row>
@@ -1520,7 +1587,10 @@
       <c r="D94">
         <v>1320000000</v>
       </c>
-      <c r="F94">
+      <c r="E94">
+        <v>1320000000</v>
+      </c>
+      <c r="G94">
         <v>0</v>
       </c>
     </row>
@@ -1539,24 +1609,27 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
+        <v>1372277</v>
+      </c>
+      <c r="C97">
         <v>120802</v>
       </c>
-      <c r="C97">
+      <c r="D97">
         <v>-134193</v>
       </c>
-      <c r="D97">
+      <c r="E97">
         <v>1992575</v>
       </c>
-      <c r="E97">
+      <c r="F97">
         <v>1856015</v>
       </c>
-      <c r="F97">
+      <c r="G97">
         <v>3399462</v>
       </c>
-      <c r="G97">
+      <c r="H97">
         <v>-769376</v>
       </c>
-      <c r="H97">
+      <c r="I97">
         <v>12285709</v>
       </c>
     </row>
@@ -1565,12 +1638,15 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B98">
+        <v>329764111</v>
+      </c>
+      <c r="C98">
         <v>214254585</v>
       </c>
-      <c r="C98">
+      <c r="D98">
         <v>145488127</v>
       </c>
-      <c r="D98">
+      <c r="E98">
         <v>69530755</v>
       </c>
     </row>
@@ -1582,21 +1658,24 @@
         <v>12010117</v>
       </c>
       <c r="C99">
-        <v>4601256</v>
+        <v>12010117</v>
       </c>
       <c r="D99">
         <v>4601256</v>
       </c>
       <c r="E99">
+        <v>4601256</v>
+      </c>
+      <c r="F99">
         <v>4601269</v>
       </c>
-      <c r="F99">
+      <c r="G99">
         <v>728160</v>
       </c>
-      <c r="G99">
+      <c r="H99">
         <v>728173</v>
       </c>
-      <c r="H99">
+      <c r="I99">
         <v>284391</v>
       </c>
     </row>
@@ -1604,13 +1683,13 @@
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="E100">
+      <c r="F100">
         <v>47917264</v>
       </c>
-      <c r="G100">
+      <c r="H100">
         <v>-6746106</v>
       </c>
-      <c r="H100">
+      <c r="I100">
         <v>14709585</v>
       </c>
     </row>
@@ -1632,7 +1711,7 @@
         <v>433993657</v>
       </c>
       <c r="C103">
-        <v>196451193</v>
+        <v>433993657</v>
       </c>
       <c r="D103">
         <v>196451193</v>
@@ -1641,12 +1720,15 @@
         <v>196451193</v>
       </c>
       <c r="F103">
+        <v>196451193</v>
+      </c>
+      <c r="G103">
         <v>35810792</v>
       </c>
-      <c r="G103">
+      <c r="H103">
         <v>-15230257</v>
       </c>
-      <c r="H103">
+      <c r="I103">
         <v>7017301</v>
       </c>
     </row>
@@ -1655,24 +1737,27 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
+        <v>72286723</v>
+      </c>
+      <c r="C104">
         <v>6901000</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>244951325</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>36930538</v>
       </c>
-      <c r="E104">
+      <c r="F104">
         <v>13896810</v>
       </c>
-      <c r="F104">
+      <c r="G104">
         <v>164513497</v>
       </c>
-      <c r="G104">
+      <c r="H104">
         <v>167186101</v>
       </c>
-      <c r="H104">
+      <c r="I104">
         <v>17092249</v>
       </c>
     </row>
@@ -1681,21 +1766,24 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B105">
+        <v>14869215</v>
+      </c>
+      <c r="C105">
         <v>16060239</v>
       </c>
-      <c r="C105">
+      <c r="D105">
         <v>17135495</v>
       </c>
-      <c r="D105">
+      <c r="E105">
         <v>17548618</v>
       </c>
-      <c r="E105">
+      <c r="F105">
         <v>15154876</v>
       </c>
-      <c r="F105">
+      <c r="G105">
         <v>10462655</v>
       </c>
-      <c r="G105">
+      <c r="H105">
         <v>384345</v>
       </c>
     </row>
@@ -1704,24 +1792,27 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
+        <v>2339296100</v>
+      </c>
+      <c r="C106">
         <v>2158340400</v>
       </c>
-      <c r="C106">
+      <c r="D106">
         <v>2083493203</v>
       </c>
-      <c r="D106">
+      <c r="E106">
         <v>1802054935</v>
       </c>
-      <c r="E106">
+      <c r="F106">
         <v>404877427</v>
       </c>
-      <c r="F106">
+      <c r="G106">
         <v>339914566</v>
       </c>
-      <c r="G106">
+      <c r="H106">
         <v>172552880</v>
       </c>
-      <c r="H106">
+      <c r="I106">
         <v>78389235</v>
       </c>
     </row>
@@ -1730,24 +1821,27 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
+        <v>4014725472</v>
+      </c>
+      <c r="C107">
         <v>3434802567</v>
       </c>
-      <c r="C107">
+      <c r="D107">
         <v>3480251067</v>
       </c>
-      <c r="D107">
+      <c r="E107">
         <v>3003420009</v>
       </c>
-      <c r="E107">
+      <c r="F107">
         <v>1674546963</v>
       </c>
-      <c r="F107">
+      <c r="G107">
         <v>1475663640</v>
       </c>
-      <c r="G107">
+      <c r="H107">
         <v>823021597</v>
       </c>
-      <c r="H107">
+      <c r="I107">
         <v>416950765</v>
       </c>
     </row>
@@ -1756,22 +1850,25 @@
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
       <c r="C108">
+        <v>1089018977</v>
+      </c>
+      <c r="D108">
         <v>450095535</v>
       </c>
-      <c r="D108">
+      <c r="E108">
         <v>182024668</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:L50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1784,6 +1881,7 @@
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
+    <col min="12" max="12" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1791,33 +1889,36 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1831,33 +1932,36 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>452350469</v>
+      </c>
+      <c r="C3">
         <v>197927592</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1011968695</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>491822469</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>267022962</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>113767057</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>628321226</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>254023160</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>157852482</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>422892272</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>156342926</v>
       </c>
     </row>
@@ -1870,13 +1974,13 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>146595738</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>32775707</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>98646262</v>
       </c>
     </row>
@@ -1884,13 +1988,13 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>863879783</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>456660229</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>547562429</v>
       </c>
     </row>
@@ -1899,33 +2003,36 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-172666830</v>
+      </c>
+      <c r="C7">
         <v>-63563455</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-338030467</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-181276792</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-98429388</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>-39868049</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-212705658</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>-125650045</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>-81685453</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>-130783032</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>-83686976</v>
       </c>
     </row>
@@ -1934,33 +2041,36 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>279683639</v>
+      </c>
+      <c r="C8">
         <v>134364137</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>673938228</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>310545677</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>168593574</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>73899008</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>415615568</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>128373115</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>76167029</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>292109240</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>72655950</v>
       </c>
     </row>
@@ -1989,33 +2099,36 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>279683639</v>
+      </c>
+      <c r="C13">
         <v>134364137</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>673938228</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>310545677</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>168593574</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>73899008</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>415615568</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>128373115</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>76167029</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>292109240</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>72655950</v>
       </c>
     </row>
@@ -2025,33 +2138,36 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-137306728</v>
+      </c>
+      <c r="C15">
         <v>-79966378</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-267134773</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-114836823</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>-66737249</v>
       </c>
-      <c r="F15">
-        <v>-13483238</v>
-      </c>
       <c r="G15">
+        <v>-39483238</v>
+      </c>
+      <c r="H15">
         <v>-79849733</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>-39044103</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>-24578203</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>-40552138</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>-19204247</v>
       </c>
     </row>
@@ -2060,33 +2176,36 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-81451386</v>
+      </c>
+      <c r="C16">
         <v>-47263904</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-80387044</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-44854991</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-30805089</v>
       </c>
-      <c r="F16">
-        <v>-1524530</v>
-      </c>
       <c r="G16">
+        <v>-15524530</v>
+      </c>
+      <c r="H16">
         <v>-39201093</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-24097951</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>-13891744</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>-21896767</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>-10639251</v>
       </c>
     </row>
@@ -2095,33 +2214,36 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-28478003</v>
+      </c>
+      <c r="C17">
         <v>-14436129</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-37603639</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>-25786217</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>-15907919</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>-7012932</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>-24577856</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>-14056343</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>-8476066</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>-11346004</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>-4515212</v>
       </c>
     </row>
@@ -2130,33 +2252,36 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>39544073</v>
+      </c>
+      <c r="C18">
         <v>3733341</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>23792181</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>40602333</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>17862530</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>8636218</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>30502172</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>22538092</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>17102048</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>19393593</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>14131630</v>
       </c>
     </row>
@@ -2165,33 +2290,36 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-28718445</v>
+        <v>-32279020</v>
       </c>
       <c r="C19">
+        <v>-28718444</v>
+      </c>
+      <c r="D19">
         <v>-57912286</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-68780795</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>-5718189</v>
       </c>
-      <c r="F19">
-        <v>-45618652</v>
-      </c>
       <c r="G19">
+        <v>-5618652</v>
+      </c>
+      <c r="H19">
         <v>-64088224</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>-22596758</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>-17415270</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>-41825078</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>-18726791</v>
       </c>
     </row>
@@ -2205,33 +2333,36 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>-32287378</v>
+        <v>39712575</v>
       </c>
       <c r="C21">
+        <v>-32287377</v>
+      </c>
+      <c r="D21">
         <v>254692667</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>96889184</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>67287658</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>14895874</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>238400834</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>51116052</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>28907794</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>195882846</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>33702079</v>
       </c>
     </row>
@@ -2251,19 +2382,19 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>26458579</v>
+      </c>
+      <c r="C25">
         <v>10482138</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>45446148</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>19320082</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>3713582</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -2271,10 +2402,13 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="J25">
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>1431413</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>457089</v>
       </c>
     </row>
@@ -2282,31 +2416,25 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
       <c r="D26">
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="E26">
         <v>0</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>-890441</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>0</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>-903639</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>-12202369</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>-8283522</v>
       </c>
     </row>
@@ -2345,33 +2473,36 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>-21805240</v>
+        <v>66171154</v>
       </c>
       <c r="C33">
+        <v>-21805239</v>
+      </c>
+      <c r="D33">
         <v>300138815</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>116209266</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>71001240</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>14895874</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>237510393</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>51116052</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>28004155</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>185111890</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>25875646</v>
       </c>
     </row>
@@ -2381,33 +2512,36 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>82911333</v>
+      </c>
+      <c r="C35">
         <v>60385379</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>69602222</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>27338661</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>12856498</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>5789437</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>1485657</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>902976</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>698119</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>593</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>1142</v>
       </c>
     </row>
@@ -2416,33 +2550,36 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-76533908</v>
+      </c>
+      <c r="C36">
         <v>-28304263</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-120416830</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-99531427</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>-65268707</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>-10162847</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>-65556831</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>-34638819</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>-25582724</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>-20196310</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>-8817366</v>
       </c>
     </row>
@@ -2456,33 +2593,36 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>10275876</v>
+        <v>72548579</v>
       </c>
       <c r="C38">
+        <v>10275877</v>
+      </c>
+      <c r="D38">
         <v>249324207</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>44016500</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>18589031</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>10522464</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>173439219</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>17380209</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>3119550</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>164916173</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>17059422</v>
       </c>
     </row>
@@ -2492,27 +2632,27 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>-2528136</v>
+      </c>
+      <c r="C40">
         <v>-4450132</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>2299958</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>0</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>0</v>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
+      <c r="I40">
         <v>-426260</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>2160710</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>32827</v>
       </c>
     </row>
@@ -2520,25 +2660,19 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="B41">
+      <c r="D41">
+        <v>-819038</v>
+      </c>
+      <c r="E41">
         <v>0</v>
       </c>
-      <c r="C41">
-        <v>-819038</v>
-      </c>
-      <c r="D41">
+      <c r="H41">
         <v>0</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
+      <c r="I41">
         <v>-426260</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>-11863</v>
       </c>
     </row>
@@ -2547,24 +2681,24 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>-2528136</v>
+      </c>
+      <c r="C42">
         <v>-4450132</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>3118996</v>
       </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42">
+      <c r="E42">
         <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
-      <c r="K42">
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="L42">
         <v>44690</v>
       </c>
     </row>
@@ -2573,45 +2707,42 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>5825744</v>
+        <v>70020443</v>
       </c>
       <c r="C43">
+        <v>5825745</v>
+      </c>
+      <c r="D43">
         <v>251624165</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>44016500</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>18589031</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>10522464</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>173439219</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>16953949</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>3119550</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>167076883</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>17092249</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
       </c>
     </row>
     <row r="45"/>
@@ -2620,33 +2751,36 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>5825744</v>
+        <v>70020443</v>
       </c>
       <c r="C46">
+        <v>5825745</v>
+      </c>
+      <c r="D46">
         <v>251624165</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>44016500</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>18589031</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>10522464</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>173439219</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>16953949</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>3119550</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>167076883</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>17092249</v>
       </c>
     </row>
@@ -2655,30 +2789,33 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
+        <v>-2266280</v>
+      </c>
+      <c r="C47">
         <v>-1075256</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>6672840</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>7085962</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>4692221</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>-688554</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>8925722</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>-673996</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>-593350</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>-109218</v>
       </c>
     </row>
@@ -2687,33 +2824,36 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>6901000</v>
+        <v>72286723</v>
       </c>
       <c r="C48">
+        <v>6901001</v>
+      </c>
+      <c r="D48">
         <v>244951325</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>36930538</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>13896810</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>11211018</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>164513497</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>17627945</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>3712900</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>167186101</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>17092249</v>
       </c>
     </row>
@@ -2723,46 +2863,49 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>59638987</v>
+      </c>
+      <c r="C50">
         <v>27484584</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>65840618</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>41967651</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>24192705</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>11372131</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>32234100</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>19259951</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>14124351</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>20585442</v>
       </c>
-      <c r="K50">
+      <c r="L50">
         <v>11926139</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:L50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2775,6 +2918,7 @@
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
+    <col min="12" max="12" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2782,33 +2926,36 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2822,24 +2969,27 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>254422877</v>
+      </c>
+      <c r="C3">
         <v>197927592</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>520146226</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>224799507</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>153255905</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>113767057</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>374298066</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>96170678</v>
       </c>
     </row>
@@ -2852,7 +3002,7 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>113820031</v>
       </c>
     </row>
@@ -2860,7 +3010,7 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>407219554</v>
       </c>
     </row>
@@ -2869,24 +3019,27 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-109103375</v>
+      </c>
+      <c r="C7">
         <v>-63563455</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-156753675</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-82847404</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-58561339</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>-39868049</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-87055613</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>-43964592</v>
       </c>
     </row>
@@ -2895,24 +3048,27 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>145319502</v>
+      </c>
+      <c r="C8">
         <v>134364137</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>363392551</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>141952103</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>94694566</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>73899008</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>287242453</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>52206086</v>
       </c>
     </row>
@@ -2941,24 +3097,27 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>145319502</v>
+      </c>
+      <c r="C13">
         <v>134364137</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>363392551</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>141952103</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>94694566</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>73899008</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>287242453</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>52206086</v>
       </c>
     </row>
@@ -2968,24 +3127,27 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-57340350</v>
+      </c>
+      <c r="C15">
         <v>-79966378</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-152297950</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-48099574</v>
       </c>
-      <c r="E15">
-        <v>-53254011</v>
-      </c>
       <c r="F15">
-        <v>-13483238</v>
+        <v>-27254011</v>
       </c>
       <c r="G15">
+        <v>-39483238</v>
+      </c>
+      <c r="H15">
         <v>-40805630</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>-14465900</v>
       </c>
     </row>
@@ -2994,24 +3156,27 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-34187482</v>
+      </c>
+      <c r="C16">
         <v>-47263904</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>-35532053</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-14049902</v>
       </c>
-      <c r="E16">
-        <v>-29280559</v>
-      </c>
       <c r="F16">
-        <v>-1524530</v>
+        <v>-15280559</v>
       </c>
       <c r="G16">
+        <v>-15524530</v>
+      </c>
+      <c r="H16">
         <v>-15103142</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>-10206207</v>
       </c>
     </row>
@@ -3020,24 +3185,27 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-14041874</v>
+      </c>
+      <c r="C17">
         <v>-14436129</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-11817422</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>-9878298</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>-8894987</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>-7012932</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>-10521513</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>-5580277</v>
       </c>
     </row>
@@ -3046,24 +3214,27 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>35810732</v>
+      </c>
+      <c r="C18">
         <v>3733341</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>-16810152</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>22739803</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>9226312</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>8636218</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>7964080</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>5436044</v>
       </c>
     </row>
@@ -3072,24 +3243,27 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-28718445</v>
+        <v>-3560576</v>
       </c>
       <c r="C19">
+        <v>-28718444</v>
+      </c>
+      <c r="D19">
         <v>10868509</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-63062606</v>
       </c>
-      <c r="E19">
-        <v>39900463</v>
-      </c>
       <c r="F19">
-        <v>-45618652</v>
+        <v>-99537</v>
       </c>
       <c r="G19">
+        <v>-5618652</v>
+      </c>
+      <c r="H19">
         <v>-41491466</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>-5181488</v>
       </c>
     </row>
@@ -3103,24 +3277,27 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>-32287378</v>
+        <v>71999952</v>
       </c>
       <c r="C21">
+        <v>-32287377</v>
+      </c>
+      <c r="D21">
         <v>157803483</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>29601526</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>52391784</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>14895874</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>187284782</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>22208258</v>
       </c>
     </row>
@@ -3140,21 +3317,24 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>15976441</v>
+      </c>
+      <c r="C25">
         <v>10482138</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>26126066</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>15606500</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>3713582</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0</v>
       </c>
     </row>
@@ -3162,19 +3342,13 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="B26">
+      <c r="D26">
         <v>0</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
+      <c r="H26">
         <v>-890441</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>903639</v>
       </c>
     </row>
@@ -3213,24 +3387,27 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>-21805240</v>
+        <v>87976393</v>
       </c>
       <c r="C33">
+        <v>-21805239</v>
+      </c>
+      <c r="D33">
         <v>183929549</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>45208026</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>56105366</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>14895874</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>186394341</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>23111897</v>
       </c>
     </row>
@@ -3240,24 +3417,27 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>22525954</v>
+      </c>
+      <c r="C35">
         <v>60385379</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>42263561</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>14482163</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>7067061</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>5789437</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>582681</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>204857</v>
       </c>
     </row>
@@ -3266,24 +3446,27 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-48229645</v>
+      </c>
+      <c r="C36">
         <v>-28304263</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-20885403</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-34262720</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>-55105860</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>-10162847</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>-30918012</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>-9056095</v>
       </c>
     </row>
@@ -3297,24 +3480,27 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>10275876</v>
+        <v>62272702</v>
       </c>
       <c r="C38">
+        <v>10275877</v>
+      </c>
+      <c r="D38">
         <v>205307707</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>25427469</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>8066567</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>10522464</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>156059010</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>14260659</v>
       </c>
     </row>
@@ -3324,15 +3510,15 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>1921996</v>
+      </c>
+      <c r="C40">
         <v>-4450132</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>2299958</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
+      <c r="H40">
         <v>426260</v>
       </c>
     </row>
@@ -3340,16 +3526,10 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
+      <c r="D41">
         <v>-819038</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
+      <c r="H41">
         <v>426260</v>
       </c>
     </row>
@@ -3358,15 +3538,15 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>1921996</v>
+      </c>
+      <c r="C42">
         <v>-4450132</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>3118996</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42">
+      <c r="H42">
         <v>0</v>
       </c>
     </row>
@@ -3375,36 +3555,33 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>5825744</v>
+        <v>64194698</v>
       </c>
       <c r="C43">
+        <v>5825745</v>
+      </c>
+      <c r="D43">
         <v>207607665</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>25427469</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>8066567</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>10522464</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>156485270</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>13834399</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
       </c>
     </row>
     <row r="45"/>
@@ -3413,24 +3590,27 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>5825744</v>
+        <v>64194698</v>
       </c>
       <c r="C46">
+        <v>5825745</v>
+      </c>
+      <c r="D46">
         <v>207607665</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>25427469</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>8066567</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>10522464</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>156485270</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>13834399</v>
       </c>
     </row>
@@ -3439,24 +3619,27 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
+        <v>-1191024</v>
+      </c>
+      <c r="C47">
         <v>-1075256</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>-413122</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>2393741</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>5380775</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>-688554</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>9599718</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>-80646</v>
       </c>
     </row>
@@ -3465,24 +3648,27 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>6901000</v>
+        <v>65385722</v>
       </c>
       <c r="C48">
+        <v>6901001</v>
+      </c>
+      <c r="D48">
         <v>208020787</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>23033728</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>2685792</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>11211018</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>146885552</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>13915045</v>
       </c>
     </row>
@@ -3492,37 +3678,40 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>32154403</v>
+      </c>
+      <c r="C50">
         <v>27484584</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>23872967</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>17774946</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>12820574</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>11372131</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>12974149</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>5135600</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:L50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3535,6 +3724,7 @@
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
+    <col min="12" max="12" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3542,33 +3732,36 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3582,24 +3775,27 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>1197296202</v>
+      </c>
+      <c r="C3">
         <v>1096129230</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1011968695</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>866120535</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>737491706</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>628321226</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>422892272</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>156342926</v>
       </c>
     </row>
@@ -3612,10 +3808,10 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>146595738</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>98646262</v>
       </c>
     </row>
@@ -3623,10 +3819,10 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>863879783</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>547562429</v>
       </c>
     </row>
@@ -3635,24 +3831,27 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-412267909</v>
+      </c>
+      <c r="C7">
         <v>-361725873</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-338030467</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-268332405</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-229449593</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-212705658</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>-130783032</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>-83686976</v>
       </c>
     </row>
@@ -3661,24 +3860,27 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>785028293</v>
+      </c>
+      <c r="C8">
         <v>734403357</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>673938228</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>597788130</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>508042113</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>415615568</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>292109240</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>72655950</v>
       </c>
     </row>
@@ -3707,24 +3909,27 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>785028293</v>
+      </c>
+      <c r="C13">
         <v>734403357</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>673938228</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>597788130</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>508042113</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>415615568</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>292109240</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>72655950</v>
       </c>
     </row>
@@ -3734,24 +3939,27 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-333617913</v>
+        <v>-337704252</v>
       </c>
       <c r="C15">
+        <v>-307617913</v>
+      </c>
+      <c r="D15">
         <v>-267134773</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-155642453</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>-122008779</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>-79849733</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>-40552138</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>-19204247</v>
       </c>
     </row>
@@ -3760,24 +3968,27 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-126126418</v>
+        <v>-131033341</v>
       </c>
       <c r="C16">
+        <v>-112126418</v>
+      </c>
+      <c r="D16">
         <v>-80387044</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>-59958133</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>-56114438</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>-39201093</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>-21896767</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>-10639251</v>
       </c>
     </row>
@@ -3786,24 +3997,27 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-50173723</v>
+      </c>
+      <c r="C17">
         <v>-45026836</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-37603639</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>-36307730</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>-32009709</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>-24577856</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>-11346004</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>-4515212</v>
       </c>
     </row>
@@ -3812,24 +4026,27 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>45473724</v>
+      </c>
+      <c r="C18">
         <v>18889304</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>23792181</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>48566413</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>31262654</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>30502172</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>19393593</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>14131630</v>
       </c>
     </row>
@@ -3838,24 +4055,27 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-41012079</v>
+        <v>-84473117</v>
       </c>
       <c r="C19">
+        <v>-81012078</v>
+      </c>
+      <c r="D19">
         <v>-57912286</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>-110272261</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>-52391143</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>-64088224</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>-41825078</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>-18726791</v>
       </c>
     </row>
@@ -3869,24 +4089,27 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>207509415</v>
+        <v>227117584</v>
       </c>
       <c r="C21">
+        <v>207509416</v>
+      </c>
+      <c r="D21">
         <v>254692667</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>284173966</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>276780698</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>238400834</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>195882846</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>33702079</v>
       </c>
     </row>
@@ -3906,21 +4129,24 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>68191145</v>
+      </c>
+      <c r="C25">
         <v>55928286</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>45446148</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>19320082</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>1431413</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>457089</v>
       </c>
     </row>
@@ -3928,22 +4154,19 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="B26">
+      <c r="D26">
         <v>0</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
+      <c r="E26">
         <v>-890441</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>-890441</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>-12202369</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>-8283522</v>
       </c>
     </row>
@@ -3982,24 +4205,27 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>263437701</v>
+        <v>295308729</v>
       </c>
       <c r="C33">
+        <v>263437702</v>
+      </c>
+      <c r="D33">
         <v>300138815</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>302603607</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>280507478</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>237510393</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>185111890</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>25875646</v>
       </c>
     </row>
@@ -4009,24 +4235,27 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>139657057</v>
+      </c>
+      <c r="C35">
         <v>124198164</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>69602222</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>27921342</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>13644036</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>1485657</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>593</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>1142</v>
       </c>
     </row>
@@ -4035,24 +4264,27 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-131682031</v>
+      </c>
+      <c r="C36">
         <v>-138558246</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-120416830</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>-130449439</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>-105242814</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>-65556831</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>-20196310</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>-8817366</v>
       </c>
     </row>
@@ -4066,24 +4298,27 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>249077619</v>
+        <v>303283755</v>
       </c>
       <c r="C38">
+        <v>249077620</v>
+      </c>
+      <c r="D38">
         <v>249324207</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>200075510</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>188908700</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>173439219</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>164916173</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>17059422</v>
       </c>
     </row>
@@ -4092,22 +4327,19 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
-      <c r="B40">
-        <v>-2150174</v>
-      </c>
-      <c r="C40">
+      <c r="D40">
         <v>2299958</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>426260</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>0</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>2160710</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>32827</v>
       </c>
     </row>
@@ -4115,19 +4347,16 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="B41">
+      <c r="D41">
         <v>-819038</v>
       </c>
-      <c r="C41">
-        <v>-819038</v>
-      </c>
-      <c r="D41">
+      <c r="E41">
         <v>426260</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>0</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>-11863</v>
       </c>
     </row>
@@ -4135,19 +4364,16 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
-      <c r="B42">
-        <v>-1331136</v>
-      </c>
-      <c r="C42">
+      <c r="D42">
         <v>3118996</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>0</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>0</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>44690</v>
       </c>
     </row>
@@ -4156,24 +4382,27 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>246927445</v>
+        <v>303055577</v>
       </c>
       <c r="C43">
+        <v>246927446</v>
+      </c>
+      <c r="D43">
         <v>251624165</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>200501770</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>188908700</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>173439219</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>167076883</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>17092249</v>
       </c>
     </row>
@@ -4188,24 +4417,27 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>246927445</v>
+        <v>303055577</v>
       </c>
       <c r="C46">
+        <v>246927446</v>
+      </c>
+      <c r="D46">
         <v>251624165</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>200501770</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>188908700</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>173439219</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>167076883</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>17092249</v>
       </c>
     </row>
@@ -4214,21 +4446,24 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
+        <v>-285661</v>
+      </c>
+      <c r="C47">
         <v>6286138</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>6672840</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>16685680</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>14211293</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>8925722</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>-109218</v>
       </c>
     </row>
@@ -4237,24 +4472,27 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>240641307</v>
+        <v>303341238</v>
       </c>
       <c r="C48">
+        <v>240641308</v>
+      </c>
+      <c r="D48">
         <v>244951325</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>183816090</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>174697407</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>164513497</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>167186101</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>17092249</v>
       </c>
     </row>
@@ -4264,37 +4502,40 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>101286900</v>
+      </c>
+      <c r="C50">
         <v>81953071</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>65840618</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>54941800</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>42302454</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>32234100</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>20585442</v>
       </c>
-      <c r="K50">
+      <c r="L50">
         <v>11926139</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:L129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4307,6 +4548,7 @@
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
+    <col min="12" max="12" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4314,33 +4556,36 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -4354,33 +4599,36 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>-365685421</v>
+      </c>
+      <c r="C3">
         <v>-469115735</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>-503185322</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>-1029328262</v>
       </c>
-      <c r="E3">
-        <v>-194359396</v>
-      </c>
       <c r="F3">
+        <v>-186693966</v>
+      </c>
+      <c r="G3">
         <v>-96320615</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>-48088078</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>-77778337</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>25195672</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>58558396</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>12848534</v>
       </c>
     </row>
@@ -4389,33 +4637,36 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>72286723</v>
+      </c>
+      <c r="C4">
         <v>6901000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>244951325</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>36930538</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>13896810</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>11211018</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>164513497</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>17627945</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>3712900</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>167186101</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>17092249</v>
       </c>
     </row>
@@ -4424,21 +4675,27 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>21341638</v>
+      </c>
+      <c r="C5">
         <v>-315830805</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-16978346</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>14250618</v>
       </c>
       <c r="F5">
+        <v>68099681</v>
+      </c>
+      <c r="G5">
         <v>7337228</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>98657147</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>2945839</v>
       </c>
     </row>
@@ -4447,33 +4704,36 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>59638987</v>
+      </c>
+      <c r="C6">
         <v>27484584</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>65840618</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>41967651</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>24192705</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>11372131</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>32234100</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>19259951</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>14124351</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>20585442</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>11926139</v>
       </c>
     </row>
@@ -4482,33 +4742,36 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
+        <v>-336269</v>
+      </c>
+      <c r="C7">
         <v>-320540</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-66325</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-54581</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-39105</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>-21791</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-62023</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>-49498</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>21380</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>-391852</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>-136354</v>
       </c>
     </row>
@@ -4517,21 +4780,27 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>3361623</v>
+      </c>
+      <c r="C8">
         <v>5607180</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>5462188</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1589088</v>
       </c>
       <c r="F8">
+        <v>-1280942</v>
+      </c>
+      <c r="G8">
         <v>97058</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1388032</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>3839795</v>
       </c>
     </row>
@@ -4555,33 +4824,36 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>-6377425</v>
+      </c>
+      <c r="C12">
         <v>-32081116</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>50814608</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>72192766</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>52330717</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>4373410</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>64071174</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>33735843</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>24873081</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>20130319</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>8804874</v>
       </c>
     </row>
@@ -4600,33 +4872,36 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>-11014835</v>
+      </c>
+      <c r="C15">
         <v>-125556163</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-136729477</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-91649780</v>
       </c>
-      <c r="E15">
-        <v>-8354105</v>
-      </c>
       <c r="F15">
+        <v>-7103694</v>
+      </c>
+      <c r="G15">
         <v>-8483580</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>1025864</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>-53840252</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>-5883645</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>-30900633</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>-13477221</v>
       </c>
     </row>
@@ -4645,15 +4920,18 @@
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B18">
+        <v>-26458579</v>
+      </c>
+      <c r="C18">
         <v>-195414882</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>-9794526</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0</v>
       </c>
     </row>
@@ -4667,21 +4945,24 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>2528136</v>
+      </c>
+      <c r="C20">
         <v>4450132</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-2299958</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
-      <c r="J20">
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="K20">
         <v>2160710</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>32827</v>
       </c>
     </row>
@@ -4689,16 +4970,13 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="E21">
-        <v>-1280942</v>
-      </c>
-      <c r="I21">
+      <c r="J21">
         <v>-2898259</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>3673212</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>265968</v>
       </c>
     </row>
@@ -4706,16 +4984,13 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="E22">
-        <v>-3713582</v>
-      </c>
-      <c r="I22">
+      <c r="J22">
         <v>903639</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>10770956</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>7826433</v>
       </c>
     </row>
@@ -4749,33 +5024,36 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-458666598</v>
+      </c>
+      <c r="C28">
         <v>-160185930</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-730180294</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>-1080509418</v>
       </c>
-      <c r="E28">
-        <v>77032498</v>
-      </c>
       <c r="F28">
+        <v>-267690457</v>
+      </c>
+      <c r="G28">
         <v>-114868861</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>-311258722</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>-98352121</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>34853447</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>193214255</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>32334915</v>
       </c>
     </row>
@@ -4783,16 +5061,16 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>-6273412</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>-523309567</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>0</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>0</v>
       </c>
     </row>
@@ -4806,33 +5084,36 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>-300662100</v>
+      </c>
+      <c r="C31">
         <v>-82621235</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-216817614</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>-243111935</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>-93079514</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>-45245739</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>-289100978</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>-57255009</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>-62440075</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>-17622181</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>-51201567</v>
       </c>
     </row>
@@ -4846,33 +5127,36 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-515554</v>
+      </c>
+      <c r="C33">
         <v>-9945313</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>-2308102</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>-2771841</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>376514</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>424822</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>2607306</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>2215027</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>-910310</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>-959214</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>175606</v>
       </c>
     </row>
@@ -4896,33 +5180,36 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>95306526</v>
+      </c>
+      <c r="C37">
         <v>129330784</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>-101887129</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>756644</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>-5336279</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>-16839937</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>-60303812</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>-25867949</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>-524195</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>-104429261</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>10948116</v>
       </c>
     </row>
@@ -4936,33 +5223,36 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-266625620</v>
+      </c>
+      <c r="C39">
         <v>-57788816</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>-457862766</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-197316407</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>-10162817</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>-63828379</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>-114336110</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>-29425921</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>65006444</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>-130501841</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>3839601</v>
       </c>
     </row>
@@ -4971,33 +5261,36 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>-117101650</v>
+      </c>
+      <c r="C40">
         <v>13268286</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>80389247</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>-18915305</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>-92746647</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>-1666228</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>83509636</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>31307380</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>3066235</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>-2036188</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>8236744</v>
       </c>
     </row>
@@ -5011,30 +5304,33 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>31295494</v>
+      </c>
+      <c r="C42">
         <v>20003187</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>18787316</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>4867683</v>
       </c>
-      <c r="E42">
-        <v>-1000000</v>
-      </c>
       <c r="F42">
+        <v>20253537</v>
+      </c>
+      <c r="G42">
         <v>11307526</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>8127802</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>41448231</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>-488617</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>-167998</v>
       </c>
     </row>
@@ -5048,33 +5344,36 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-254149</v>
+      </c>
+      <c r="C44">
         <v>-735918</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-38768386</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>-39441131</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>6245353</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>-9761401</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>44528922</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>6517920</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>53191859</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>-923122</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>3547293</v>
       </c>
     </row>
@@ -5093,33 +5392,36 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>151929447</v>
+      </c>
+      <c r="C47">
         <v>-162467519</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>81488454</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>-40273266</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>-89375788</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>12386094</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>12725059</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>-60762778</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>-62269602</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>121587623</v>
       </c>
-      <c r="K47">
+      <c r="L47">
         <v>3953812</v>
       </c>
     </row>
@@ -5128,33 +5430,36 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-52038992</v>
+      </c>
+      <c r="C48">
         <v>-9229386</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>-86927902</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>-20994293</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>-3864816</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>-1645619</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>983453</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>-6529022</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>-4778131</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>-1008266</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>458653</v>
       </c>
     </row>
@@ -5163,21 +5468,27 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>-365038237</v>
+      </c>
+      <c r="C49">
         <v>-469115735</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>-502207315</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>-1029328262</v>
       </c>
       <c r="F49">
+        <v>-185693966</v>
+      </c>
+      <c r="G49">
         <v>-96320615</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>-48088078</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>-77778337</v>
       </c>
     </row>
@@ -5205,16 +5516,19 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="C54">
+      <c r="B54">
+        <v>-647184</v>
+      </c>
+      <c r="D54">
         <v>-171855</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>0</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>-2160710</v>
       </c>
-      <c r="K54">
+      <c r="L54">
         <v>-32827</v>
       </c>
     </row>
@@ -5257,19 +5571,19 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>-806152</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>0</v>
       </c>
-      <c r="E62">
-        <v>17552100</v>
-      </c>
-      <c r="H62">
+      <c r="F62">
+        <v>-1000000</v>
+      </c>
+      <c r="I62">
         <v>0</v>
       </c>
-      <c r="I62">
+      <c r="J62">
         <v>-5312101</v>
       </c>
     </row>
@@ -5294,33 +5608,36 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-651345840</v>
+      </c>
+      <c r="C67">
         <v>-71252567</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>-428503635</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>-84542318</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>-43607628</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>-22095128</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>-89669978</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>-70451695</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>-45082744</v>
       </c>
-      <c r="J67">
+      <c r="K67">
         <v>6317149</v>
       </c>
-      <c r="K67">
+      <c r="L67">
         <v>-27499067</v>
       </c>
     </row>
@@ -5368,33 +5685,36 @@
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
+      <c r="B76">
+        <v>-357609522</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>0</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>361234</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>3713582</v>
       </c>
-      <c r="G77">
+      <c r="H77">
         <v>3652873</v>
       </c>
-      <c r="H77">
+      <c r="I77">
         <v>9150837</v>
       </c>
-      <c r="I77">
+      <c r="J77">
         <v>2793705</v>
       </c>
-      <c r="J77">
+      <c r="K77">
         <v>26001500</v>
       </c>
-      <c r="K77">
+      <c r="L77">
         <v>15577842</v>
       </c>
     </row>
@@ -5403,33 +5723,36 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-293736318</v>
+      </c>
+      <c r="C78">
         <v>-71252567</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>-428503635</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>-84903552</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>-47321210</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>-22095128</v>
       </c>
-      <c r="G78">
+      <c r="H78">
         <v>-93322851</v>
       </c>
-      <c r="H78">
+      <c r="I78">
         <v>-79602532</v>
       </c>
-      <c r="I78">
+      <c r="J78">
         <v>-47876449</v>
       </c>
-      <c r="J78">
+      <c r="K78">
         <v>-19684351</v>
       </c>
-      <c r="K78">
+      <c r="L78">
         <v>-43076909</v>
       </c>
     </row>
@@ -5544,33 +5867,36 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>628425381</v>
+      </c>
+      <c r="C101">
         <v>48615714</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>1418179757</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>1443915777</v>
       </c>
-      <c r="E101">
-        <v>191035455</v>
-      </c>
       <c r="F101">
+        <v>183370025</v>
+      </c>
+      <c r="G101">
         <v>145764664</v>
       </c>
-      <c r="G101">
+      <c r="H101">
         <v>178191856</v>
       </c>
-      <c r="H101">
+      <c r="I101">
         <v>133521590</v>
       </c>
-      <c r="I101">
+      <c r="J101">
         <v>8468858</v>
       </c>
-      <c r="J101">
+      <c r="K101">
         <v>-20934216</v>
       </c>
-      <c r="K101">
+      <c r="L101">
         <v>10779707</v>
       </c>
     </row>
@@ -5588,22 +5914,22 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B104">
+      <c r="C104">
         <v>254995</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>1320711229</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>1322837997</v>
       </c>
-      <c r="F104">
+      <c r="G104">
         <v>-59555</v>
       </c>
-      <c r="G104">
+      <c r="H104">
         <v>-76046</v>
       </c>
-      <c r="H104">
+      <c r="I104">
         <v>212004</v>
       </c>
     </row>
@@ -5616,7 +5942,7 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="J106">
+      <c r="K106">
         <v>-18408566</v>
       </c>
     </row>
@@ -5624,19 +5950,19 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C107">
-        <v>30000000</v>
-      </c>
       <c r="D107">
         <v>30000000</v>
       </c>
-      <c r="G107">
-        <v>0</v>
+      <c r="E107">
+        <v>30000000</v>
       </c>
       <c r="H107">
         <v>0</v>
       </c>
-      <c r="K107">
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="L107">
         <v>22000000</v>
       </c>
     </row>
@@ -5650,33 +5976,36 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
+        <v>830093298</v>
+      </c>
+      <c r="C109">
         <v>16279603</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>118283136</v>
       </c>
-      <c r="D109">
+      <c r="E109">
         <v>163270546</v>
       </c>
-      <c r="E109">
-        <v>240746227</v>
-      </c>
       <c r="F109">
+        <v>330954571</v>
+      </c>
+      <c r="G109">
         <v>150197629</v>
       </c>
-      <c r="G109">
+      <c r="H109">
         <v>260484128</v>
       </c>
-      <c r="H109">
+      <c r="I109">
         <v>185190481</v>
       </c>
-      <c r="I109">
+      <c r="J109">
         <v>48649964</v>
       </c>
-      <c r="J109">
+      <c r="K109">
         <v>51147213</v>
       </c>
-      <c r="K109">
+      <c r="L109">
         <v>-2580974</v>
       </c>
     </row>
@@ -5684,6 +6013,12 @@
       <c r="A110" t="str">
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
+      <c r="B110">
+        <v>-203511771</v>
+      </c>
+      <c r="F110">
+        <v>-90208344</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -5699,6 +6034,12 @@
       <c r="A113" t="str">
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
+      <c r="B113">
+        <v>-4737545</v>
+      </c>
+      <c r="F113">
+        <v>-5045485</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -5719,14 +6060,11 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="C117">
-        <v>0</v>
-      </c>
       <c r="D117">
         <v>0</v>
       </c>
-      <c r="G117">
-        <v>-18145052</v>
+      <c r="E117">
+        <v>0</v>
       </c>
       <c r="H117">
         <v>-18145052</v>
@@ -5735,6 +6073,9 @@
         <v>-18145052</v>
       </c>
       <c r="J117">
+        <v>-18145052</v>
+      </c>
+      <c r="K117">
         <v>-21675261</v>
       </c>
     </row>
@@ -5743,33 +6084,36 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-76329934</v>
+      </c>
+      <c r="C118">
         <v>-28304263</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>-120416830</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>-99531427</v>
       </c>
-      <c r="E118">
-        <v>-65268707</v>
-      </c>
       <c r="F118">
+        <v>-65187215</v>
+      </c>
+      <c r="G118">
         <v>-10162847</v>
       </c>
-      <c r="G118">
+      <c r="H118">
         <v>-65556831</v>
       </c>
-      <c r="H118">
+      <c r="I118">
         <v>-34638819</v>
       </c>
-      <c r="I118">
+      <c r="J118">
         <v>-25582724</v>
       </c>
-      <c r="J118">
+      <c r="K118">
         <v>-20130912</v>
       </c>
-      <c r="K118">
+      <c r="L118">
         <v>-8806015</v>
       </c>
     </row>
@@ -5778,33 +6122,36 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
+        <v>82911333</v>
+      </c>
+      <c r="C119">
         <v>60385379</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>69602222</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>27338661</v>
       </c>
-      <c r="E119">
+      <c r="F119">
         <v>12856498</v>
       </c>
-      <c r="F119">
+      <c r="G119">
         <v>5789437</v>
       </c>
-      <c r="G119">
+      <c r="H119">
         <v>1485657</v>
       </c>
-      <c r="H119">
+      <c r="I119">
         <v>902976</v>
       </c>
-      <c r="I119">
+      <c r="J119">
         <v>698119</v>
       </c>
-      <c r="J119">
+      <c r="K119">
         <v>593</v>
       </c>
-      <c r="K119">
+      <c r="L119">
         <v>1142</v>
       </c>
     </row>
@@ -5827,16 +6174,13 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="E123">
-        <v>2701437</v>
-      </c>
-      <c r="I123">
+      <c r="J123">
         <v>2848551</v>
       </c>
-      <c r="J123">
+      <c r="K123">
         <v>-11867283</v>
       </c>
-      <c r="K123">
+      <c r="L123">
         <v>165554</v>
       </c>
     </row>
@@ -5850,33 +6194,36 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>-388605880</v>
+      </c>
+      <c r="C125">
         <v>-491752588</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>486490800</v>
       </c>
-      <c r="D125">
+      <c r="E125">
         <v>330045197</v>
       </c>
-      <c r="E125">
+      <c r="F125">
         <v>-46931569</v>
       </c>
-      <c r="F125">
+      <c r="G125">
         <v>27348921</v>
       </c>
-      <c r="G125">
+      <c r="H125">
         <v>40433800</v>
       </c>
-      <c r="H125">
+      <c r="I125">
         <v>-14708442</v>
       </c>
-      <c r="I125">
+      <c r="J125">
         <v>-16730315</v>
       </c>
-      <c r="J125">
+      <c r="K125">
         <v>43941329</v>
       </c>
-      <c r="K125">
+      <c r="L125">
         <v>-3870826</v>
       </c>
     </row>
@@ -5891,27 +6238,30 @@
         <v>141243243</v>
       </c>
       <c r="D126">
+        <v>141243243</v>
+      </c>
+      <c r="E126">
         <v>65285871</v>
       </c>
-      <c r="E126">
+      <c r="F126">
         <v>44157919</v>
       </c>
-      <c r="F126">
+      <c r="G126">
         <v>18887737</v>
       </c>
-      <c r="G126">
+      <c r="H126">
         <v>51051049</v>
       </c>
-      <c r="H126">
+      <c r="I126">
         <v>10990976</v>
       </c>
-      <c r="I126">
+      <c r="J126">
         <v>14808978</v>
       </c>
-      <c r="J126">
+      <c r="K126">
         <v>-21455677</v>
       </c>
-      <c r="K126">
+      <c r="L126">
         <v>8491086</v>
       </c>
     </row>
@@ -5920,33 +6270,36 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>-247362637</v>
+      </c>
+      <c r="C127">
         <v>-350509345</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>627734043</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>395331068</v>
       </c>
-      <c r="E127">
+      <c r="F127">
         <v>-2773650</v>
       </c>
-      <c r="F127">
+      <c r="G127">
         <v>46236658</v>
       </c>
-      <c r="G127">
+      <c r="H127">
         <v>91484849</v>
       </c>
-      <c r="H127">
+      <c r="I127">
         <v>-3717466</v>
       </c>
-      <c r="I127">
+      <c r="J127">
         <v>-1921337</v>
       </c>
-      <c r="J127">
+      <c r="K127">
         <v>22485652</v>
       </c>
-      <c r="K127">
+      <c r="L127">
         <v>4620260</v>
       </c>
     </row>
@@ -5958,18 +6311,24 @@
         <v>748413520</v>
       </c>
       <c r="C128">
-        <v>120679477</v>
+        <v>748413520</v>
       </c>
       <c r="D128">
         <v>120679477</v>
       </c>
+      <c r="E128">
+        <v>120679477</v>
+      </c>
       <c r="F128">
         <v>120679477</v>
       </c>
       <c r="G128">
+        <v>120679477</v>
+      </c>
+      <c r="H128">
         <v>29194628</v>
       </c>
-      <c r="H128">
+      <c r="I128">
         <v>29194628</v>
       </c>
     </row>
@@ -5978,34 +6337,40 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>501050883</v>
+      </c>
+      <c r="C129">
         <v>397904175</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>748413520</v>
       </c>
-      <c r="D129">
+      <c r="E129">
         <v>516010545</v>
       </c>
       <c r="F129">
+        <v>117905827</v>
+      </c>
+      <c r="G129">
         <v>166916135</v>
       </c>
-      <c r="G129">
+      <c r="H129">
         <v>120679477</v>
       </c>
-      <c r="H129">
+      <c r="I129">
         <v>25477162</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:L129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6018,6 +6383,7 @@
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
+    <col min="12" max="12" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6025,33 +6391,36 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -6065,24 +6434,27 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>103430314</v>
+      </c>
+      <c r="C3">
         <v>-469115735</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>526142940</v>
       </c>
-      <c r="D3">
-        <v>-834968866</v>
-      </c>
       <c r="E3">
-        <v>-98038781</v>
+        <v>-842634296</v>
       </c>
       <c r="F3">
+        <v>-90373351</v>
+      </c>
+      <c r="G3">
         <v>-96320615</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>29690259</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>-102974009</v>
       </c>
     </row>
@@ -6091,24 +6463,27 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>65385723</v>
+      </c>
+      <c r="C4">
         <v>6901000</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>208020787</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>23033728</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>2685792</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>11211018</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>146885552</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>13915045</v>
       </c>
     </row>
@@ -6117,15 +6492,24 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>337172443</v>
+      </c>
+      <c r="C5">
         <v>-315830805</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-31228964</v>
       </c>
+      <c r="E5">
+        <v>-53849063</v>
+      </c>
       <c r="F5">
+        <v>60762453</v>
+      </c>
+      <c r="G5">
         <v>7337228</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>95711308</v>
       </c>
     </row>
@@ -6134,24 +6518,27 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>32154403</v>
+      </c>
+      <c r="C6">
         <v>27484584</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>23872967</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>17774946</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>12820574</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>11372131</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>12974149</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>5135600</v>
       </c>
     </row>
@@ -6160,24 +6547,27 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
+        <v>-15729</v>
+      </c>
+      <c r="C7">
         <v>-320540</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-11744</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-15476</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-17314</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>-21791</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-12525</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>-70878</v>
       </c>
     </row>
@@ -6186,15 +6576,24 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>-2245557</v>
+      </c>
+      <c r="C8">
         <v>5607180</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>3873100</v>
       </c>
+      <c r="E8">
+        <v>2870030</v>
+      </c>
       <c r="F8">
+        <v>-1378000</v>
+      </c>
+      <c r="G8">
         <v>97058</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>-2451763</v>
       </c>
     </row>
@@ -6218,24 +6617,27 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>25703691</v>
+      </c>
+      <c r="C12">
         <v>-32081116</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>-21378158</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>19862049</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>47957307</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>4373410</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>30335331</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>8862762</v>
       </c>
     </row>
@@ -6254,24 +6656,27 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>114541328</v>
+      </c>
+      <c r="C15">
         <v>-125556163</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-45079697</v>
       </c>
-      <c r="D15">
-        <v>-83295675</v>
-      </c>
       <c r="E15">
-        <v>129475</v>
+        <v>-84546086</v>
       </c>
       <c r="F15">
+        <v>1379886</v>
+      </c>
+      <c r="G15">
         <v>-8483580</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>54866116</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>-47956607</v>
       </c>
     </row>
@@ -6290,9 +6695,12 @@
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B18">
+        <v>168956303</v>
+      </c>
+      <c r="C18">
         <v>-195414882</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0</v>
       </c>
     </row>
@@ -6306,9 +6714,12 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>-1921996</v>
+      </c>
+      <c r="C20">
         <v>4450132</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0</v>
       </c>
     </row>
@@ -6352,24 +6763,27 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-298480668</v>
+      </c>
+      <c r="C28">
         <v>-160185930</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>350329124</v>
       </c>
-      <c r="D28">
-        <v>-1157541916</v>
-      </c>
       <c r="E28">
-        <v>191901359</v>
+        <v>-812818961</v>
       </c>
       <c r="F28">
+        <v>-152821596</v>
+      </c>
+      <c r="G28">
         <v>-114868861</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>-212906601</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>-133205568</v>
       </c>
     </row>
@@ -6377,10 +6791,10 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>517036155</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>0</v>
       </c>
     </row>
@@ -6394,24 +6808,27 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>-218040865</v>
+      </c>
+      <c r="C31">
         <v>-82621235</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>26294321</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>-150032421</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>-47833775</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>-45245739</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>-231845969</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>5185066</v>
       </c>
     </row>
@@ -6425,24 +6842,27 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>9429759</v>
+      </c>
+      <c r="C33">
         <v>-9945313</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>463739</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>-3148355</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>-48308</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>424822</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>392279</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>3125337</v>
       </c>
     </row>
@@ -6466,24 +6886,27 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>-34024258</v>
+      </c>
+      <c r="C37">
         <v>129330784</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>-102643773</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>6092923</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>11503658</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>-16839937</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>-34435863</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>-25343754</v>
       </c>
     </row>
@@ -6497,24 +6920,27 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-208836804</v>
+      </c>
+      <c r="C39">
         <v>-57788816</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>-260546359</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-187153590</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>53665562</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>-63828379</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>-84910189</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>-94432365</v>
       </c>
     </row>
@@ -6523,24 +6949,27 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>-130369936</v>
+      </c>
+      <c r="C40">
         <v>13268286</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>99304552</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>73831342</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>-91080419</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>-1666228</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>52202256</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>28241145</v>
       </c>
     </row>
@@ -6554,21 +6983,24 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>11292307</v>
+      </c>
+      <c r="C42">
         <v>20003187</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>13919633</v>
       </c>
-      <c r="D42">
-        <v>5867683</v>
-      </c>
       <c r="E42">
-        <v>-12307526</v>
+        <v>-15385854</v>
       </c>
       <c r="F42">
+        <v>8946011</v>
+      </c>
+      <c r="G42">
         <v>11307526</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>-33320429</v>
       </c>
     </row>
@@ -6582,24 +7014,27 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>481769</v>
+      </c>
+      <c r="C44">
         <v>-735918</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>672745</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>-45686484</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>16006754</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>-9761401</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>38011002</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>-46673939</v>
       </c>
     </row>
@@ -6618,24 +7053,27 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>314396966</v>
+      </c>
+      <c r="C47">
         <v>-162467519</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>121761720</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>49102522</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>-101761882</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>12386094</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>73487837</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>1506824</v>
       </c>
     </row>
@@ -6644,24 +7082,27 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-42809606</v>
+      </c>
+      <c r="C48">
         <v>-9229386</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>-65933609</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>-17129477</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>-2219197</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>-1645619</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>7512475</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>-1750891</v>
       </c>
     </row>
@@ -6670,15 +7111,24 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>104077498</v>
+      </c>
+      <c r="C49">
         <v>-469115735</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>527120947</v>
       </c>
+      <c r="E49">
+        <v>-843634296</v>
+      </c>
       <c r="F49">
+        <v>-89373351</v>
+      </c>
+      <c r="G49">
         <v>-96320615</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>29690259</v>
       </c>
     </row>
@@ -6746,13 +7196,13 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>-806152</v>
       </c>
-      <c r="D62">
-        <v>-17552100</v>
-      </c>
-      <c r="H62">
+      <c r="E62">
+        <v>1000000</v>
+      </c>
+      <c r="I62">
         <v>5312101</v>
       </c>
     </row>
@@ -6777,24 +7227,27 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-580093273</v>
+      </c>
+      <c r="C67">
         <v>-71252567</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>-343961317</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>-40934690</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>-21512500</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>-22095128</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>-19218283</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>-25368951</v>
       </c>
     </row>
@@ -6847,16 +7300,16 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>-361234</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>-3352348</v>
       </c>
-      <c r="G77">
+      <c r="H77">
         <v>-5497964</v>
       </c>
-      <c r="H77">
+      <c r="I77">
         <v>6357132</v>
       </c>
     </row>
@@ -6865,24 +7318,27 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-222483751</v>
+      </c>
+      <c r="C78">
         <v>-71252567</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>-343600083</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>-37582342</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>-25226082</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>-22095128</v>
       </c>
-      <c r="G78">
+      <c r="H78">
         <v>-13720319</v>
       </c>
-      <c r="H78">
+      <c r="I78">
         <v>-31726083</v>
       </c>
     </row>
@@ -6997,24 +7453,27 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>579809667</v>
+      </c>
+      <c r="C101">
         <v>48615714</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>-25736020</v>
       </c>
-      <c r="D101">
-        <v>1252880322</v>
-      </c>
       <c r="E101">
-        <v>45270791</v>
+        <v>1260545752</v>
       </c>
       <c r="F101">
+        <v>37605361</v>
+      </c>
+      <c r="G101">
         <v>145764664</v>
       </c>
-      <c r="G101">
+      <c r="H101">
         <v>44670266</v>
       </c>
-      <c r="H101">
+      <c r="I101">
         <v>125052732</v>
       </c>
     </row>
@@ -7032,16 +7491,16 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B104">
+      <c r="C104">
         <v>254995</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>-2126768</v>
       </c>
-      <c r="F104">
+      <c r="G104">
         <v>-59555</v>
       </c>
-      <c r="G104">
+      <c r="H104">
         <v>-288050</v>
       </c>
     </row>
@@ -7059,10 +7518,10 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C107">
+      <c r="D107">
         <v>0</v>
       </c>
-      <c r="G107">
+      <c r="H107">
         <v>0</v>
       </c>
     </row>
@@ -7076,24 +7535,27 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
+        <v>813813695</v>
+      </c>
+      <c r="C109">
         <v>16279603</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>-44987410</v>
       </c>
-      <c r="D109">
-        <v>-77475681</v>
-      </c>
       <c r="E109">
-        <v>90548598</v>
+        <v>-167684025</v>
       </c>
       <c r="F109">
+        <v>180756942</v>
+      </c>
+      <c r="G109">
         <v>150197629</v>
       </c>
-      <c r="G109">
+      <c r="H109">
         <v>75293647</v>
       </c>
-      <c r="H109">
+      <c r="I109">
         <v>136540517</v>
       </c>
     </row>
@@ -7136,13 +7598,13 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="C117">
+      <c r="D117">
         <v>0</v>
       </c>
-      <c r="G117">
+      <c r="H117">
         <v>0</v>
       </c>
-      <c r="H117">
+      <c r="I117">
         <v>0</v>
       </c>
     </row>
@@ -7151,24 +7613,27 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-48025671</v>
+      </c>
+      <c r="C118">
         <v>-28304263</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>-20885403</v>
       </c>
-      <c r="D118">
-        <v>-34262720</v>
-      </c>
       <c r="E118">
-        <v>-55105860</v>
+        <v>-34344212</v>
       </c>
       <c r="F118">
+        <v>-55024368</v>
+      </c>
+      <c r="G118">
         <v>-10162847</v>
       </c>
-      <c r="G118">
+      <c r="H118">
         <v>-30918012</v>
       </c>
-      <c r="H118">
+      <c r="I118">
         <v>-9056095</v>
       </c>
     </row>
@@ -7177,24 +7642,27 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
+        <v>22525954</v>
+      </c>
+      <c r="C119">
         <v>60385379</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>42263561</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>14482163</v>
       </c>
-      <c r="E119">
+      <c r="F119">
         <v>7067061</v>
       </c>
-      <c r="F119">
+      <c r="G119">
         <v>5789437</v>
       </c>
-      <c r="G119">
+      <c r="H119">
         <v>582681</v>
       </c>
-      <c r="H119">
+      <c r="I119">
         <v>204857</v>
       </c>
     </row>
@@ -7228,24 +7696,27 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>103146708</v>
+      </c>
+      <c r="C125">
         <v>-491752588</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>156445603</v>
       </c>
-      <c r="D125">
+      <c r="E125">
         <v>376976766</v>
       </c>
-      <c r="E125">
+      <c r="F125">
         <v>-74280490</v>
       </c>
-      <c r="F125">
+      <c r="G125">
         <v>27348921</v>
       </c>
-      <c r="G125">
+      <c r="H125">
         <v>55142242</v>
       </c>
-      <c r="H125">
+      <c r="I125">
         <v>2021873</v>
       </c>
     </row>
@@ -7254,24 +7725,27 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
         <v>141243243</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>75957372</v>
       </c>
-      <c r="D126">
+      <c r="E126">
         <v>21127952</v>
       </c>
-      <c r="E126">
+      <c r="F126">
         <v>25270182</v>
       </c>
-      <c r="F126">
+      <c r="G126">
         <v>18887737</v>
       </c>
-      <c r="G126">
+      <c r="H126">
         <v>40060073</v>
       </c>
-      <c r="H126">
+      <c r="I126">
         <v>-3818002</v>
       </c>
     </row>
@@ -7280,24 +7754,27 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>103146708</v>
+      </c>
+      <c r="C127">
         <v>-350509345</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>232402975</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>398104718</v>
       </c>
-      <c r="E127">
+      <c r="F127">
         <v>-49010308</v>
       </c>
-      <c r="F127">
+      <c r="G127">
         <v>46236658</v>
       </c>
-      <c r="G127">
+      <c r="H127">
         <v>95202315</v>
       </c>
-      <c r="H127">
+      <c r="I127">
         <v>-1796129</v>
       </c>
     </row>
@@ -7306,15 +7783,24 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
         <v>748413520</v>
       </c>
-      <c r="C128">
+      <c r="D128">
         <v>0</v>
       </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
       <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
         <v>120679477</v>
       </c>
-      <c r="G128">
+      <c r="H128">
         <v>0</v>
       </c>
     </row>
@@ -7323,28 +7809,37 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>103146708</v>
+      </c>
+      <c r="C129">
         <v>397904175</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>232402975</v>
       </c>
+      <c r="E129">
+        <v>398104718</v>
+      </c>
       <c r="F129">
+        <v>-49010308</v>
+      </c>
+      <c r="G129">
         <v>166916135</v>
       </c>
-      <c r="G129">
+      <c r="H129">
         <v>95202315</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:L129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -7357,6 +7852,7 @@
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
+    <col min="12" max="12" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7364,33 +7860,36 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -7404,24 +7903,27 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>-682176777</v>
+      </c>
+      <c r="C3">
         <v>-875980442</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>-503185322</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>-999638003</v>
       </c>
-      <c r="E3">
-        <v>-267643146</v>
-      </c>
-      <c r="G3">
+      <c r="F3">
+        <v>-259977716</v>
+      </c>
+      <c r="H3">
         <v>-48088078</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>58558396</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>12848534</v>
       </c>
     </row>
@@ -7430,24 +7932,27 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>303341238</v>
+      </c>
+      <c r="C4">
         <v>240641307</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>244951325</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>183816090</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>174697407</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>164513497</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>167186101</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>17092249</v>
       </c>
     </row>
@@ -7456,15 +7961,18 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-63736389</v>
+      </c>
+      <c r="C5">
         <v>-340146379</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-16978346</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>109961926</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>98657147</v>
       </c>
     </row>
@@ -7473,24 +7981,27 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>101286900</v>
+      </c>
+      <c r="C6">
         <v>81953071</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>65840618</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>54941800</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>42302454</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>32234100</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>20585442</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>11926139</v>
       </c>
     </row>
@@ -7499,24 +8010,27 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
+        <v>-363489</v>
+      </c>
+      <c r="C7">
         <v>-365074</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-66325</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>-67106</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>-122508</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-62023</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>-391852</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>-136354</v>
       </c>
     </row>
@@ -7525,15 +8039,18 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>10104753</v>
+      </c>
+      <c r="C8">
         <v>10972310</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>5462188</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>-862675</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1388032</v>
       </c>
     </row>
@@ -7557,24 +8074,27 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>-7893534</v>
+      </c>
+      <c r="C12">
         <v>14360082</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>50814608</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>102528097</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>91528810</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>64071174</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>20130319</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>8804874</v>
       </c>
     </row>
@@ -7593,24 +8113,27 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>-140640618</v>
+      </c>
+      <c r="C15">
         <v>-253802060</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-136729477</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>-36783664</v>
       </c>
-      <c r="E15">
-        <v>-1444596</v>
-      </c>
-      <c r="G15">
+      <c r="F15">
+        <v>-194185</v>
+      </c>
+      <c r="H15">
         <v>1025864</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>-30900633</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>-13477221</v>
       </c>
     </row>
@@ -7638,19 +8161,19 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>2150174</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-2299958</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>2160710</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>32827</v>
       </c>
     </row>
@@ -7658,10 +8181,10 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>3673212</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>265968</v>
       </c>
     </row>
@@ -7669,10 +8192,10 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>10770956</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>7826433</v>
       </c>
     </row>
@@ -7706,24 +8229,27 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-921156435</v>
+      </c>
+      <c r="C28">
         <v>-775497363</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-730180294</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>-1293416019</v>
       </c>
-      <c r="E28">
-        <v>-269079671</v>
-      </c>
-      <c r="G28">
+      <c r="F28">
+        <v>-613802626</v>
+      </c>
+      <c r="H28">
         <v>-311258722</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>193214255</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>32334915</v>
       </c>
     </row>
@@ -7731,13 +8257,13 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>-6273412</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>-523309567</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>0</v>
       </c>
     </row>
@@ -7751,24 +8277,27 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>-424400200</v>
+      </c>
+      <c r="C31">
         <v>-254193110</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-216817614</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>-474957904</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>-319740417</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>-289100978</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>-17622181</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>-51201567</v>
       </c>
     </row>
@@ -7782,24 +8311,27 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-3200170</v>
+      </c>
+      <c r="C33">
         <v>-12678237</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>-2308102</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>-2379562</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>3894130</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>2607306</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>-959214</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>175606</v>
       </c>
     </row>
@@ -7823,24 +8355,27 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>-1244324</v>
+      </c>
+      <c r="C37">
         <v>44283592</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>-101887129</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>-33679219</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>-65115896</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>-60303812</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>-104429261</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>10948116</v>
       </c>
     </row>
@@ -7854,24 +8389,27 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-714325569</v>
+      </c>
+      <c r="C39">
         <v>-451823203</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>-457862766</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>-282226596</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>-189505371</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>-114336110</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>-130501841</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>3839601</v>
       </c>
     </row>
@@ -7880,24 +8418,27 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>56034244</v>
+      </c>
+      <c r="C40">
         <v>95323761</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>80389247</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>33286951</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>-12303246</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>83509636</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>-2036188</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>8236744</v>
       </c>
     </row>
@@ -7911,21 +8452,24 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>29829273</v>
+      </c>
+      <c r="C42">
         <v>27482977</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>18787316</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>-28452746</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>8127802</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>-488617</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>-167998</v>
       </c>
     </row>
@@ -7939,24 +8483,27 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-45267888</v>
+      </c>
+      <c r="C44">
         <v>-29742903</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-38768386</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>-1430129</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>-2417584</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>44528922</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>-923122</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>3547293</v>
       </c>
     </row>
@@ -7975,24 +8522,27 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>322793689</v>
+      </c>
+      <c r="C47">
         <v>-93365159</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>81488454</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>33214571</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>-14381127</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>12725059</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>121587623</v>
       </c>
-      <c r="K47">
+      <c r="L47">
         <v>3953812</v>
       </c>
     </row>
@@ -8001,24 +8551,27 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-135102078</v>
+      </c>
+      <c r="C48">
         <v>-94511669</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>-86927902</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>-13481818</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>1896768</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>983453</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>-1008266</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>458653</v>
       </c>
     </row>
@@ -8027,15 +8580,18 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>-681551586</v>
+      </c>
+      <c r="C49">
         <v>-875002435</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>-502207315</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>-999638003</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>-48088078</v>
       </c>
     </row>
@@ -8063,16 +8619,16 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>-171855</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>0</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>-2160710</v>
       </c>
-      <c r="K54">
+      <c r="L54">
         <v>-32827</v>
       </c>
     </row>
@@ -8115,7 +8671,7 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>-806152</v>
       </c>
     </row>
@@ -8140,24 +8696,27 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-1036241847</v>
+      </c>
+      <c r="C67">
         <v>-477661074</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>-428503635</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>-103760601</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>-88194862</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>-89669978</v>
       </c>
-      <c r="J67">
+      <c r="K67">
         <v>6317149</v>
       </c>
-      <c r="K67">
+      <c r="L67">
         <v>-27499067</v>
       </c>
     </row>
@@ -8210,22 +8769,22 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>0</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>-5136730</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>4572750</v>
       </c>
-      <c r="G77">
+      <c r="H77">
         <v>3652873</v>
       </c>
-      <c r="J77">
+      <c r="K77">
         <v>26001500</v>
       </c>
-      <c r="K77">
+      <c r="L77">
         <v>15577842</v>
       </c>
     </row>
@@ -8234,24 +8793,27 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-674918743</v>
+      </c>
+      <c r="C78">
         <v>-477661074</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>-428503635</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>-98623871</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>-92767612</v>
       </c>
-      <c r="G78">
+      <c r="H78">
         <v>-93322851</v>
       </c>
-      <c r="J78">
+      <c r="K78">
         <v>-19684351</v>
       </c>
-      <c r="K78">
+      <c r="L78">
         <v>-43076909</v>
       </c>
     </row>
@@ -8366,24 +8928,27 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>1863235113</v>
+      </c>
+      <c r="C101">
         <v>1321030807</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>1418179757</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>1488586043</v>
       </c>
-      <c r="E101">
-        <v>360758453</v>
-      </c>
-      <c r="G101">
+      <c r="F101">
+        <v>353093023</v>
+      </c>
+      <c r="H101">
         <v>178191856</v>
       </c>
-      <c r="J101">
+      <c r="K101">
         <v>-20934216</v>
       </c>
-      <c r="K101">
+      <c r="L101">
         <v>10779707</v>
       </c>
     </row>
@@ -8401,16 +8966,16 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B104">
+      <c r="C104">
         <v>1321025779</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>1320711229</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>1322549947</v>
       </c>
-      <c r="G104">
+      <c r="H104">
         <v>-76046</v>
       </c>
     </row>
@@ -8423,7 +8988,7 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="J106">
+      <c r="K106">
         <v>-18408566</v>
       </c>
     </row>
@@ -8431,16 +8996,16 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C107">
-        <v>30000000</v>
-      </c>
       <c r="D107">
         <v>30000000</v>
       </c>
-      <c r="G107">
+      <c r="E107">
+        <v>30000000</v>
+      </c>
+      <c r="H107">
         <v>0</v>
       </c>
-      <c r="K107">
+      <c r="L107">
         <v>22000000</v>
       </c>
     </row>
@@ -8454,24 +9019,27 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
+        <v>617421863</v>
+      </c>
+      <c r="C109">
         <v>-15634890</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>118283136</v>
       </c>
-      <c r="D109">
+      <c r="E109">
         <v>238564193</v>
       </c>
-      <c r="E109">
-        <v>452580391</v>
-      </c>
-      <c r="G109">
+      <c r="F109">
+        <v>542788735</v>
+      </c>
+      <c r="H109">
         <v>260484128</v>
       </c>
-      <c r="J109">
+      <c r="K109">
         <v>51147213</v>
       </c>
-      <c r="K109">
+      <c r="L109">
         <v>-2580974</v>
       </c>
     </row>
@@ -8514,16 +9082,16 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="C117">
-        <v>0</v>
-      </c>
       <c r="D117">
         <v>0</v>
       </c>
-      <c r="G117">
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="H117">
         <v>-18145052</v>
       </c>
-      <c r="J117">
+      <c r="K117">
         <v>-21675261</v>
       </c>
     </row>
@@ -8532,24 +9100,27 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-131559549</v>
+      </c>
+      <c r="C118">
         <v>-138558246</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>-120416830</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>-130449439</v>
       </c>
-      <c r="E118">
-        <v>-105242814</v>
-      </c>
-      <c r="G118">
+      <c r="F118">
+        <v>-105161322</v>
+      </c>
+      <c r="H118">
         <v>-65556831</v>
       </c>
-      <c r="J118">
+      <c r="K118">
         <v>-20130912</v>
       </c>
-      <c r="K118">
+      <c r="L118">
         <v>-8806015</v>
       </c>
     </row>
@@ -8558,24 +9129,27 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
+        <v>139657057</v>
+      </c>
+      <c r="C119">
         <v>124198164</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>69602222</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>27921342</v>
       </c>
-      <c r="E119">
+      <c r="F119">
         <v>13644036</v>
       </c>
-      <c r="G119">
+      <c r="H119">
         <v>1485657</v>
       </c>
-      <c r="J119">
+      <c r="K119">
         <v>593</v>
       </c>
-      <c r="K119">
+      <c r="L119">
         <v>1142</v>
       </c>
     </row>
@@ -8598,10 +9172,10 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="J123">
+      <c r="K123">
         <v>-11867283</v>
       </c>
-      <c r="K123">
+      <c r="L123">
         <v>165554</v>
       </c>
     </row>
@@ -8615,24 +9189,27 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>144816489</v>
+      </c>
+      <c r="C125">
         <v>-32610709</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>486490800</v>
       </c>
-      <c r="D125">
+      <c r="E125">
         <v>385187439</v>
       </c>
-      <c r="E125">
+      <c r="F125">
         <v>10232546</v>
       </c>
-      <c r="G125">
+      <c r="H125">
         <v>40433800</v>
       </c>
-      <c r="J125">
+      <c r="K125">
         <v>43941329</v>
       </c>
-      <c r="K125">
+      <c r="L125">
         <v>-3870826</v>
       </c>
     </row>
@@ -8641,24 +9218,27 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
+        <v>238328567</v>
+      </c>
+      <c r="C126">
         <v>263598749</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>141243243</v>
       </c>
-      <c r="D126">
+      <c r="E126">
         <v>105345944</v>
       </c>
-      <c r="E126">
+      <c r="F126">
         <v>80399990</v>
       </c>
-      <c r="G126">
+      <c r="H126">
         <v>51051049</v>
       </c>
-      <c r="J126">
+      <c r="K126">
         <v>-21455677</v>
       </c>
-      <c r="K126">
+      <c r="L126">
         <v>8491086</v>
       </c>
     </row>
@@ -8667,24 +9247,27 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>383145056</v>
+      </c>
+      <c r="C127">
         <v>230988040</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>627734043</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>490533383</v>
       </c>
-      <c r="E127">
+      <c r="F127">
         <v>90632536</v>
       </c>
-      <c r="G127">
+      <c r="H127">
         <v>91484849</v>
       </c>
-      <c r="J127">
+      <c r="K127">
         <v>22485652</v>
       </c>
-      <c r="K127">
+      <c r="L127">
         <v>4620260</v>
       </c>
     </row>
@@ -8696,12 +9279,15 @@
         <v>748413520</v>
       </c>
       <c r="C128">
-        <v>120679477</v>
+        <v>748413520</v>
       </c>
       <c r="D128">
         <v>120679477</v>
       </c>
-      <c r="G128">
+      <c r="E128">
+        <v>120679477</v>
+      </c>
+      <c r="H128">
         <v>29194628</v>
       </c>
     </row>
@@ -8710,21 +9296,24 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>1131558576</v>
+      </c>
+      <c r="C129">
         <v>979401560</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>748413520</v>
       </c>
-      <c r="D129">
+      <c r="E129">
         <v>611212860</v>
       </c>
-      <c r="G129">
+      <c r="H129">
         <v>120679477</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L129"/>
   </ignoredErrors>
 </worksheet>
 </file>